--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918D6738-E45F-4135-A2B4-6DB687A3BD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40693DA3-71AC-476D-BA65-BB3F15A94400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
   <sheets>
     <sheet name="logs" sheetId="1" r:id="rId1"/>
+    <sheet name="current" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">current!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">logs!$A$1:$F$127</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="60">
   <si>
     <t>date</t>
   </si>
@@ -213,17 +218,24 @@
   </si>
   <si>
     <t>VDE</t>
+  </si>
+  <si>
+    <t>ticker</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="6">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="174" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -236,6 +248,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -256,10 +275,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -279,8 +299,16 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -613,7 +641,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
-  <dimension ref="A1:F126"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
@@ -644,7 +673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45903.43472222222</v>
       </c>
@@ -665,7 +694,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45903.435416666667</v>
       </c>
@@ -686,7 +715,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45903.436111111114</v>
       </c>
@@ -707,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45903.436805555553</v>
       </c>
@@ -728,7 +757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45903.438194444447</v>
       </c>
@@ -770,7 +799,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45903.418749999997</v>
       </c>
@@ -791,7 +820,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45903.445138888892</v>
       </c>
@@ -812,7 +841,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45903.445833333331</v>
       </c>
@@ -823,17 +852,16 @@
         <v>19.989999999999998</v>
       </c>
       <c r="D10" s="6">
-        <v>7.92</v>
+        <v>39.6</v>
       </c>
       <c r="E10" s="6">
-        <f t="shared" si="0"/>
-        <v>2.5239898989898988</v>
+        <v>0.55984</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45903.448611111111</v>
       </c>
@@ -854,7 +882,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45903.455555555556</v>
       </c>
@@ -875,7 +903,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45903.463888888888</v>
       </c>
@@ -888,7 +916,7 @@
       <c r="D13" s="6">
         <v>506.14</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="9">
         <f t="shared" si="0"/>
         <v>3.9495001383016558E-2</v>
       </c>
@@ -896,7 +924,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45903.46597222222</v>
       </c>
@@ -917,7 +945,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45903.467361111114</v>
       </c>
@@ -938,7 +966,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45903.46875</v>
       </c>
@@ -959,7 +987,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>45903.470138888886</v>
       </c>
@@ -980,7 +1008,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45903.474999999999</v>
       </c>
@@ -1001,7 +1029,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>45903.476388888892</v>
       </c>
@@ -1022,7 +1050,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>45903.479861111111</v>
       </c>
@@ -1043,7 +1071,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>45903.480555555558</v>
       </c>
@@ -1064,7 +1092,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>45903.493750000001</v>
       </c>
@@ -1085,7 +1113,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -1106,7 +1134,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -1127,7 +1155,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>45903.495138888888</v>
       </c>
@@ -1148,7 +1176,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>45903.504861111112</v>
       </c>
@@ -1169,7 +1197,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>45904.404861111114</v>
       </c>
@@ -1190,7 +1218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>45904.406944444447</v>
       </c>
@@ -1211,7 +1239,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>45904.407638888886</v>
       </c>
@@ -1232,7 +1260,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>45904.412499999999</v>
       </c>
@@ -1253,7 +1281,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>45904.414583333331</v>
       </c>
@@ -1274,7 +1302,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>45904.418749999997</v>
       </c>
@@ -1295,7 +1323,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>45905.408333333333</v>
       </c>
@@ -1316,7 +1344,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>45908.665277777778</v>
       </c>
@@ -1337,7 +1365,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>45909.415277777778</v>
       </c>
@@ -1358,7 +1386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>45909.418055555558</v>
       </c>
@@ -1379,7 +1407,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>45909.427083333336</v>
       </c>
@@ -1400,7 +1428,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>45909.427777777775</v>
       </c>
@@ -1421,7 +1449,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>45909.431250000001</v>
       </c>
@@ -1463,7 +1491,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>45909.439583333333</v>
       </c>
@@ -1484,7 +1512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -1505,7 +1533,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -1526,7 +1554,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>45910</v>
       </c>
@@ -1547,7 +1575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>45910</v>
       </c>
@@ -1568,7 +1596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45911</v>
       </c>
@@ -1589,7 +1617,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45911</v>
       </c>
@@ -1610,7 +1638,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>45912</v>
       </c>
@@ -1631,7 +1659,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>45912</v>
       </c>
@@ -1652,7 +1680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>45912</v>
       </c>
@@ -1673,7 +1701,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>45912</v>
       </c>
@@ -1694,7 +1722,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>45923</v>
       </c>
@@ -1715,7 +1743,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>45923</v>
       </c>
@@ -1736,7 +1764,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>45923</v>
       </c>
@@ -1757,7 +1785,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>45923</v>
       </c>
@@ -1778,7 +1806,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>45923</v>
       </c>
@@ -1799,7 +1827,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>45923</v>
       </c>
@@ -1820,7 +1848,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>45924</v>
       </c>
@@ -1841,7 +1869,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>45924</v>
       </c>
@@ -1862,7 +1890,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>45929</v>
       </c>
@@ -1883,7 +1911,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>45937</v>
       </c>
@@ -1904,7 +1932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>45937</v>
       </c>
@@ -1925,7 +1953,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>45937</v>
       </c>
@@ -1946,7 +1974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>45937.40625</v>
       </c>
@@ -1967,7 +1995,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>45937.462500000001</v>
       </c>
@@ -1988,7 +2016,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>45937.465277777781</v>
       </c>
@@ -2009,7 +2037,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>45938.413194444445</v>
       </c>
@@ -2029,7 +2057,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>45939.417361111111</v>
       </c>
@@ -2049,7 +2077,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>45943.410416666666</v>
       </c>
@@ -2069,7 +2097,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>45943.411805555559</v>
       </c>
@@ -2089,7 +2117,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>45943.412499999999</v>
       </c>
@@ -2109,7 +2137,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>45943.413194444445</v>
       </c>
@@ -2129,7 +2157,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>45943.415277777778</v>
       </c>
@@ -2149,7 +2177,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>45943.417361111111</v>
       </c>
@@ -2169,7 +2197,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>45946.399305555555</v>
       </c>
@@ -2189,7 +2217,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>45957.457638888889</v>
       </c>
@@ -2209,7 +2237,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>45957.459722222222</v>
       </c>
@@ -2229,7 +2257,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>45957.460416666669</v>
       </c>
@@ -2249,7 +2277,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>45957.462500000001</v>
       </c>
@@ -2269,7 +2297,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>45957.463194444441</v>
       </c>
@@ -2289,7 +2317,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>45957.463888888888</v>
       </c>
@@ -2309,7 +2337,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -2329,7 +2357,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -2349,7 +2377,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -2369,7 +2397,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -2389,7 +2417,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>45957.47152777778</v>
       </c>
@@ -2409,7 +2437,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>45958.512499999997</v>
       </c>
@@ -2422,14 +2450,14 @@
       <c r="D87" s="6">
         <v>541.79</v>
       </c>
-      <c r="E87" s="6">
+      <c r="E87" s="9">
         <v>0.96050999999999997</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>45958.515277777777</v>
       </c>
@@ -2449,7 +2477,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>45958.517361111109</v>
       </c>
@@ -2469,7 +2497,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>45958.520138888889</v>
       </c>
@@ -2489,7 +2517,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -2509,7 +2537,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -2529,7 +2557,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>45958.529166666667</v>
       </c>
@@ -2549,7 +2577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>45965.642361111109</v>
       </c>
@@ -2569,7 +2597,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>45974.67291666667</v>
       </c>
@@ -2589,7 +2617,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46002.439583333333</v>
       </c>
@@ -2609,7 +2637,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46002.443749999999</v>
       </c>
@@ -2629,7 +2657,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46002.446527777778</v>
       </c>
@@ -2649,7 +2677,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>46008.648611111108</v>
       </c>
@@ -2669,7 +2697,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>46008.650694444441</v>
       </c>
@@ -2689,7 +2717,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>46020.463888888888</v>
       </c>
@@ -2709,7 +2737,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>46021.472916666666</v>
       </c>
@@ -2729,7 +2757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>46027.567361111112</v>
       </c>
@@ -2743,13 +2771,13 @@
         <v>0.44</v>
       </c>
       <c r="E103" s="6">
-        <v>39</v>
+        <v>39.246000000000002</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46027.568055555559</v>
       </c>
@@ -2769,7 +2797,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>46027.568749999999</v>
       </c>
@@ -2789,7 +2817,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>46029.449305555558</v>
       </c>
@@ -2809,7 +2837,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -2829,7 +2857,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -2849,7 +2877,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>46035.44027777778</v>
       </c>
@@ -2869,7 +2897,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>46035.441666666666</v>
       </c>
@@ -2889,7 +2917,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>46036.448611111111</v>
       </c>
@@ -2909,7 +2937,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>46042.441666666666</v>
       </c>
@@ -2929,7 +2957,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>46042.44027777778</v>
       </c>
@@ -2949,7 +2977,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>46042.45</v>
       </c>
@@ -2969,7 +2997,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -2990,7 +3018,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -3010,7 +3038,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>46044.49722222222</v>
       </c>
@@ -3030,7 +3058,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>46045.445833333331</v>
       </c>
@@ -3050,7 +3078,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>46045.493055555555</v>
       </c>
@@ -3070,7 +3098,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>46048.572222222225</v>
       </c>
@@ -3090,7 +3118,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>46049.448611111111</v>
       </c>
@@ -3110,7 +3138,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>46050.563888888886</v>
       </c>
@@ -3130,87 +3158,416 @@
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
+        <v>46059</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C123" s="6">
+        <v>649.04</v>
+      </c>
+      <c r="D123" s="6">
+        <v>59.58</v>
+      </c>
+      <c r="E123" s="6">
+        <v>10.89</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
         <v>46055.650694444441</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B124" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C123" s="6">
+      <c r="C124" s="6">
         <v>649.35</v>
       </c>
-      <c r="D123" s="6">
+      <c r="D124" s="6">
         <v>711.77</v>
       </c>
-      <c r="E123" s="6">
+      <c r="E124" s="6">
         <v>0.91229000000000005</v>
       </c>
-      <c r="F123" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
+      <c r="F124" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
         <v>46055.652083333334</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B125" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C124" s="6">
+      <c r="C125" s="6">
         <v>234.14</v>
       </c>
-      <c r="D124" s="6">
+      <c r="D125" s="6">
         <v>4.96</v>
       </c>
-      <c r="E124" s="6">
+      <c r="E125" s="6">
         <v>47.2</v>
       </c>
-      <c r="F124" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="1">
+      <c r="F125" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
         <v>46083.456250000003</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B126" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C125" s="6">
+      <c r="C126" s="6">
         <v>480.63</v>
       </c>
-      <c r="D125" s="6">
+      <c r="D126" s="6">
         <v>160.21</v>
       </c>
-      <c r="E125" s="6">
+      <c r="E126" s="6">
         <v>3</v>
       </c>
-      <c r="F125" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="1">
+      <c r="F126" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
         <v>46086</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B127" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C126" s="6">
+      <c r="C127" s="6">
         <v>175.04</v>
       </c>
-      <c r="D126" s="6">
+      <c r="D127" s="6">
         <v>98.34</v>
       </c>
-      <c r="E126" s="6">
+      <c r="E127" s="6">
         <v>1.7799471222290013</v>
       </c>
-      <c r="F126" s="2" t="s">
+      <c r="F127" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C128" s="6">
+        <v>499.99</v>
+      </c>
+      <c r="D128" s="6">
+        <v>685.2</v>
+      </c>
+      <c r="E128" s="6">
+        <v>0.72970000000000002</v>
+      </c>
+      <c r="F128" s="2" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F127" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="SPY"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE2B80C-EA19-4ACD-BFC2-2521030D6707}">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.875" style="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="7">
+        <v>73.045047841790193</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>73.049850000000006</v>
+      </c>
+      <c r="G2" s="8">
+        <f>E2-B2</f>
+        <v>4.8021582098130011E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="7">
+        <v>20.095474685434699</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>20.093769999999999</v>
+      </c>
+      <c r="G3" s="8">
+        <f t="shared" ref="G3:G15" si="0">E3-B3</f>
+        <v>-1.7046854346993712E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="7">
+        <v>13.89</v>
+      </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4">
+        <v>13.9215</v>
+      </c>
+      <c r="G4" s="8">
+        <f t="shared" si="0"/>
+        <v>3.1499999999999417E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="7">
+        <v>10.8173189029906</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5">
+        <v>10.81081</v>
+      </c>
+      <c r="G5" s="8">
+        <f t="shared" si="0"/>
+        <v>-6.5089029905998075E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="7">
+        <v>10.290471281296</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6">
+        <v>10.297129999999999</v>
+      </c>
+      <c r="G6" s="8">
+        <f t="shared" si="0"/>
+        <v>6.6587187039992557E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="7">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7">
+        <v>8.8120799999999999</v>
+      </c>
+      <c r="G7" s="8">
+        <f t="shared" si="0"/>
+        <v>2.2080000000000766E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="7">
+        <v>5.71</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8">
+        <v>5.7142799999999996</v>
+      </c>
+      <c r="G8" s="8">
+        <f t="shared" si="0"/>
+        <v>4.2799999999996174E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="7">
+        <v>3.6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9">
+        <v>3.60785</v>
+      </c>
+      <c r="G9" s="8">
+        <f t="shared" si="0"/>
+        <v>7.8499999999999126E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="7">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="G10" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="7">
+        <v>1.9977277643522</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11">
+        <v>2.0009399999999999</v>
+      </c>
+      <c r="G11" s="8">
+        <f t="shared" si="0"/>
+        <v>3.2122356477999325E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="7">
+        <v>1.7799542444927501</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12">
+        <v>1.7799400000000001</v>
+      </c>
+      <c r="G12" s="8">
+        <f t="shared" si="0"/>
+        <v>-1.4244492750004056E-5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="7">
+        <v>1.00000500138302</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>1.50752</v>
+      </c>
+      <c r="G13" s="8">
+        <f t="shared" si="0"/>
+        <v>0.50751499861698002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="7">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14">
+        <v>1.0013399999999999</v>
+      </c>
+      <c r="G14" s="8">
+        <f t="shared" si="0"/>
+        <v>1.3399999999998968E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.773338109298358</v>
+      </c>
+      <c r="D15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" si="0"/>
+        <v>0.226661890701642</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B15">
+    <sortCondition descending="1" ref="B2:B15"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -1,24 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johanrosa/Desktop/web_development/personal/finance_portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40693DA3-71AC-476D-BA65-BB3F15A94400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8AAEDD-FE80-1B4B-9F32-586F9D3D2E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
   <sheets>
     <sheet name="logs" sheetId="1" r:id="rId1"/>
-    <sheet name="current" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">current!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">logs!$A$1:$F$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">logs!$A$1:$F$128</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="59">
   <si>
     <t>date</t>
   </si>
@@ -218,24 +216,18 @@
   </si>
   <si>
     <t>VDE</t>
-  </si>
-  <si>
-    <t>ticker</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="174" formatCode="0.00000"/>
+    <numFmt numFmtId="168" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -248,13 +240,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -275,11 +260,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -299,16 +283,11 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -641,19 +620,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F128"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" style="6" customWidth="1"/>
     <col min="4" max="4" width="21.5" style="6" customWidth="1"/>
-    <col min="5" max="5" width="10.875" style="6"/>
-    <col min="6" max="6" width="10.875" style="2"/>
+    <col min="5" max="5" width="10.83203125" style="6"/>
+    <col min="6" max="6" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -673,7 +651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>45903.43472222222</v>
       </c>
@@ -694,7 +672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>45903.435416666667</v>
       </c>
@@ -715,7 +693,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>45903.436111111114</v>
       </c>
@@ -736,7 +714,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>45903.436805555553</v>
       </c>
@@ -757,7 +735,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>45903.438194444447</v>
       </c>
@@ -778,7 +756,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>45903.438888888886</v>
       </c>
@@ -799,7 +777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>45903.418749999997</v>
       </c>
@@ -820,7 +798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>45903.445138888892</v>
       </c>
@@ -841,7 +819,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>45903.445833333331</v>
       </c>
@@ -861,7 +839,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>45903.448611111111</v>
       </c>
@@ -882,7 +860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>45903.455555555556</v>
       </c>
@@ -903,7 +881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>45903.463888888888</v>
       </c>
@@ -916,7 +894,7 @@
       <c r="D13" s="6">
         <v>506.14</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="7">
         <f t="shared" si="0"/>
         <v>3.9495001383016558E-2</v>
       </c>
@@ -924,7 +902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>45903.46597222222</v>
       </c>
@@ -945,7 +923,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>45903.467361111114</v>
       </c>
@@ -966,7 +944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>45903.46875</v>
       </c>
@@ -987,7 +965,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>45903.470138888886</v>
       </c>
@@ -1008,7 +986,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>45903.474999999999</v>
       </c>
@@ -1029,7 +1007,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>45903.476388888892</v>
       </c>
@@ -1050,7 +1028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>45903.479861111111</v>
       </c>
@@ -1071,7 +1049,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>45903.480555555558</v>
       </c>
@@ -1092,7 +1070,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>45903.493750000001</v>
       </c>
@@ -1113,7 +1091,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -1134,7 +1112,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -1155,7 +1133,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>45903.495138888888</v>
       </c>
@@ -1176,7 +1154,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>45903.504861111112</v>
       </c>
@@ -1197,7 +1175,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>45904.404861111114</v>
       </c>
@@ -1218,7 +1196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>45904.406944444447</v>
       </c>
@@ -1239,7 +1217,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>45904.407638888886</v>
       </c>
@@ -1260,7 +1238,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>45904.412499999999</v>
       </c>
@@ -1281,7 +1259,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>45904.414583333331</v>
       </c>
@@ -1302,7 +1280,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>45904.418749999997</v>
       </c>
@@ -1323,7 +1301,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>45905.408333333333</v>
       </c>
@@ -1344,7 +1322,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>45908.665277777778</v>
       </c>
@@ -1365,7 +1343,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>45909.415277777778</v>
       </c>
@@ -1386,7 +1364,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>45909.418055555558</v>
       </c>
@@ -1407,7 +1385,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>45909.427083333336</v>
       </c>
@@ -1428,7 +1406,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>45909.427777777775</v>
       </c>
@@ -1449,7 +1427,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>45909.431250000001</v>
       </c>
@@ -1470,7 +1448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>45909.43472222222</v>
       </c>
@@ -1491,7 +1469,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>45909.439583333333</v>
       </c>
@@ -1512,7 +1490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -1533,7 +1511,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -1554,7 +1532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>45910</v>
       </c>
@@ -1575,7 +1553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>45910</v>
       </c>
@@ -1596,7 +1574,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>45911</v>
       </c>
@@ -1617,7 +1595,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>45911</v>
       </c>
@@ -1638,7 +1616,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>45912</v>
       </c>
@@ -1659,7 +1637,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>45912</v>
       </c>
@@ -1680,7 +1658,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>45912</v>
       </c>
@@ -1701,7 +1679,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>45912</v>
       </c>
@@ -1722,7 +1700,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>45923</v>
       </c>
@@ -1743,7 +1721,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>45923</v>
       </c>
@@ -1764,7 +1742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>45923</v>
       </c>
@@ -1785,7 +1763,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>45923</v>
       </c>
@@ -1806,7 +1784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>45923</v>
       </c>
@@ -1827,7 +1805,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>45923</v>
       </c>
@@ -1848,7 +1826,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>45924</v>
       </c>
@@ -1869,7 +1847,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>45924</v>
       </c>
@@ -1890,7 +1868,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>45929</v>
       </c>
@@ -1911,7 +1889,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>45937</v>
       </c>
@@ -1932,7 +1910,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>45937</v>
       </c>
@@ -1953,7 +1931,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>45937</v>
       </c>
@@ -1974,7 +1952,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>45937.40625</v>
       </c>
@@ -1995,7 +1973,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>45937.462500000001</v>
       </c>
@@ -2016,7 +1994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>45937.465277777781</v>
       </c>
@@ -2037,7 +2015,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>45938.413194444445</v>
       </c>
@@ -2057,7 +2035,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>45939.417361111111</v>
       </c>
@@ -2077,7 +2055,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>45943.410416666666</v>
       </c>
@@ -2097,7 +2075,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>45943.411805555559</v>
       </c>
@@ -2117,7 +2095,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>45943.412499999999</v>
       </c>
@@ -2137,7 +2115,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>45943.413194444445</v>
       </c>
@@ -2157,7 +2135,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>45943.415277777778</v>
       </c>
@@ -2177,7 +2155,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>45943.417361111111</v>
       </c>
@@ -2197,7 +2175,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>45946.399305555555</v>
       </c>
@@ -2217,7 +2195,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>45957.457638888889</v>
       </c>
@@ -2237,7 +2215,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>45957.459722222222</v>
       </c>
@@ -2257,7 +2235,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>45957.460416666669</v>
       </c>
@@ -2277,7 +2255,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>45957.462500000001</v>
       </c>
@@ -2297,7 +2275,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>45957.463194444441</v>
       </c>
@@ -2317,7 +2295,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>45957.463888888888</v>
       </c>
@@ -2337,7 +2315,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -2357,7 +2335,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -2377,7 +2355,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -2397,7 +2375,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -2417,7 +2395,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>45957.47152777778</v>
       </c>
@@ -2437,7 +2415,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>45958.512499999997</v>
       </c>
@@ -2450,14 +2428,14 @@
       <c r="D87" s="6">
         <v>541.79</v>
       </c>
-      <c r="E87" s="9">
+      <c r="E87" s="7">
         <v>0.96050999999999997</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>45958.515277777777</v>
       </c>
@@ -2477,7 +2455,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>45958.517361111109</v>
       </c>
@@ -2497,7 +2475,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>45958.520138888889</v>
       </c>
@@ -2517,7 +2495,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -2537,7 +2515,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -2557,7 +2535,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>45958.529166666667</v>
       </c>
@@ -2577,7 +2555,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>45965.642361111109</v>
       </c>
@@ -2597,7 +2575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>45974.67291666667</v>
       </c>
@@ -2617,7 +2595,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>46002.439583333333</v>
       </c>
@@ -2637,7 +2615,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>46002.443749999999</v>
       </c>
@@ -2657,7 +2635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>46002.446527777778</v>
       </c>
@@ -2677,7 +2655,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>46008.648611111108</v>
       </c>
@@ -2697,7 +2675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>46008.650694444441</v>
       </c>
@@ -2717,7 +2695,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>46020.463888888888</v>
       </c>
@@ -2737,7 +2715,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>46021.472916666666</v>
       </c>
@@ -2757,7 +2735,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>46027.567361111112</v>
       </c>
@@ -2777,7 +2755,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>46027.568055555559</v>
       </c>
@@ -2797,7 +2775,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>46027.568749999999</v>
       </c>
@@ -2817,7 +2795,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>46029.449305555558</v>
       </c>
@@ -2837,7 +2815,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -2857,7 +2835,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -2877,7 +2855,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>46035.44027777778</v>
       </c>
@@ -2897,7 +2875,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>46035.441666666666</v>
       </c>
@@ -2917,7 +2895,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>46036.448611111111</v>
       </c>
@@ -2937,7 +2915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>46042.441666666666</v>
       </c>
@@ -2957,7 +2935,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>46042.44027777778</v>
       </c>
@@ -2977,7 +2955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>46042.45</v>
       </c>
@@ -2997,7 +2975,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -3018,7 +2996,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -3038,7 +3016,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>46044.49722222222</v>
       </c>
@@ -3058,7 +3036,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>46045.445833333331</v>
       </c>
@@ -3078,7 +3056,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>46045.493055555555</v>
       </c>
@@ -3098,7 +3076,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>46048.572222222225</v>
       </c>
@@ -3118,7 +3096,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>46049.448611111111</v>
       </c>
@@ -3138,7 +3116,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>46050.563888888886</v>
       </c>
@@ -3158,7 +3136,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>46059</v>
       </c>
@@ -3178,7 +3156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>46055.650694444441</v>
       </c>
@@ -3198,7 +3176,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>46055.652083333334</v>
       </c>
@@ -3218,7 +3196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>46083.456250000003</v>
       </c>
@@ -3238,7 +3216,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>46086</v>
       </c>
@@ -3258,7 +3236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>46002</v>
       </c>
@@ -3279,295 +3257,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F127" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="SPY"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE2B80C-EA19-4ACD-BFC2-2521030D6707}">
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="11.875" style="7" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="7">
-        <v>73.045047841790193</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2">
-        <v>73.049850000000006</v>
-      </c>
-      <c r="G2" s="8">
-        <f>E2-B2</f>
-        <v>4.8021582098130011E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="7">
-        <v>20.095474685434699</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>20.093769999999999</v>
-      </c>
-      <c r="G3" s="8">
-        <f t="shared" ref="G3:G15" si="0">E3-B3</f>
-        <v>-1.7046854346993712E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="7">
-        <v>13.89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4">
-        <v>13.9215</v>
-      </c>
-      <c r="G4" s="8">
-        <f t="shared" si="0"/>
-        <v>3.1499999999999417E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="7">
-        <v>10.8173189029906</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5">
-        <v>10.81081</v>
-      </c>
-      <c r="G5" s="8">
-        <f t="shared" si="0"/>
-        <v>-6.5089029905998075E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="7">
-        <v>10.290471281296</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6">
-        <v>10.297129999999999</v>
-      </c>
-      <c r="G6" s="8">
-        <f t="shared" si="0"/>
-        <v>6.6587187039992557E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="7">
-        <v>8.7899999999999991</v>
-      </c>
-      <c r="D7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7">
-        <v>8.8120799999999999</v>
-      </c>
-      <c r="G7" s="8">
-        <f t="shared" si="0"/>
-        <v>2.2080000000000766E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="7">
-        <v>5.71</v>
-      </c>
-      <c r="D8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8">
-        <v>5.7142799999999996</v>
-      </c>
-      <c r="G8" s="8">
-        <f t="shared" si="0"/>
-        <v>4.2799999999996174E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="7">
-        <v>3.6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9">
-        <v>3.60785</v>
-      </c>
-      <c r="G9" s="8">
-        <f t="shared" si="0"/>
-        <v>7.8499999999999126E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="7">
-        <v>3</v>
-      </c>
-      <c r="D10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="G10" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="7">
-        <v>1.9977277643522</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11">
-        <v>2.0009399999999999</v>
-      </c>
-      <c r="G11" s="8">
-        <f t="shared" si="0"/>
-        <v>3.2122356477999325E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="7">
-        <v>1.7799542444927501</v>
-      </c>
-      <c r="D12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12">
-        <v>1.7799400000000001</v>
-      </c>
-      <c r="G12" s="8">
-        <f t="shared" si="0"/>
-        <v>-1.4244492750004056E-5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="7">
-        <v>1.00000500138302</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13">
-        <v>1.50752</v>
-      </c>
-      <c r="G13" s="8">
-        <f t="shared" si="0"/>
-        <v>0.50751499861698002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="7">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14">
-        <v>1.0013399999999999</v>
-      </c>
-      <c r="G14" s="8">
-        <f t="shared" si="0"/>
-        <v>1.3399999999998968E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0.773338109298358</v>
-      </c>
-      <c r="D15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="8">
-        <f t="shared" si="0"/>
-        <v>0.226661890701642</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B15">
-    <sortCondition descending="1" ref="B2:B15"/>
-  </sortState>
+  <autoFilter ref="A1:F128" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johanrosa/Desktop/web_development/personal/finance_portfolio/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8AAEDD-FE80-1B4B-9F32-586F9D3D2E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B624C6E8-36BD-4F8F-93E3-91426187A02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
   <sheets>
     <sheet name="logs" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="59">
   <si>
     <t>date</t>
   </si>
@@ -225,7 +225,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -283,7 +283,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -620,18 +620,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
-  <dimension ref="A1:F128"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F135"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="6" customWidth="1"/>
     <col min="4" max="4" width="21.5" style="6" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="6"/>
-    <col min="6" max="6" width="10.83203125" style="2"/>
+    <col min="5" max="5" width="10.875" style="6"/>
+    <col min="6" max="6" width="10.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45903.43472222222</v>
       </c>
@@ -672,7 +672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45903.435416666667</v>
       </c>
@@ -693,7 +693,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45903.436111111114</v>
       </c>
@@ -714,7 +714,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45903.436805555553</v>
       </c>
@@ -735,7 +735,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45903.438194444447</v>
       </c>
@@ -756,7 +756,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45903.438888888886</v>
       </c>
@@ -777,7 +777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45903.418749999997</v>
       </c>
@@ -798,7 +798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45903.445138888892</v>
       </c>
@@ -819,7 +819,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45903.445833333331</v>
       </c>
@@ -839,7 +839,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45903.448611111111</v>
       </c>
@@ -860,7 +860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45903.455555555556</v>
       </c>
@@ -881,7 +881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45903.463888888888</v>
       </c>
@@ -902,7 +902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45903.46597222222</v>
       </c>
@@ -923,7 +923,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45903.467361111114</v>
       </c>
@@ -944,7 +944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45903.46875</v>
       </c>
@@ -965,7 +965,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>45903.470138888886</v>
       </c>
@@ -986,7 +986,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45903.474999999999</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>45903.476388888892</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>45903.479861111111</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>45903.480555555558</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>45903.493750000001</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>45903.495138888888</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>45903.504861111112</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>45904.404861111114</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>45904.406944444447</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>45904.407638888886</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>45904.412499999999</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>45904.414583333331</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>45904.418749999997</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>45905.408333333333</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>45908.665277777778</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>45909.415277777778</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>45909.418055555558</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>45909.427083333336</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>45909.427777777775</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>45909.431250000001</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>45909.43472222222</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>45909.439583333333</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>45910</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>45910</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45911</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45911</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>45912</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>45912</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>45912</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>45912</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>45923</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>45923</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>45923</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>45923</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>45923</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>45923</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>45924</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>45924</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>45929</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>45937</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>45937</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>45937</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>45937.40625</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>45937.462500000001</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>45937.465277777781</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>45938.413194444445</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>45939.417361111111</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>45943.410416666666</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>45943.411805555559</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>45943.412499999999</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>45943.413194444445</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>45943.415277777778</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>45943.417361111111</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>45946.399305555555</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>45957.457638888889</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>45957.459722222222</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>45957.460416666669</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>45957.462500000001</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>45957.463194444441</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>45957.463888888888</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>45957.47152777778</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>45958.512499999997</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>45958.515277777777</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>45958.517361111109</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>45958.520138888889</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>45958.529166666667</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>45965.642361111109</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>45974.67291666667</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46002.439583333333</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46002.443749999999</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46002.446527777778</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>46008.648611111108</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>46008.650694444441</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>46020.463888888888</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>46021.472916666666</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>46027.567361111112</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46027.568055555559</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>46027.568749999999</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>46029.449305555558</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>46035.44027777778</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>46035.441666666666</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>46036.448611111111</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>46042.441666666666</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>46042.44027777778</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>46042.45</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>46044.49722222222</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>46045.445833333331</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>46045.493055555555</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>46048.572222222225</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>46049.448611111111</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>46050.563888888886</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>46059</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>46055.650694444441</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>46055.652083333334</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>46083.456250000003</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>46086</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>46002</v>
       </c>
@@ -3254,6 +3254,146 @@
       </c>
       <c r="F128" s="2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C129" s="6">
+        <v>599.1</v>
+      </c>
+      <c r="D129" s="6">
+        <v>299.41000000000003</v>
+      </c>
+      <c r="E129" s="6">
+        <v>2.0009399999999999</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C130" s="6">
+        <v>467.44</v>
+      </c>
+      <c r="D130" s="6">
+        <v>45.39</v>
+      </c>
+      <c r="E130" s="6">
+        <v>10.297129999999999</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" s="6">
+        <v>333.26</v>
+      </c>
+      <c r="D131" s="6">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="E131" s="6">
+        <v>20.037700000000001</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C132" s="6">
+        <v>525.9</v>
+      </c>
+      <c r="D132" s="6">
+        <v>59.68</v>
+      </c>
+      <c r="E132" s="6">
+        <v>8.8120799999999999</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C133" s="6">
+        <v>462.97</v>
+      </c>
+      <c r="D133" s="6">
+        <v>81.02</v>
+      </c>
+      <c r="E133" s="6">
+        <v>5.7142799999999996</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C134" s="6">
+        <v>291.45999999999998</v>
+      </c>
+      <c r="D134" s="6">
+        <v>80.78</v>
+      </c>
+      <c r="E134" s="6">
+        <v>3.60785</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C135" s="6">
+        <v>222.54</v>
+      </c>
+      <c r="D135" s="6">
+        <v>20.58</v>
+      </c>
+      <c r="E135" s="6">
+        <v>10.81081</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B624C6E8-36BD-4F8F-93E3-91426187A02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4836B82-EE96-45B7-8CD4-796BBD814446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="61">
   <si>
     <t>date</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>VDE</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>YPF</t>
   </si>
 </sst>
 </file>
@@ -620,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
@@ -3396,6 +3402,86 @@
         <v>38</v>
       </c>
     </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C136" s="6">
+        <v>790.6</v>
+      </c>
+      <c r="D136" s="6">
+        <v>56.79</v>
+      </c>
+      <c r="E136" s="6">
+        <v>13.9215</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C137" s="6">
+        <v>788</v>
+      </c>
+      <c r="D137" s="6">
+        <v>116.55</v>
+      </c>
+      <c r="E137" s="6">
+        <v>6.7617500000000001</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C138" s="6">
+        <v>500</v>
+      </c>
+      <c r="D138" s="6">
+        <v>63.36</v>
+      </c>
+      <c r="E138" s="6">
+        <v>7.89</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C139" s="6">
+        <v>500</v>
+      </c>
+      <c r="D139" s="6">
+        <v>37.89</v>
+      </c>
+      <c r="E139" s="6">
+        <v>13.19</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F128" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4836B82-EE96-45B7-8CD4-796BBD814446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D9E977-EBCA-48E9-B220-22A29387DA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="61">
   <si>
     <t>date</t>
   </si>
@@ -626,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
@@ -3482,6 +3482,26 @@
         <v>7</v>
       </c>
     </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C140" s="6">
+        <v>1113.31</v>
+      </c>
+      <c r="D140" s="6">
+        <v>677.47</v>
+      </c>
+      <c r="E140" s="6">
+        <v>1.6433199999999999</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F128" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D9E977-EBCA-48E9-B220-22A29387DA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358B0B51-7A3D-4995-9222-D0CE0BE8753B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="62">
   <si>
     <t>date</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>YPF</t>
+  </si>
+  <si>
+    <t>RING</t>
   </si>
 </sst>
 </file>
@@ -626,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
@@ -3502,6 +3505,106 @@
         <v>7</v>
       </c>
     </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C141" s="6">
+        <v>476.34</v>
+      </c>
+      <c r="D141" s="6">
+        <v>158.78</v>
+      </c>
+      <c r="E141" s="6">
+        <v>3</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C142" s="6">
+        <v>489.57</v>
+      </c>
+      <c r="D142" s="6">
+        <v>37.1</v>
+      </c>
+      <c r="E142" s="6">
+        <v>13.19</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C143" s="6">
+        <v>590</v>
+      </c>
+      <c r="D143" s="6">
+        <v>409.79</v>
+      </c>
+      <c r="E143" s="6">
+        <v>1.43988</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C144" s="6">
+        <v>450.15</v>
+      </c>
+      <c r="D144" s="6">
+        <v>90.02</v>
+      </c>
+      <c r="E144" s="6">
+        <v>5</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C145" s="6">
+        <v>466.86</v>
+      </c>
+      <c r="D145" s="6">
+        <v>59.16</v>
+      </c>
+      <c r="E145" s="6">
+        <v>7.89079</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F128" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johanrosa/Desktop/web_development/personal/finance_portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358B0B51-7A3D-4995-9222-D0CE0BE8753B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228B155B-5321-DC43-AA95-FE664358C160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
   <sheets>
     <sheet name="logs" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="62">
   <si>
     <t>date</t>
   </si>
@@ -629,18 +629,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
-  <dimension ref="A1:F145"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F146"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" style="6" customWidth="1"/>
     <col min="4" max="4" width="21.5" style="6" customWidth="1"/>
-    <col min="5" max="5" width="10.875" style="6"/>
-    <col min="6" max="6" width="10.875" style="2"/>
+    <col min="5" max="5" width="10.83203125" style="6"/>
+    <col min="6" max="6" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -660,7 +660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>45903.43472222222</v>
       </c>
@@ -681,7 +681,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>45903.435416666667</v>
       </c>
@@ -702,7 +702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>45903.436111111114</v>
       </c>
@@ -723,7 +723,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>45903.436805555553</v>
       </c>
@@ -744,7 +744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>45903.438194444447</v>
       </c>
@@ -765,7 +765,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>45903.438888888886</v>
       </c>
@@ -786,7 +786,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>45903.418749999997</v>
       </c>
@@ -807,7 +807,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>45903.445138888892</v>
       </c>
@@ -828,7 +828,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>45903.445833333331</v>
       </c>
@@ -848,7 +848,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>45903.448611111111</v>
       </c>
@@ -869,7 +869,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>45903.455555555556</v>
       </c>
@@ -890,7 +890,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>45903.463888888888</v>
       </c>
@@ -911,7 +911,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>45903.46597222222</v>
       </c>
@@ -932,7 +932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>45903.467361111114</v>
       </c>
@@ -953,7 +953,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>45903.46875</v>
       </c>
@@ -974,7 +974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>45903.470138888886</v>
       </c>
@@ -995,7 +995,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>45903.474999999999</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>45903.476388888892</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>45903.479861111111</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>45903.480555555558</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>45903.493750000001</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>45903.495138888888</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>45903.504861111112</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>45904.404861111114</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>45904.406944444447</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>45904.407638888886</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>45904.412499999999</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>45904.414583333331</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>45904.418749999997</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>45905.408333333333</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>45908.665277777778</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>45909.415277777778</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>45909.418055555558</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>45909.427083333336</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>45909.427777777775</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>45909.431250000001</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>45909.43472222222</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>45909.439583333333</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>45910</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>45910</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>45911</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>45911</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>45912</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>45912</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>45912</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>45912</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>45923</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>45923</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>45923</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>45923</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>45923</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>45923</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>45924</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>45924</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>45929</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>45937</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>45937</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>45937</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>45937.40625</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>45937.462500000001</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>45937.465277777781</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>45938.413194444445</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>45939.417361111111</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>45943.410416666666</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>45943.411805555559</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>45943.412499999999</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>45943.413194444445</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>45943.415277777778</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>45943.417361111111</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>45946.399305555555</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>45957.457638888889</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>45957.459722222222</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>45957.460416666669</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>45957.462500000001</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>45957.463194444441</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>45957.463888888888</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>45957.47152777778</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>45958.512499999997</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>45958.515277777777</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>45958.517361111109</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>45958.520138888889</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>45958.529166666667</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>45965.642361111109</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>45974.67291666667</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>46002.439583333333</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>46002.443749999999</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>46002.446527777778</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>46008.648611111108</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>46008.650694444441</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>46020.463888888888</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>46021.472916666666</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>46027.567361111112</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>46027.568055555559</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>46027.568749999999</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>46029.449305555558</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>46035.44027777778</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>46035.441666666666</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>46036.448611111111</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>46042.441666666666</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>46042.44027777778</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>46042.45</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>46044.49722222222</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>46045.445833333331</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>46045.493055555555</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>46048.572222222225</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>46049.448611111111</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>46050.563888888886</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>46059</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>46055.650694444441</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>46055.652083333334</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>46083.456250000003</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>46086</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>46002</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>46087</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>46087</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>46087</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>46087</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>46087</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>46087</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>46087</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>46090</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>46090</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>46090</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>46090</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>46090</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>46091</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>46091</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>46091</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>46091</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>46091</v>
       </c>
@@ -3603,6 +3603,26 @@
       </c>
       <c r="F145" s="2" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" s="6">
+        <v>1000</v>
+      </c>
+      <c r="D146" s="6">
+        <v>40.119900000000001</v>
+      </c>
+      <c r="E146" s="7">
+        <v>24.925280000000001</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johanrosa/Desktop/web_development/personal/finance_portfolio/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228B155B-5321-DC43-AA95-FE664358C160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC93EB0-C50D-495B-BE81-6E7968941840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
   <sheets>
     <sheet name="logs" sheetId="1" r:id="rId1"/>
@@ -630,17 +630,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
   <dimension ref="A1:F146"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="6" customWidth="1"/>
     <col min="4" max="4" width="21.5" style="6" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="6"/>
-    <col min="6" max="6" width="10.83203125" style="2"/>
+    <col min="5" max="5" width="10.875" style="6"/>
+    <col min="6" max="6" width="10.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -660,7 +660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45903.43472222222</v>
       </c>
@@ -681,7 +681,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45903.435416666667</v>
       </c>
@@ -702,7 +702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45903.436111111114</v>
       </c>
@@ -723,7 +723,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45903.436805555553</v>
       </c>
@@ -744,7 +744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45903.438194444447</v>
       </c>
@@ -765,7 +765,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45903.438888888886</v>
       </c>
@@ -786,7 +786,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45903.418749999997</v>
       </c>
@@ -807,7 +807,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45903.445138888892</v>
       </c>
@@ -828,7 +828,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45903.445833333331</v>
       </c>
@@ -848,7 +848,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45903.448611111111</v>
       </c>
@@ -869,7 +869,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45903.455555555556</v>
       </c>
@@ -890,7 +890,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45903.463888888888</v>
       </c>
@@ -911,7 +911,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45903.46597222222</v>
       </c>
@@ -932,7 +932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45903.467361111114</v>
       </c>
@@ -953,7 +953,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45903.46875</v>
       </c>
@@ -974,7 +974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>45903.470138888886</v>
       </c>
@@ -995,7 +995,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45903.474999999999</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>45903.476388888892</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>45903.479861111111</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>45903.480555555558</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>45903.493750000001</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>45903.495138888888</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>45903.504861111112</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>45904.404861111114</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>45904.406944444447</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>45904.407638888886</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>45904.412499999999</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>45904.414583333331</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>45904.418749999997</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>45905.408333333333</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>45908.665277777778</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>45909.415277777778</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>45909.418055555558</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>45909.427083333336</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>45909.427777777775</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>45909.431250000001</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>45909.43472222222</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>45909.439583333333</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>45910</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>45910</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45911</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45911</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>45912</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>45912</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>45912</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>45912</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>45923</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>45923</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>45923</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>45923</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>45923</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>45923</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>45924</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>45924</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>45929</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>45937</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>45937</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>45937</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>45937.40625</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>45937.462500000001</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>45937.465277777781</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>45938.413194444445</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>45939.417361111111</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>45943.410416666666</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>45943.411805555559</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>45943.412499999999</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>45943.413194444445</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>45943.415277777778</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>45943.417361111111</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>45946.399305555555</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>45957.457638888889</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>45957.459722222222</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>45957.460416666669</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>45957.462500000001</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>45957.463194444441</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>45957.463888888888</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>45957.47152777778</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>45958.512499999997</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>45958.515277777777</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>45958.517361111109</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>45958.520138888889</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>45958.529166666667</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>45965.642361111109</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>45974.67291666667</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46002.439583333333</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46002.443749999999</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46002.446527777778</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>46008.648611111108</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>46008.650694444441</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>46020.463888888888</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>46021.472916666666</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>46027.567361111112</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46027.568055555559</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>46027.568749999999</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>46029.449305555558</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>46035.44027777778</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>46035.441666666666</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>46036.448611111111</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>46042.441666666666</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>46042.44027777778</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>46042.45</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>46044.49722222222</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>46045.445833333331</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>46045.493055555555</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>46048.572222222225</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>46049.448611111111</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>46050.563888888886</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>46059</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>46055.650694444441</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>46055.652083333334</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>46083.456250000003</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>46086</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>46002</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>46087</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>46087</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>46087</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>46087</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>46087</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>46087</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>46087</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>46090</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>46090</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>46090</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>46090</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>46090</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>46091</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>46091</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>46091</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>46091</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>46091</v>
       </c>
@@ -3605,7 +3605,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>46092</v>
       </c>

--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC93EB0-C50D-495B-BE81-6E7968941840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AC8212-F905-4291-B03B-D12169F7BD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="62">
   <si>
     <t>date</t>
   </si>
@@ -629,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
@@ -3625,6 +3625,47 @@
         <v>7</v>
       </c>
     </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C147" s="6">
+        <f>D147*E147</f>
+        <v>357.59999999999997</v>
+      </c>
+      <c r="D147" s="6">
+        <v>71.52</v>
+      </c>
+      <c r="E147" s="6">
+        <v>5</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C148" s="6">
+        <v>534.99</v>
+      </c>
+      <c r="D148" s="6">
+        <v>74.150000000000006</v>
+      </c>
+      <c r="E148" s="6">
+        <v>7.2149599999999996</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F128" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AC8212-F905-4291-B03B-D12169F7BD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECF0BE5-D668-45AD-AF70-049381FD0252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="62">
   <si>
     <t>date</t>
   </si>
@@ -629,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
@@ -3666,6 +3666,86 @@
         <v>7</v>
       </c>
     </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C149" s="6">
+        <v>1054.31</v>
+      </c>
+      <c r="D149" s="6">
+        <v>123.39</v>
+      </c>
+      <c r="E149" s="6">
+        <v>8.5441699999999994</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C150" s="6">
+        <v>515.58000000000004</v>
+      </c>
+      <c r="D150" s="6">
+        <v>71.459999999999994</v>
+      </c>
+      <c r="E150" s="6">
+        <v>7.2149599999999996</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C151" s="6">
+        <v>500</v>
+      </c>
+      <c r="D151" s="6">
+        <v>83.33</v>
+      </c>
+      <c r="E151" s="6">
+        <v>6.0002399999999998</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C152" s="6">
+        <v>715.9</v>
+      </c>
+      <c r="D152" s="6">
+        <v>371.51</v>
+      </c>
+      <c r="E152" s="6">
+        <v>1.927</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F128" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECF0BE5-D668-45AD-AF70-049381FD0252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0017A1D-3F4C-494D-AF23-18D2C93F7C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="63">
   <si>
     <t>date</t>
   </si>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>RING</t>
+  </si>
+  <si>
+    <t>HOOD</t>
   </si>
 </sst>
 </file>
@@ -629,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
@@ -3746,6 +3749,46 @@
         <v>7</v>
       </c>
     </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C153" s="6">
+        <v>638.77</v>
+      </c>
+      <c r="D153" s="6">
+        <v>86.03</v>
+      </c>
+      <c r="E153" s="6">
+        <v>7.42</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C154" s="6">
+        <v>525.80999999999995</v>
+      </c>
+      <c r="D154" s="6">
+        <v>175.27</v>
+      </c>
+      <c r="E154" s="6">
+        <v>3</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F128" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0017A1D-3F4C-494D-AF23-18D2C93F7C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33DFDF0-01BD-4090-8E9D-C1A4A4D25C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
+    <workbookView xWindow="2835" yWindow="1440" windowWidth="21585" windowHeight="11295" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
   <sheets>
     <sheet name="logs" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">logs!$A$1:$F$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">logs!$A$1:$F$155</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="63">
   <si>
     <t>date</t>
   </si>
@@ -234,10 +234,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="167" formatCode="0.000000000000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -275,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -296,6 +297,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -632,14 +636,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
-  <dimension ref="A1:F154"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.5" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.625" style="6" customWidth="1"/>
     <col min="4" max="4" width="21.5" style="6" customWidth="1"/>
-    <col min="5" max="5" width="10.875" style="6"/>
+    <col min="5" max="5" width="15.5" style="6" customWidth="1"/>
     <col min="6" max="6" width="10.875" style="2"/>
   </cols>
   <sheetData>
@@ -665,20 +669,20 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>45903.43472222222</v>
+        <v>45903.418749999997</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C2" s="6">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" s="6">
-        <v>63.42</v>
+        <v>9.14</v>
       </c>
       <c r="E2" s="6">
-        <f>C2/D2</f>
-        <v>3.1535793125197098</v>
+        <f t="shared" ref="E2:E9" si="0">C2/D2</f>
+        <v>5.4704595185995624</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>7</v>
@@ -686,20 +690,20 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>45903.435416666667</v>
+        <v>45903.43472222222</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6">
         <v>200</v>
       </c>
       <c r="D3" s="6">
-        <v>33.61</v>
+        <v>63.42</v>
       </c>
       <c r="E3" s="6">
-        <f t="shared" ref="E3:E66" si="0">C3/D3</f>
-        <v>5.9506099375185961</v>
+        <f t="shared" si="0"/>
+        <v>3.1535793125197098</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
@@ -707,20 +711,20 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>45903.436111111114</v>
+        <v>45903.435416666667</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6">
         <v>200</v>
       </c>
       <c r="D4" s="6">
-        <v>317.19</v>
+        <v>33.61</v>
       </c>
       <c r="E4" s="6">
         <f t="shared" si="0"/>
-        <v>0.6305369021721996</v>
+        <v>5.9506099375185961</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>7</v>
@@ -728,20 +732,20 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>45903.436805555553</v>
+        <v>45903.436111111114</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="6">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="D5" s="6">
-        <v>328.13</v>
+        <v>317.19</v>
       </c>
       <c r="E5" s="6">
         <f t="shared" si="0"/>
-        <v>0.76189315210434894</v>
+        <v>0.6305369021721996</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>7</v>
@@ -749,20 +753,20 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>45903.438194444447</v>
+        <v>45903.436805555553</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="6">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D6" s="6">
-        <v>131.86000000000001</v>
+        <v>328.13</v>
       </c>
       <c r="E6" s="6">
         <f t="shared" si="0"/>
-        <v>0.37919005005308659</v>
+        <v>0.76189315210434894</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>7</v>
@@ -770,20 +774,20 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>45903.438888888886</v>
+        <v>45903.438194444447</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="6">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D7" s="6">
-        <v>643.12</v>
+        <v>131.86000000000001</v>
       </c>
       <c r="E7" s="6">
         <f t="shared" si="0"/>
-        <v>0.31098395322801342</v>
+        <v>0.37919005005308659</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>7</v>
@@ -791,20 +795,20 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>45903.418749999997</v>
+        <v>45903.438888888886</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="6">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D8" s="6">
-        <v>9.14</v>
+        <v>643.12</v>
       </c>
       <c r="E8" s="6">
         <f t="shared" si="0"/>
-        <v>5.4704595185995624</v>
+        <v>0.31098395322801342</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>7</v>
@@ -865,7 +869,7 @@
         <v>5.26</v>
       </c>
       <c r="E11" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E11:E42" si="1">C11/D11</f>
         <v>4.752851711026616</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -886,7 +890,7 @@
         <v>339.97</v>
       </c>
       <c r="E12" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.8799305821101849E-2</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -907,7 +911,7 @@
         <v>506.14</v>
       </c>
       <c r="E13" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.9495001383016558E-2</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -928,7 +932,7 @@
         <v>737.72</v>
       </c>
       <c r="E14" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.7083446293986877E-2</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -948,8 +952,8 @@
       <c r="D15" s="6">
         <v>236.43</v>
       </c>
-      <c r="E15" s="6">
-        <f t="shared" si="0"/>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
         <v>8.4549338070464816E-2</v>
       </c>
       <c r="F15" s="2" t="s">
@@ -970,7 +974,7 @@
         <v>230.24</v>
       </c>
       <c r="E16" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.21716469770674079</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -991,7 +995,7 @@
         <v>225.92</v>
       </c>
       <c r="E17" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.13279036827195467</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -1012,7 +1016,7 @@
         <v>61.94</v>
       </c>
       <c r="E18" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.48433968356474011</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -1033,7 +1037,7 @@
         <v>93.52</v>
       </c>
       <c r="E19" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0692899914456802</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -1054,7 +1058,7 @@
         <v>1218.2</v>
       </c>
       <c r="E20" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.1035954687243477E-2</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -1075,7 +1079,7 @@
         <v>111.61</v>
       </c>
       <c r="E21" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.9597706298718757E-2</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -1096,7 +1100,7 @@
         <v>74.92</v>
       </c>
       <c r="E22" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.40042712226374799</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -1117,7 +1121,7 @@
         <v>17.5</v>
       </c>
       <c r="E23" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.4285714285714286</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -1138,7 +1142,7 @@
         <v>37.47</v>
       </c>
       <c r="E24" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3344008540165466</v>
       </c>
       <c r="F24" s="2" t="s">
@@ -1159,7 +1163,7 @@
         <v>13</v>
       </c>
       <c r="E25" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.5376923076923075</v>
       </c>
       <c r="F25" s="2" t="s">
@@ -1180,7 +1184,7 @@
         <v>158.88999999999999</v>
       </c>
       <c r="E26" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.12581030901881804</v>
       </c>
       <c r="F26" s="2" t="s">
@@ -1201,7 +1205,7 @@
         <v>49.57</v>
       </c>
       <c r="E27" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0086746015735324</v>
       </c>
       <c r="F27" s="2" t="s">
@@ -1222,7 +1226,7 @@
         <v>8.94</v>
       </c>
       <c r="E28" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.3557046979865772</v>
       </c>
       <c r="F28" s="2" t="s">
@@ -1243,7 +1247,7 @@
         <v>27.16</v>
       </c>
       <c r="E29" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.92047128129602351</v>
       </c>
       <c r="F29" s="2" t="s">
@@ -1264,7 +1268,7 @@
         <v>74.34</v>
       </c>
       <c r="E30" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3451708366962603</v>
       </c>
       <c r="F30" s="2" t="s">
@@ -1285,7 +1289,7 @@
         <v>185.21</v>
       </c>
       <c r="E31" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.16197829490848226</v>
       </c>
       <c r="F31" s="2" t="s">
@@ -1306,7 +1310,7 @@
         <v>647.66</v>
       </c>
       <c r="E32" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.15440200104993362</v>
       </c>
       <c r="F32" s="2" t="s">
@@ -1327,7 +1331,7 @@
         <v>6.65</v>
       </c>
       <c r="E33" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.255639097744361</v>
       </c>
       <c r="F33" s="2" t="s">
@@ -1348,7 +1352,7 @@
         <v>61.73</v>
       </c>
       <c r="E34" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.48436740644743237</v>
       </c>
       <c r="F34" s="2" t="s">
@@ -1369,7 +1373,7 @@
         <v>6.16</v>
       </c>
       <c r="E35" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.0032467532467533</v>
       </c>
       <c r="F35" s="2" t="s">
@@ -1390,7 +1394,7 @@
         <v>32.69</v>
       </c>
       <c r="E36" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.38452126032425821</v>
       </c>
       <c r="F36" s="2" t="s">
@@ -1411,7 +1415,7 @@
         <v>72.319999999999993</v>
       </c>
       <c r="E37" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3827433628318586</v>
       </c>
       <c r="F37" s="2" t="s">
@@ -1432,7 +1436,7 @@
         <v>2362.94</v>
       </c>
       <c r="E38" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.4513360474662916E-3</v>
       </c>
       <c r="F38" s="2" t="s">
@@ -1453,7 +1457,7 @@
         <v>335.9</v>
       </c>
       <c r="E39" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F39" s="2" t="s">
@@ -1474,7 +1478,7 @@
         <v>648.80999999999995</v>
       </c>
       <c r="E40" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.46235415607034425</v>
       </c>
       <c r="F40" s="2" t="s">
@@ -1495,7 +1499,7 @@
         <v>9.89</v>
       </c>
       <c r="E41" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3650151668351871</v>
       </c>
       <c r="F41" s="2" t="s">
@@ -1507,17 +1511,17 @@
         <v>45909.449305555558</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C42" s="6">
         <v>100</v>
       </c>
       <c r="D42" s="6">
-        <v>215.58</v>
+        <v>579.10599999999999</v>
       </c>
       <c r="E42" s="6">
-        <f t="shared" si="0"/>
-        <v>0.46386492253455791</v>
+        <f t="shared" si="1"/>
+        <v>0.17267995841866601</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>7</v>
@@ -1528,17 +1532,17 @@
         <v>45909.449305555558</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="6">
         <v>100</v>
       </c>
       <c r="D43" s="6">
-        <v>579.10599999999999</v>
+        <v>215.58</v>
       </c>
       <c r="E43" s="6">
-        <f t="shared" si="0"/>
-        <v>0.17267995841866601</v>
+        <f t="shared" ref="E43:E74" si="2">C43/D43</f>
+        <v>0.46386492253455791</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>7</v>
@@ -1549,17 +1553,17 @@
         <v>45910</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C44" s="6">
-        <v>20.14</v>
+        <v>8.4</v>
       </c>
       <c r="D44" s="6">
-        <v>341.71</v>
+        <v>5.69</v>
       </c>
       <c r="E44" s="6">
-        <f t="shared" si="0"/>
-        <v>5.8938866290129059E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.476274165202109</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>7</v>
@@ -1570,17 +1574,17 @@
         <v>45910</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C45" s="6">
-        <v>8.4</v>
+        <v>20.14</v>
       </c>
       <c r="D45" s="6">
-        <v>5.69</v>
+        <v>341.71</v>
       </c>
       <c r="E45" s="6">
-        <f t="shared" si="0"/>
-        <v>1.476274165202109</v>
+        <f t="shared" si="2"/>
+        <v>5.8938866290129059E-2</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>7</v>
@@ -1591,17 +1595,17 @@
         <v>45911</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C46" s="6">
-        <v>18.059999999999999</v>
+        <v>101.44</v>
       </c>
       <c r="D46" s="6">
-        <v>308.70999999999998</v>
+        <v>73.36</v>
       </c>
       <c r="E46" s="6">
-        <f t="shared" si="0"/>
-        <v>5.8501506268018526E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.3827699018538713</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>38</v>
@@ -1612,17 +1616,17 @@
         <v>45911</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C47" s="6">
-        <v>101.44</v>
+        <v>18.059999999999999</v>
       </c>
       <c r="D47" s="6">
-        <v>73.36</v>
+        <v>308.70999999999998</v>
       </c>
       <c r="E47" s="6">
-        <f t="shared" si="0"/>
-        <v>1.3827699018538713</v>
+        <f t="shared" si="2"/>
+        <v>5.8501506268018526E-2</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>38</v>
@@ -1633,17 +1637,17 @@
         <v>45912</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C48" s="6">
-        <v>54.9</v>
+        <v>13.8</v>
       </c>
       <c r="D48" s="6">
-        <v>54.9</v>
+        <v>1.37</v>
       </c>
       <c r="E48" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>10.072992700729927</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>7</v>
@@ -1657,14 +1661,14 @@
         <v>45</v>
       </c>
       <c r="C49" s="6">
-        <v>13.8</v>
+        <v>43</v>
       </c>
       <c r="D49" s="6">
-        <v>1.37</v>
+        <v>1.71</v>
       </c>
       <c r="E49" s="6">
-        <f t="shared" si="0"/>
-        <v>10.072992700729927</v>
+        <f t="shared" si="2"/>
+        <v>25.146198830409357</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>7</v>
@@ -1678,14 +1682,14 @@
         <v>45</v>
       </c>
       <c r="C50" s="6">
-        <v>43</v>
+        <v>6.04</v>
       </c>
       <c r="D50" s="6">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="E50" s="6">
-        <f t="shared" si="0"/>
-        <v>25.146198830409357</v>
+        <f t="shared" si="2"/>
+        <v>4.0266666666666664</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>7</v>
@@ -1696,17 +1700,17 @@
         <v>45912</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C51" s="6">
-        <v>6.04</v>
+        <v>54.9</v>
       </c>
       <c r="D51" s="6">
-        <v>1.5</v>
+        <v>54.9</v>
       </c>
       <c r="E51" s="6">
-        <f t="shared" si="0"/>
-        <v>4.0266666666666664</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>7</v>
@@ -1717,17 +1721,17 @@
         <v>45923</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C52" s="6">
-        <v>68.2</v>
+        <v>146</v>
       </c>
       <c r="D52" s="6">
-        <v>68.19</v>
+        <v>251.48</v>
       </c>
       <c r="E52" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0001466490687785</v>
+        <f t="shared" si="2"/>
+        <v>0.58056306664545887</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>7</v>
@@ -1738,20 +1742,20 @@
         <v>45923</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C53" s="6">
-        <v>146</v>
+        <v>103.08</v>
       </c>
       <c r="D53" s="6">
-        <v>251.48</v>
+        <v>666.18</v>
       </c>
       <c r="E53" s="6">
-        <f t="shared" si="0"/>
-        <v>0.58056306664545887</v>
+        <f t="shared" si="2"/>
+        <v>0.15473295505719176</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1759,17 +1763,17 @@
         <v>45923</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="C54" s="6">
-        <v>170.44</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="D54" s="6">
-        <v>170.43</v>
+        <v>765.72</v>
       </c>
       <c r="E54" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0000586751158833</v>
+        <f t="shared" si="2"/>
+        <v>0.10446377265841299</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>7</v>
@@ -1780,17 +1784,17 @@
         <v>45923</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C55" s="6">
-        <v>79.989999999999995</v>
+        <v>35.79</v>
       </c>
       <c r="D55" s="6">
-        <v>765.72</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="E55" s="6">
-        <f t="shared" si="0"/>
-        <v>0.10446377265841299</v>
+        <f t="shared" si="2"/>
+        <v>4.4570361145703616</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>7</v>
@@ -1801,17 +1805,17 @@
         <v>45923</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C56" s="6">
-        <v>35.79</v>
+        <v>68.2</v>
       </c>
       <c r="D56" s="6">
-        <v>8.0299999999999994</v>
+        <v>68.19</v>
       </c>
       <c r="E56" s="6">
-        <f t="shared" si="0"/>
-        <v>4.4570361145703616</v>
+        <f t="shared" si="2"/>
+        <v>1.0001466490687785</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>7</v>
@@ -1822,20 +1826,20 @@
         <v>45923</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C57" s="6">
-        <v>103.08</v>
+        <v>170.44</v>
       </c>
       <c r="D57" s="6">
-        <v>666.18</v>
+        <v>170.43</v>
       </c>
       <c r="E57" s="6">
-        <f t="shared" si="0"/>
-        <v>0.15473295505719176</v>
+        <f t="shared" si="2"/>
+        <v>1.0000586751158833</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -1843,17 +1847,17 @@
         <v>45924</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C58" s="6">
-        <v>49.37</v>
+        <v>49.84</v>
       </c>
       <c r="D58" s="6">
-        <v>48.95</v>
+        <v>121.43</v>
       </c>
       <c r="E58" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0085801838610826</v>
+        <f t="shared" si="2"/>
+        <v>0.41044223009141068</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>38</v>
@@ -1864,17 +1868,17 @@
         <v>45924</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C59" s="6">
-        <v>49.84</v>
+        <v>49.37</v>
       </c>
       <c r="D59" s="6">
-        <v>121.43</v>
+        <v>48.95</v>
       </c>
       <c r="E59" s="6">
-        <f t="shared" si="0"/>
-        <v>0.41044223009141068</v>
+        <f t="shared" si="2"/>
+        <v>1.0085801838610826</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>38</v>
@@ -1894,7 +1898,7 @@
         <v>327</v>
       </c>
       <c r="E60" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.6180122324159022</v>
       </c>
       <c r="F60" s="2" t="s">
@@ -1906,17 +1910,17 @@
         <v>45937</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C61" s="6">
-        <v>61.28</v>
+        <v>67.88</v>
       </c>
       <c r="D61" s="6">
-        <v>61.27</v>
+        <v>33.94</v>
       </c>
       <c r="E61" s="6">
-        <f t="shared" si="0"/>
-        <v>1.000163212012404</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>7</v>
@@ -1927,17 +1931,17 @@
         <v>45937</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C62" s="6">
-        <v>67.88</v>
+        <v>61.28</v>
       </c>
       <c r="D62" s="6">
-        <v>33.94</v>
+        <v>61.27</v>
       </c>
       <c r="E62" s="6">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>1.000163212012404</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>7</v>
@@ -1957,7 +1961,7 @@
         <v>12.39</v>
       </c>
       <c r="E63" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4.0016142050040351</v>
       </c>
       <c r="F63" s="2" t="s">
@@ -1978,7 +1982,7 @@
         <v>5.32</v>
       </c>
       <c r="E64" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
@@ -1999,7 +2003,7 @@
         <v>57.48</v>
       </c>
       <c r="E65" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="F65" s="2" t="s">
@@ -2020,7 +2024,7 @@
         <v>604.97</v>
       </c>
       <c r="E66" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.12197299039621799</v>
       </c>
       <c r="F66" s="2" t="s">
@@ -2100,8 +2104,9 @@
       <c r="D70" s="6">
         <v>246.88</v>
       </c>
-      <c r="E70" s="6">
-        <v>8.4540000000000004E-2</v>
+      <c r="E70" s="8">
+        <f>C70/D70</f>
+        <v>8.4534996759559305E-2</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>38</v>
@@ -2332,16 +2337,16 @@
         <v>45957.464583333334</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C82" s="6">
-        <v>19.87</v>
+        <v>19.239999999999998</v>
       </c>
       <c r="D82" s="6">
-        <v>12.92</v>
+        <v>2277.38</v>
       </c>
       <c r="E82" s="6">
-        <v>1.53</v>
+        <v>8.4499999999999992E-3</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>38</v>
@@ -2352,16 +2357,16 @@
         <v>45957.464583333334</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C83" s="6">
-        <v>19.239999999999998</v>
+        <v>19.87</v>
       </c>
       <c r="D83" s="6">
-        <v>2277.38</v>
+        <v>12.92</v>
       </c>
       <c r="E83" s="6">
-        <v>8.4499999999999992E-3</v>
+        <v>1.53</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>38</v>
@@ -2512,16 +2517,16 @@
         <v>45958.522222222222</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C91" s="6">
-        <v>27.36</v>
+        <v>28.62</v>
       </c>
       <c r="D91" s="6">
-        <v>465.39</v>
+        <v>51.12</v>
       </c>
       <c r="E91" s="6">
-        <v>5.8790000000000002E-2</v>
+        <v>0.55984</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>38</v>
@@ -2532,16 +2537,16 @@
         <v>45958.522222222222</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C92" s="6">
-        <v>28.62</v>
+        <v>27.36</v>
       </c>
       <c r="D92" s="6">
-        <v>51.12</v>
+        <v>465.39</v>
       </c>
       <c r="E92" s="6">
-        <v>0.55984</v>
+        <v>5.8790000000000002E-2</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>38</v>
@@ -2609,19 +2614,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>46002.439583333333</v>
+        <v>46002</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C96" s="6">
-        <v>85.87</v>
+        <v>499.99</v>
       </c>
       <c r="D96" s="6">
-        <v>41.27</v>
+        <v>685.2</v>
       </c>
       <c r="E96" s="6">
-        <v>2.08</v>
+        <v>0.72970000000000002</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>7</v>
@@ -2629,19 +2634,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>46002.443749999999</v>
+        <v>46002.439583333333</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C97" s="6">
-        <v>123.81</v>
+        <v>85.87</v>
       </c>
       <c r="D97" s="6">
-        <v>51.34</v>
+        <v>41.27</v>
       </c>
       <c r="E97" s="6">
-        <v>2.41</v>
+        <v>2.08</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>7</v>
@@ -2649,19 +2654,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>46002.446527777778</v>
+        <v>46002.443749999999</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C98" s="6">
-        <v>163.26</v>
+        <v>123.81</v>
       </c>
       <c r="D98" s="6">
-        <v>24.08</v>
+        <v>51.34</v>
       </c>
       <c r="E98" s="6">
-        <v>6.77</v>
+        <v>2.41</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>7</v>
@@ -2669,19 +2674,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>46008.648611111108</v>
+        <v>46002.446527777778</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C99" s="6">
-        <v>42.24</v>
+        <v>163.26</v>
       </c>
       <c r="D99" s="6">
-        <v>21.11</v>
+        <v>24.08</v>
       </c>
       <c r="E99" s="6">
-        <v>2</v>
+        <v>6.77</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>7</v>
@@ -2689,19 +2694,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>46008.650694444441</v>
+        <v>46008.648611111108</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C100" s="6">
-        <v>87.04</v>
+        <v>42.24</v>
       </c>
       <c r="D100" s="6">
-        <v>48.49</v>
+        <v>21.11</v>
       </c>
       <c r="E100" s="6">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>7</v>
@@ -2709,79 +2714,79 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>46020.463888888888</v>
+        <v>46008.650694444441</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="C101" s="6">
-        <v>59.64</v>
+        <v>87.04</v>
       </c>
       <c r="D101" s="6">
-        <v>59.54</v>
+        <v>48.49</v>
       </c>
       <c r="E101" s="6">
-        <v>1</v>
+        <v>1.79</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>46021.472916666666</v>
+        <v>46020.463888888888</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C102" s="6">
-        <v>56.4</v>
+        <v>59.64</v>
       </c>
       <c r="D102" s="6">
-        <v>5.69</v>
+        <v>59.54</v>
       </c>
       <c r="E102" s="6">
-        <v>9.9</v>
+        <v>1</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>46027.567361111112</v>
+        <v>46021.472916666666</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C103" s="6">
-        <v>17.54</v>
+        <v>56.4</v>
       </c>
       <c r="D103" s="6">
-        <v>0.44</v>
+        <v>5.69</v>
       </c>
       <c r="E103" s="6">
-        <v>39.246000000000002</v>
+        <v>9.9</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>46027.568055555559</v>
+        <v>46027.567361111112</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C104" s="6">
-        <v>31.01</v>
+        <v>17.54</v>
       </c>
       <c r="D104" s="6">
-        <v>233.54</v>
+        <v>0.44</v>
       </c>
       <c r="E104" s="6">
-        <v>0.13278000000000001</v>
+        <v>39.246000000000002</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>38</v>
@@ -2789,19 +2794,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>46027.568749999999</v>
+        <v>46027.568055555559</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C105" s="6">
-        <v>36.840000000000003</v>
+        <v>31.01</v>
       </c>
       <c r="D105" s="6">
-        <v>36.83</v>
+        <v>233.54</v>
       </c>
       <c r="E105" s="6">
-        <v>1</v>
+        <v>0.13278000000000001</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>38</v>
@@ -2809,19 +2814,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>46029.449305555558</v>
+        <v>46027.568749999999</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C106" s="6">
-        <v>107.56</v>
+        <v>36.840000000000003</v>
       </c>
       <c r="D106" s="6">
-        <v>100.39</v>
+        <v>36.83</v>
       </c>
       <c r="E106" s="6">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>38</v>
@@ -2829,19 +2834,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>46034.47152777778</v>
+        <v>46029.449305555558</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C107" s="6">
-        <v>184.51</v>
+        <v>107.56</v>
       </c>
       <c r="D107" s="6">
-        <v>625.9</v>
+        <v>100.39</v>
       </c>
       <c r="E107" s="6">
-        <v>0.29479</v>
+        <v>1.07</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>38</v>
@@ -2852,16 +2857,16 @@
         <v>46034.47152777778</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C108" s="6">
-        <v>428.25</v>
+        <v>184.51</v>
       </c>
       <c r="D108" s="6">
-        <v>342</v>
+        <v>625.9</v>
       </c>
       <c r="E108" s="6">
-        <v>1.25</v>
+        <v>0.29479</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>38</v>
@@ -2869,39 +2874,39 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>46035.44027777778</v>
+        <v>46034.47152777778</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C109" s="6">
-        <v>262</v>
+        <v>428.25</v>
       </c>
       <c r="D109" s="6">
-        <v>49.47</v>
+        <v>342</v>
       </c>
       <c r="E109" s="6">
-        <v>5.29</v>
+        <v>1.25</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>46035.441666666666</v>
+        <v>46035.44027777778</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C110" s="6">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="D110" s="6">
-        <v>56.67</v>
+        <v>49.47</v>
       </c>
       <c r="E110" s="6">
-        <v>4.8600000000000003</v>
+        <v>5.29</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>7</v>
@@ -2909,19 +2914,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>46036.448611111111</v>
+        <v>46035.441666666666</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C111" s="6">
-        <v>269.58999999999997</v>
+        <v>276</v>
       </c>
       <c r="D111" s="6">
-        <v>183.13</v>
+        <v>56.67</v>
       </c>
       <c r="E111" s="6">
-        <v>1.47</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>7</v>
@@ -2929,19 +2934,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>46042.441666666666</v>
+        <v>46036.448611111111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C112" s="6">
-        <v>300</v>
+        <v>269.58999999999997</v>
       </c>
       <c r="D112" s="6">
-        <v>14.93</v>
+        <v>183.13</v>
       </c>
       <c r="E112" s="6">
-        <v>20.09</v>
+        <v>1.47</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>7</v>
@@ -2969,19 +2974,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>46042.45</v>
+        <v>46042.441666666666</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C114" s="6">
-        <v>376.94</v>
+        <v>300</v>
       </c>
       <c r="D114" s="6">
-        <v>376.93</v>
+        <v>14.93</v>
       </c>
       <c r="E114" s="6">
-        <v>1</v>
+        <v>20.09</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>7</v>
@@ -2989,23 +2994,22 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>46044.496527777781</v>
+        <v>46042.45</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C115" s="6">
-        <v>59.02</v>
+        <v>376.94</v>
       </c>
       <c r="D115" s="6">
-        <v>127.23</v>
+        <v>376.93</v>
       </c>
       <c r="E115" s="6">
-        <f>D115/C115</f>
-        <v>2.1557099288376822</v>
+        <v>1</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3030,19 +3034,20 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>46044.49722222222</v>
+        <v>46044.496527777781</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C117" s="6">
-        <v>335.17</v>
+        <v>59.02</v>
       </c>
       <c r="D117" s="6">
-        <v>22.18</v>
+        <v>127.23</v>
       </c>
       <c r="E117" s="6">
-        <v>15.11</v>
+        <f>D117/C117</f>
+        <v>2.1557099288376822</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>38</v>
@@ -3050,39 +3055,39 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>46045.445833333331</v>
+        <v>46044.49722222222</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="C118" s="6">
-        <v>400</v>
+        <v>335.17</v>
       </c>
       <c r="D118" s="6">
-        <v>70</v>
+        <v>22.18</v>
       </c>
       <c r="E118" s="6">
-        <v>5.71</v>
+        <v>15.11</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>46045.493055555555</v>
+        <v>46045.445833333331</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C119" s="6">
-        <v>515.05999999999995</v>
+        <v>400</v>
       </c>
       <c r="D119" s="6">
-        <v>659.79</v>
+        <v>70</v>
       </c>
       <c r="E119" s="6">
-        <v>0.78064</v>
+        <v>5.71</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>7</v>
@@ -3090,82 +3095,82 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>46048.572222222225</v>
+        <v>46045.493055555555</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C120" s="6">
-        <v>322.73</v>
+        <v>515.05999999999995</v>
       </c>
       <c r="D120" s="6">
-        <v>80.680000000000007</v>
+        <v>659.79</v>
       </c>
       <c r="E120" s="6">
-        <v>4</v>
+        <v>0.78064</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>46049.448611111111</v>
+        <v>46048.572222222225</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C121" s="6">
-        <v>322.47000000000003</v>
+        <v>322.73</v>
       </c>
       <c r="D121" s="6">
-        <v>89.38</v>
+        <v>80.680000000000007</v>
       </c>
       <c r="E121" s="6">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>46050.563888888886</v>
+        <v>46049.448611111111</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C122" s="6">
-        <v>234.4</v>
+        <v>322.47000000000003</v>
       </c>
       <c r="D122" s="6">
-        <v>159.22999999999999</v>
+        <v>89.38</v>
       </c>
       <c r="E122" s="6">
-        <v>1.47</v>
+        <v>3.6</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>46059</v>
+        <v>46050.563888888886</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C123" s="6">
-        <v>649.04</v>
+        <v>234.4</v>
       </c>
       <c r="D123" s="6">
-        <v>59.58</v>
+        <v>159.22999999999999</v>
       </c>
       <c r="E123" s="6">
-        <v>10.89</v>
+        <v>1.47</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3210,19 +3215,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>46083.456250000003</v>
+        <v>46059</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C126" s="6">
-        <v>480.63</v>
+        <v>649.04</v>
       </c>
       <c r="D126" s="6">
-        <v>160.21</v>
+        <v>59.58</v>
       </c>
       <c r="E126" s="6">
-        <v>3</v>
+        <v>10.89</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>7</v>
@@ -3230,19 +3235,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>46086</v>
+        <v>46083.456250000003</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C127" s="6">
-        <v>175.04</v>
+        <v>480.63</v>
       </c>
       <c r="D127" s="6">
-        <v>98.34</v>
+        <v>160.21</v>
       </c>
       <c r="E127" s="6">
-        <v>1.7799471222290013</v>
+        <v>3</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>7</v>
@@ -3250,19 +3255,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>46002</v>
+        <v>46086</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C128" s="6">
-        <v>499.99</v>
+        <v>175.04</v>
       </c>
       <c r="D128" s="6">
-        <v>685.2</v>
+        <v>98.34</v>
       </c>
       <c r="E128" s="6">
-        <v>0.72970000000000002</v>
+        <v>1.7799471222290013</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>7</v>
@@ -3273,16 +3278,16 @@
         <v>46087</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="C129" s="6">
-        <v>599.1</v>
+        <v>462.97</v>
       </c>
       <c r="D129" s="6">
-        <v>299.41000000000003</v>
+        <v>81.02</v>
       </c>
       <c r="E129" s="6">
-        <v>2.0009399999999999</v>
+        <v>5.7142799999999996</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>38</v>
@@ -3313,16 +3318,16 @@
         <v>46087</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C131" s="6">
-        <v>333.26</v>
+        <v>291.45999999999998</v>
       </c>
       <c r="D131" s="6">
-        <v>16.579999999999998</v>
+        <v>80.78</v>
       </c>
       <c r="E131" s="6">
-        <v>20.037700000000001</v>
+        <v>3.60785</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>38</v>
@@ -3333,16 +3338,16 @@
         <v>46087</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="C132" s="6">
-        <v>525.9</v>
+        <v>333.26</v>
       </c>
       <c r="D132" s="6">
-        <v>59.68</v>
+        <v>16.579999999999998</v>
       </c>
       <c r="E132" s="6">
-        <v>8.8120799999999999</v>
+        <v>20.037700000000001</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>38</v>
@@ -3353,16 +3358,16 @@
         <v>46087</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="C133" s="6">
-        <v>462.97</v>
+        <v>599.1</v>
       </c>
       <c r="D133" s="6">
-        <v>81.02</v>
+        <v>299.41000000000003</v>
       </c>
       <c r="E133" s="6">
-        <v>5.7142799999999996</v>
+        <v>2.0009399999999999</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>38</v>
@@ -3373,16 +3378,16 @@
         <v>46087</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C134" s="6">
-        <v>291.45999999999998</v>
+        <v>222.54</v>
       </c>
       <c r="D134" s="6">
-        <v>80.78</v>
+        <v>20.58</v>
       </c>
       <c r="E134" s="6">
-        <v>3.60785</v>
+        <v>10.81081</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>38</v>
@@ -3393,16 +3398,16 @@
         <v>46087</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C135" s="6">
-        <v>222.54</v>
+        <v>525.9</v>
       </c>
       <c r="D135" s="6">
-        <v>20.58</v>
+        <v>59.68</v>
       </c>
       <c r="E135" s="6">
-        <v>10.81081</v>
+        <v>8.8120799999999999</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>38</v>
@@ -3433,16 +3438,16 @@
         <v>46090</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C137" s="6">
-        <v>788</v>
+        <v>1113.31</v>
       </c>
       <c r="D137" s="6">
-        <v>116.55</v>
+        <v>677.47</v>
       </c>
       <c r="E137" s="6">
-        <v>6.7617500000000001</v>
+        <v>1.6433199999999999</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>7</v>
@@ -3453,16 +3458,16 @@
         <v>46090</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C138" s="6">
-        <v>500</v>
+        <v>788</v>
       </c>
       <c r="D138" s="6">
-        <v>63.36</v>
+        <v>116.55</v>
       </c>
       <c r="E138" s="6">
-        <v>7.89</v>
+        <v>6.7617500000000001</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>7</v>
@@ -3473,16 +3478,16 @@
         <v>46090</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C139" s="6">
         <v>500</v>
       </c>
       <c r="D139" s="6">
-        <v>37.89</v>
+        <v>63.36</v>
       </c>
       <c r="E139" s="6">
-        <v>13.19</v>
+        <v>7.89</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>7</v>
@@ -3493,16 +3498,16 @@
         <v>46090</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C140" s="6">
-        <v>1113.31</v>
+        <v>500</v>
       </c>
       <c r="D140" s="6">
-        <v>677.47</v>
+        <v>37.89</v>
       </c>
       <c r="E140" s="6">
-        <v>1.6433199999999999</v>
+        <v>13.19</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>7</v>
@@ -3513,19 +3518,19 @@
         <v>46091</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C141" s="6">
-        <v>476.34</v>
+        <v>590</v>
       </c>
       <c r="D141" s="6">
-        <v>158.78</v>
+        <v>409.79</v>
       </c>
       <c r="E141" s="6">
-        <v>3</v>
+        <v>1.43988</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -3533,19 +3538,19 @@
         <v>46091</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C142" s="6">
-        <v>489.57</v>
+        <v>450.15</v>
       </c>
       <c r="D142" s="6">
-        <v>37.1</v>
+        <v>90.02</v>
       </c>
       <c r="E142" s="6">
-        <v>13.19</v>
+        <v>5</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -3553,19 +3558,19 @@
         <v>46091</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C143" s="6">
-        <v>590</v>
+        <v>476.34</v>
       </c>
       <c r="D143" s="6">
-        <v>409.79</v>
+        <v>158.78</v>
       </c>
       <c r="E143" s="6">
-        <v>1.43988</v>
+        <v>3</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -3573,19 +3578,19 @@
         <v>46091</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C144" s="6">
-        <v>450.15</v>
+        <v>466.86</v>
       </c>
       <c r="D144" s="6">
-        <v>90.02</v>
+        <v>59.16</v>
       </c>
       <c r="E144" s="6">
-        <v>5</v>
+        <v>7.89079</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -3593,16 +3598,16 @@
         <v>46091</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C145" s="6">
-        <v>466.86</v>
+        <v>489.57</v>
       </c>
       <c r="D145" s="6">
-        <v>59.16</v>
+        <v>37.1</v>
       </c>
       <c r="E145" s="6">
-        <v>7.89079</v>
+        <v>13.19</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>38</v>
@@ -3674,19 +3679,19 @@
         <v>46113</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="C149" s="6">
-        <v>1054.31</v>
+        <v>500</v>
       </c>
       <c r="D149" s="6">
-        <v>123.39</v>
+        <v>83.33</v>
       </c>
       <c r="E149" s="6">
-        <v>8.5441699999999994</v>
+        <v>6.0002399999999998</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -3694,16 +3699,16 @@
         <v>46113</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C150" s="6">
-        <v>515.58000000000004</v>
+        <v>1054.31</v>
       </c>
       <c r="D150" s="6">
-        <v>71.459999999999994</v>
+        <v>123.39</v>
       </c>
       <c r="E150" s="6">
-        <v>7.2149599999999996</v>
+        <v>8.5441699999999994</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>38</v>
@@ -3714,19 +3719,19 @@
         <v>46113</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C151" s="6">
-        <v>500</v>
+        <v>515.58000000000004</v>
       </c>
       <c r="D151" s="6">
-        <v>83.33</v>
+        <v>71.459999999999994</v>
       </c>
       <c r="E151" s="6">
-        <v>6.0002399999999998</v>
+        <v>7.2149599999999996</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -3789,8 +3794,32 @@
         <v>7</v>
       </c>
     </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" s="6">
+        <v>353.72</v>
+      </c>
+      <c r="D155" s="6">
+        <v>4.78</v>
+      </c>
+      <c r="E155" s="6">
+        <v>74</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F128" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}"/>
+  <autoFilter ref="A1:F155" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F154">
+      <sortCondition ref="A1:A128"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33DFDF0-01BD-4090-8E9D-C1A4A4D25C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7E98F1-68C3-4256-8FD0-860A879BFD06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="1440" windowWidth="21585" windowHeight="11295" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
   <sheets>
     <sheet name="logs" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="68">
   <si>
     <t>date</t>
   </si>
@@ -228,6 +228,21 @@
   </si>
   <si>
     <t>HOOD</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>IGV</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>CRM</t>
   </si>
 </sst>
 </file>
@@ -235,12 +250,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.000000000000"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -253,6 +268,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -273,10 +295,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -290,20 +313,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -636,13 +663,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F174"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="21.5" style="6" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="21.5" style="5" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="6" customWidth="1"/>
     <col min="6" max="6" width="10.875" style="2"/>
   </cols>
@@ -654,16 +681,16 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
@@ -674,10 +701,10 @@
       <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>50</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <v>9.14</v>
       </c>
       <c r="E2" s="6">
@@ -695,10 +722,10 @@
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>200</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>63.42</v>
       </c>
       <c r="E3" s="6">
@@ -716,10 +743,10 @@
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>200</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>33.61</v>
       </c>
       <c r="E4" s="6">
@@ -737,10 +764,10 @@
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>200</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>317.19</v>
       </c>
       <c r="E5" s="6">
@@ -758,10 +785,10 @@
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>250</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>328.13</v>
       </c>
       <c r="E6" s="6">
@@ -779,10 +806,10 @@
       <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>50</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>131.86000000000001</v>
       </c>
       <c r="E7" s="6">
@@ -800,10 +827,10 @@
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>200</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>643.12</v>
       </c>
       <c r="E8" s="6">
@@ -821,10 +848,10 @@
       <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>19.989999999999998</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>45.22</v>
       </c>
       <c r="E9" s="6">
@@ -842,10 +869,10 @@
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>19.989999999999998</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>39.6</v>
       </c>
       <c r="E10" s="6">
@@ -862,10 +889,10 @@
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>25</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>5.26</v>
       </c>
       <c r="E11" s="6">
@@ -883,10 +910,10 @@
       <c r="B12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>19.989999999999998</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>339.97</v>
       </c>
       <c r="E12" s="6">
@@ -904,13 +931,13 @@
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>19.989999999999998</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>506.14</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <f t="shared" si="1"/>
         <v>3.9495001383016558E-2</v>
       </c>
@@ -925,10 +952,10 @@
       <c r="B14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>19.98</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>737.72</v>
       </c>
       <c r="E14" s="6">
@@ -946,13 +973,13 @@
       <c r="B15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>19.989999999999998</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>236.43</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="6">
         <f t="shared" si="1"/>
         <v>8.4549338070464816E-2</v>
       </c>
@@ -967,10 +994,10 @@
       <c r="B16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>50</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>230.24</v>
       </c>
       <c r="E16" s="6">
@@ -988,10 +1015,10 @@
       <c r="B17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>30</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>225.92</v>
       </c>
       <c r="E17" s="6">
@@ -1009,10 +1036,10 @@
       <c r="B18" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>30</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>61.94</v>
       </c>
       <c r="E18" s="6">
@@ -1030,10 +1057,10 @@
       <c r="B19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>100</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>93.52</v>
       </c>
       <c r="E19" s="6">
@@ -1051,10 +1078,10 @@
       <c r="B20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>49.99</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>1218.2</v>
       </c>
       <c r="E20" s="6">
@@ -1072,10 +1099,10 @@
       <c r="B21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>10</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <v>111.61</v>
       </c>
       <c r="E21" s="6">
@@ -1093,10 +1120,10 @@
       <c r="B22" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>30</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <v>74.92</v>
       </c>
       <c r="E22" s="6">
@@ -1114,10 +1141,10 @@
       <c r="B23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>25</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <v>17.5</v>
       </c>
       <c r="E23" s="6">
@@ -1135,10 +1162,10 @@
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <v>50</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <v>37.47</v>
       </c>
       <c r="E24" s="6">
@@ -1156,10 +1183,10 @@
       <c r="B25" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <v>19.989999999999998</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="5">
         <v>13</v>
       </c>
       <c r="E25" s="6">
@@ -1177,10 +1204,10 @@
       <c r="B26" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <v>19.989999999999998</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="5">
         <v>158.88999999999999</v>
       </c>
       <c r="E26" s="6">
@@ -1198,10 +1225,10 @@
       <c r="B27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>50</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="5">
         <v>49.57</v>
       </c>
       <c r="E27" s="6">
@@ -1219,10 +1246,10 @@
       <c r="B28" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="5">
         <v>30</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="5">
         <v>8.94</v>
       </c>
       <c r="E28" s="6">
@@ -1240,10 +1267,10 @@
       <c r="B29" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <v>25</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="5">
         <v>27.16</v>
       </c>
       <c r="E29" s="6">
@@ -1261,10 +1288,10 @@
       <c r="B30" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="5">
         <v>100</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="5">
         <v>74.34</v>
       </c>
       <c r="E30" s="6">
@@ -1282,10 +1309,10 @@
       <c r="B31" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>30</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="5">
         <v>185.21</v>
       </c>
       <c r="E31" s="6">
@@ -1303,10 +1330,10 @@
       <c r="B32" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="5">
         <v>100</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="5">
         <v>647.66</v>
       </c>
       <c r="E32" s="6">
@@ -1324,10 +1351,10 @@
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>15</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="5">
         <v>6.65</v>
       </c>
       <c r="E33" s="6">
@@ -1345,10 +1372,10 @@
       <c r="B34" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="5">
         <v>29.9</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="5">
         <v>61.73</v>
       </c>
       <c r="E34" s="6">
@@ -1366,10 +1393,10 @@
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="5">
         <v>18.5</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="5">
         <v>6.16</v>
       </c>
       <c r="E35" s="6">
@@ -1387,10 +1414,10 @@
       <c r="B36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="5">
         <v>12.57</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="5">
         <v>32.69</v>
       </c>
       <c r="E36" s="6">
@@ -1408,10 +1435,10 @@
       <c r="B37" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="5">
         <v>100</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="5">
         <v>72.319999999999993</v>
       </c>
       <c r="E37" s="6">
@@ -1429,10 +1456,10 @@
       <c r="B38" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="5">
         <v>19.97</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="5">
         <v>2362.94</v>
       </c>
       <c r="E38" s="6">
@@ -1450,10 +1477,10 @@
       <c r="B39" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="5">
         <v>335.9</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="5">
         <v>335.9</v>
       </c>
       <c r="E39" s="6">
@@ -1471,10 +1498,10 @@
       <c r="B40" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="5">
         <v>299.98</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="5">
         <v>648.80999999999995</v>
       </c>
       <c r="E40" s="6">
@@ -1492,10 +1519,10 @@
       <c r="B41" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="5">
         <v>13.5</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="5">
         <v>9.89</v>
       </c>
       <c r="E41" s="6">
@@ -1513,10 +1540,10 @@
       <c r="B42" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="5">
         <v>100</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="5">
         <v>579.10599999999999</v>
       </c>
       <c r="E42" s="6">
@@ -1534,14 +1561,14 @@
       <c r="B43" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="5">
         <v>100</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="5">
         <v>215.58</v>
       </c>
       <c r="E43" s="6">
-        <f t="shared" ref="E43:E74" si="2">C43/D43</f>
+        <f t="shared" ref="E43:E66" si="2">C43/D43</f>
         <v>0.46386492253455791</v>
       </c>
       <c r="F43" s="2" t="s">
@@ -1555,10 +1582,10 @@
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="5">
         <v>8.4</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="5">
         <v>5.69</v>
       </c>
       <c r="E44" s="6">
@@ -1576,10 +1603,10 @@
       <c r="B45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="5">
         <v>20.14</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="5">
         <v>341.71</v>
       </c>
       <c r="E45" s="6">
@@ -1597,10 +1624,10 @@
       <c r="B46" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="5">
         <v>101.44</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="5">
         <v>73.36</v>
       </c>
       <c r="E46" s="6">
@@ -1618,10 +1645,10 @@
       <c r="B47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="5">
         <v>18.059999999999999</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="5">
         <v>308.70999999999998</v>
       </c>
       <c r="E47" s="6">
@@ -1639,10 +1666,10 @@
       <c r="B48" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="5">
         <v>13.8</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="5">
         <v>1.37</v>
       </c>
       <c r="E48" s="6">
@@ -1660,10 +1687,10 @@
       <c r="B49" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="5">
         <v>43</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="5">
         <v>1.71</v>
       </c>
       <c r="E49" s="6">
@@ -1681,10 +1708,10 @@
       <c r="B50" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="5">
         <v>6.04</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="5">
         <v>1.5</v>
       </c>
       <c r="E50" s="6">
@@ -1702,10 +1729,10 @@
       <c r="B51" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="5">
         <v>54.9</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="5">
         <v>54.9</v>
       </c>
       <c r="E51" s="6">
@@ -1723,10 +1750,10 @@
       <c r="B52" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="5">
         <v>146</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="5">
         <v>251.48</v>
       </c>
       <c r="E52" s="6">
@@ -1744,10 +1771,10 @@
       <c r="B53" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53" s="5">
         <v>103.08</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="5">
         <v>666.18</v>
       </c>
       <c r="E53" s="6">
@@ -1765,10 +1792,10 @@
       <c r="B54" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="5">
         <v>79.989999999999995</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="5">
         <v>765.72</v>
       </c>
       <c r="E54" s="6">
@@ -1786,10 +1813,10 @@
       <c r="B55" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="5">
         <v>35.79</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="5">
         <v>8.0299999999999994</v>
       </c>
       <c r="E55" s="6">
@@ -1807,10 +1834,10 @@
       <c r="B56" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="5">
         <v>68.2</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="5">
         <v>68.19</v>
       </c>
       <c r="E56" s="6">
@@ -1828,10 +1855,10 @@
       <c r="B57" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="5">
         <v>170.44</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="5">
         <v>170.43</v>
       </c>
       <c r="E57" s="6">
@@ -1849,10 +1876,10 @@
       <c r="B58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="5">
         <v>49.84</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="5">
         <v>121.43</v>
       </c>
       <c r="E58" s="6">
@@ -1870,10 +1897,10 @@
       <c r="B59" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="5">
         <v>49.37</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59" s="5">
         <v>48.95</v>
       </c>
       <c r="E59" s="6">
@@ -1891,10 +1918,10 @@
       <c r="B60" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="5">
         <v>202.09</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60" s="5">
         <v>327</v>
       </c>
       <c r="E60" s="6">
@@ -1912,10 +1939,10 @@
       <c r="B61" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="5">
         <v>67.88</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="5">
         <v>33.94</v>
       </c>
       <c r="E61" s="6">
@@ -1933,10 +1960,10 @@
       <c r="B62" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="5">
         <v>61.28</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D62" s="5">
         <v>61.27</v>
       </c>
       <c r="E62" s="6">
@@ -1954,10 +1981,10 @@
       <c r="B63" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63" s="5">
         <v>49.58</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D63" s="5">
         <v>12.39</v>
       </c>
       <c r="E63" s="6">
@@ -1975,10 +2002,10 @@
       <c r="B64" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C64" s="5">
         <v>26.6</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64" s="5">
         <v>5.32</v>
       </c>
       <c r="E64" s="6">
@@ -1996,10 +2023,10 @@
       <c r="B65" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65" s="5">
         <v>114.96</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65" s="5">
         <v>57.48</v>
       </c>
       <c r="E65" s="6">
@@ -2017,10 +2044,10 @@
       <c r="B66" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C66" s="5">
         <v>73.790000000000006</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66" s="5">
         <v>604.97</v>
       </c>
       <c r="E66" s="6">
@@ -2038,10 +2065,10 @@
       <c r="B67" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C67" s="5">
         <v>118.69</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D67" s="5">
         <v>59.34</v>
       </c>
       <c r="E67" s="6">
@@ -2058,10 +2085,10 @@
       <c r="B68" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="5">
         <v>118.51</v>
       </c>
-      <c r="D68" s="6">
+      <c r="D68" s="5">
         <v>124.22</v>
       </c>
       <c r="E68" s="6">
@@ -2078,10 +2105,10 @@
       <c r="B69" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C69" s="5">
         <v>10.11</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D69" s="5">
         <v>112.2</v>
       </c>
       <c r="E69" s="6">
@@ -2098,13 +2125,13 @@
       <c r="B70" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70" s="5">
         <v>20.87</v>
       </c>
-      <c r="D70" s="6">
+      <c r="D70" s="5">
         <v>246.88</v>
       </c>
-      <c r="E70" s="8">
+      <c r="E70" s="6">
         <f>C70/D70</f>
         <v>8.4534996759559305E-2</v>
       </c>
@@ -2119,10 +2146,10 @@
       <c r="B71" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71" s="5">
         <v>24.74</v>
       </c>
-      <c r="D71" s="6">
+      <c r="D71" s="5">
         <v>17.309999999999999</v>
       </c>
       <c r="E71" s="6">
@@ -2139,10 +2166,10 @@
       <c r="B72" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72" s="5">
         <v>48.88</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D72" s="5">
         <v>128.91</v>
       </c>
       <c r="E72" s="6">
@@ -2159,10 +2186,10 @@
       <c r="B73" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C73" s="5">
         <v>29.7</v>
       </c>
-      <c r="D73" s="6">
+      <c r="D73" s="5">
         <v>183.36</v>
       </c>
       <c r="E73" s="6">
@@ -2179,10 +2206,10 @@
       <c r="B74" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C74" s="5">
         <v>28.24</v>
       </c>
-      <c r="D74" s="6">
+      <c r="D74" s="5">
         <v>70.52</v>
       </c>
       <c r="E74" s="6">
@@ -2199,10 +2226,10 @@
       <c r="B75" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C75" s="5">
         <v>161.63</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D75" s="5">
         <v>41.11</v>
       </c>
       <c r="E75" s="6">
@@ -2219,10 +2246,10 @@
       <c r="B76" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76" s="5">
         <v>192.61</v>
       </c>
-      <c r="D76" s="6">
+      <c r="D76" s="5">
         <v>192.61</v>
       </c>
       <c r="E76" s="6">
@@ -2239,10 +2266,10 @@
       <c r="B77" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C77" s="5">
         <v>70.31</v>
       </c>
-      <c r="D77" s="6">
+      <c r="D77" s="5">
         <v>10.29</v>
       </c>
       <c r="E77" s="6">
@@ -2259,10 +2286,10 @@
       <c r="B78" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C78" s="5">
         <v>89.15</v>
       </c>
-      <c r="D78" s="6">
+      <c r="D78" s="5">
         <v>12.12</v>
       </c>
       <c r="E78" s="6">
@@ -2279,10 +2306,10 @@
       <c r="B79" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79" s="5">
         <v>644.76</v>
       </c>
-      <c r="D79" s="6">
+      <c r="D79" s="5">
         <v>365.94</v>
       </c>
       <c r="E79" s="6">
@@ -2299,10 +2326,10 @@
       <c r="B80" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="5">
         <v>117.32</v>
       </c>
-      <c r="D80" s="6">
+      <c r="D80" s="5">
         <v>122.97</v>
       </c>
       <c r="E80" s="6">
@@ -2319,10 +2346,10 @@
       <c r="B81" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C81" s="5">
         <v>55.76</v>
       </c>
-      <c r="D81" s="6">
+      <c r="D81" s="5">
         <v>41.78</v>
       </c>
       <c r="E81" s="6">
@@ -2339,10 +2366,10 @@
       <c r="B82" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82" s="5">
         <v>19.239999999999998</v>
       </c>
-      <c r="D82" s="6">
+      <c r="D82" s="5">
         <v>2277.38</v>
       </c>
       <c r="E82" s="6">
@@ -2359,10 +2386,10 @@
       <c r="B83" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C83" s="5">
         <v>19.87</v>
       </c>
-      <c r="D83" s="6">
+      <c r="D83" s="5">
         <v>12.92</v>
       </c>
       <c r="E83" s="6">
@@ -2379,10 +2406,10 @@
       <c r="B84" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C84" s="5">
         <v>23.32</v>
       </c>
-      <c r="D84" s="6">
+      <c r="D84" s="5">
         <v>52.74</v>
       </c>
       <c r="E84" s="6">
@@ -2399,10 +2426,10 @@
       <c r="B85" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C85" s="5">
         <v>24.23</v>
       </c>
-      <c r="D85" s="6">
+      <c r="D85" s="5">
         <v>4.84</v>
       </c>
       <c r="E85" s="6">
@@ -2419,10 +2446,10 @@
       <c r="B86" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C86" s="5">
         <v>52.96</v>
       </c>
-      <c r="D86" s="6">
+      <c r="D86" s="5">
         <v>52.95</v>
       </c>
       <c r="E86" s="6">
@@ -2439,13 +2466,13 @@
       <c r="B87" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C87" s="5">
         <v>520.39</v>
       </c>
-      <c r="D87" s="6">
+      <c r="D87" s="5">
         <v>541.79</v>
       </c>
-      <c r="E87" s="7">
+      <c r="E87" s="6">
         <v>0.96050999999999997</v>
       </c>
       <c r="F87" s="2" t="s">
@@ -2459,10 +2486,10 @@
       <c r="B88" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C88" s="5">
         <v>238.39</v>
       </c>
-      <c r="D88" s="6">
+      <c r="D88" s="5">
         <v>89.79</v>
       </c>
       <c r="E88" s="6">
@@ -2479,10 +2506,10 @@
       <c r="B89" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C89" s="6">
+      <c r="C89" s="5">
         <v>320.8</v>
       </c>
-      <c r="D89" s="6">
+      <c r="D89" s="5">
         <v>266.82</v>
       </c>
       <c r="E89" s="6">
@@ -2499,10 +2526,10 @@
       <c r="B90" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90" s="5">
         <v>23.77</v>
       </c>
-      <c r="D90" s="6">
+      <c r="D90" s="5">
         <v>188.92</v>
       </c>
       <c r="E90" s="6">
@@ -2519,10 +2546,10 @@
       <c r="B91" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C91" s="5">
         <v>28.62</v>
       </c>
-      <c r="D91" s="6">
+      <c r="D91" s="5">
         <v>51.12</v>
       </c>
       <c r="E91" s="6">
@@ -2539,10 +2566,10 @@
       <c r="B92" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C92" s="5">
         <v>27.36</v>
       </c>
-      <c r="D92" s="6">
+      <c r="D92" s="5">
         <v>465.39</v>
       </c>
       <c r="E92" s="6">
@@ -2559,10 +2586,10 @@
       <c r="B93" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93" s="5">
         <v>166.64</v>
       </c>
-      <c r="D93" s="6">
+      <c r="D93" s="5">
         <v>55.54</v>
       </c>
       <c r="E93" s="6">
@@ -2579,10 +2606,10 @@
       <c r="B94" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C94" s="6">
+      <c r="C94" s="5">
         <v>106.52</v>
       </c>
-      <c r="D94" s="6">
+      <c r="D94" s="5">
         <v>57.69</v>
       </c>
       <c r="E94" s="6">
@@ -2599,10 +2626,10 @@
       <c r="B95" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C95" s="6">
+      <c r="C95" s="5">
         <v>39.07</v>
       </c>
-      <c r="D95" s="6">
+      <c r="D95" s="5">
         <v>55.85</v>
       </c>
       <c r="E95" s="6">
@@ -2619,10 +2646,10 @@
       <c r="B96" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C96" s="5">
         <v>499.99</v>
       </c>
-      <c r="D96" s="6">
+      <c r="D96" s="5">
         <v>685.2</v>
       </c>
       <c r="E96" s="6">
@@ -2639,10 +2666,10 @@
       <c r="B97" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C97" s="6">
+      <c r="C97" s="5">
         <v>85.87</v>
       </c>
-      <c r="D97" s="6">
+      <c r="D97" s="5">
         <v>41.27</v>
       </c>
       <c r="E97" s="6">
@@ -2659,10 +2686,10 @@
       <c r="B98" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C98" s="6">
+      <c r="C98" s="5">
         <v>123.81</v>
       </c>
-      <c r="D98" s="6">
+      <c r="D98" s="5">
         <v>51.34</v>
       </c>
       <c r="E98" s="6">
@@ -2679,10 +2706,10 @@
       <c r="B99" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C99" s="6">
+      <c r="C99" s="5">
         <v>163.26</v>
       </c>
-      <c r="D99" s="6">
+      <c r="D99" s="5">
         <v>24.08</v>
       </c>
       <c r="E99" s="6">
@@ -2699,10 +2726,10 @@
       <c r="B100" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C100" s="5">
         <v>42.24</v>
       </c>
-      <c r="D100" s="6">
+      <c r="D100" s="5">
         <v>21.11</v>
       </c>
       <c r="E100" s="6">
@@ -2719,10 +2746,10 @@
       <c r="B101" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C101" s="6">
+      <c r="C101" s="5">
         <v>87.04</v>
       </c>
-      <c r="D101" s="6">
+      <c r="D101" s="5">
         <v>48.49</v>
       </c>
       <c r="E101" s="6">
@@ -2739,10 +2766,10 @@
       <c r="B102" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C102" s="6">
+      <c r="C102" s="5">
         <v>59.64</v>
       </c>
-      <c r="D102" s="6">
+      <c r="D102" s="5">
         <v>59.54</v>
       </c>
       <c r="E102" s="6">
@@ -2759,10 +2786,10 @@
       <c r="B103" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C103" s="6">
+      <c r="C103" s="5">
         <v>56.4</v>
       </c>
-      <c r="D103" s="6">
+      <c r="D103" s="5">
         <v>5.69</v>
       </c>
       <c r="E103" s="6">
@@ -2779,10 +2806,10 @@
       <c r="B104" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C104" s="6">
+      <c r="C104" s="5">
         <v>17.54</v>
       </c>
-      <c r="D104" s="6">
+      <c r="D104" s="5">
         <v>0.44</v>
       </c>
       <c r="E104" s="6">
@@ -2799,10 +2826,10 @@
       <c r="B105" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C105" s="6">
+      <c r="C105" s="5">
         <v>31.01</v>
       </c>
-      <c r="D105" s="6">
+      <c r="D105" s="5">
         <v>233.54</v>
       </c>
       <c r="E105" s="6">
@@ -2819,10 +2846,10 @@
       <c r="B106" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C106" s="6">
+      <c r="C106" s="5">
         <v>36.840000000000003</v>
       </c>
-      <c r="D106" s="6">
+      <c r="D106" s="5">
         <v>36.83</v>
       </c>
       <c r="E106" s="6">
@@ -2839,10 +2866,10 @@
       <c r="B107" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C107" s="6">
+      <c r="C107" s="5">
         <v>107.56</v>
       </c>
-      <c r="D107" s="6">
+      <c r="D107" s="5">
         <v>100.39</v>
       </c>
       <c r="E107" s="6">
@@ -2859,10 +2886,10 @@
       <c r="B108" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C108" s="6">
+      <c r="C108" s="5">
         <v>184.51</v>
       </c>
-      <c r="D108" s="6">
+      <c r="D108" s="5">
         <v>625.9</v>
       </c>
       <c r="E108" s="6">
@@ -2879,10 +2906,10 @@
       <c r="B109" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C109" s="6">
+      <c r="C109" s="5">
         <v>428.25</v>
       </c>
-      <c r="D109" s="6">
+      <c r="D109" s="5">
         <v>342</v>
       </c>
       <c r="E109" s="6">
@@ -2899,10 +2926,10 @@
       <c r="B110" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C110" s="6">
+      <c r="C110" s="5">
         <v>262</v>
       </c>
-      <c r="D110" s="6">
+      <c r="D110" s="5">
         <v>49.47</v>
       </c>
       <c r="E110" s="6">
@@ -2919,10 +2946,10 @@
       <c r="B111" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C111" s="6">
+      <c r="C111" s="5">
         <v>276</v>
       </c>
-      <c r="D111" s="6">
+      <c r="D111" s="5">
         <v>56.67</v>
       </c>
       <c r="E111" s="6">
@@ -2939,10 +2966,10 @@
       <c r="B112" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C112" s="6">
+      <c r="C112" s="5">
         <v>269.58999999999997</v>
       </c>
-      <c r="D112" s="6">
+      <c r="D112" s="5">
         <v>183.13</v>
       </c>
       <c r="E112" s="6">
@@ -2959,10 +2986,10 @@
       <c r="B113" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C113" s="6">
+      <c r="C113" s="5">
         <v>300</v>
       </c>
-      <c r="D113" s="6">
+      <c r="D113" s="5">
         <v>27.75</v>
       </c>
       <c r="E113" s="6">
@@ -2979,10 +3006,10 @@
       <c r="B114" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C114" s="6">
+      <c r="C114" s="5">
         <v>300</v>
       </c>
-      <c r="D114" s="6">
+      <c r="D114" s="5">
         <v>14.93</v>
       </c>
       <c r="E114" s="6">
@@ -2999,10 +3026,10 @@
       <c r="B115" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C115" s="6">
+      <c r="C115" s="5">
         <v>376.94</v>
       </c>
-      <c r="D115" s="6">
+      <c r="D115" s="5">
         <v>376.93</v>
       </c>
       <c r="E115" s="6">
@@ -3019,10 +3046,10 @@
       <c r="B116" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C116" s="6">
+      <c r="C116" s="5">
         <v>499.32</v>
       </c>
-      <c r="D116" s="6">
+      <c r="D116" s="5">
         <v>50.4</v>
       </c>
       <c r="E116" s="6">
@@ -3039,10 +3066,10 @@
       <c r="B117" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C117" s="6">
+      <c r="C117" s="5">
         <v>59.02</v>
       </c>
-      <c r="D117" s="6">
+      <c r="D117" s="5">
         <v>127.23</v>
       </c>
       <c r="E117" s="6">
@@ -3060,10 +3087,10 @@
       <c r="B118" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C118" s="6">
+      <c r="C118" s="5">
         <v>335.17</v>
       </c>
-      <c r="D118" s="6">
+      <c r="D118" s="5">
         <v>22.18</v>
       </c>
       <c r="E118" s="6">
@@ -3080,10 +3107,10 @@
       <c r="B119" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C119" s="6">
+      <c r="C119" s="5">
         <v>400</v>
       </c>
-      <c r="D119" s="6">
+      <c r="D119" s="5">
         <v>70</v>
       </c>
       <c r="E119" s="6">
@@ -3100,10 +3127,10 @@
       <c r="B120" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C120" s="6">
+      <c r="C120" s="5">
         <v>515.05999999999995</v>
       </c>
-      <c r="D120" s="6">
+      <c r="D120" s="5">
         <v>659.79</v>
       </c>
       <c r="E120" s="6">
@@ -3120,10 +3147,10 @@
       <c r="B121" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C121" s="6">
+      <c r="C121" s="5">
         <v>322.73</v>
       </c>
-      <c r="D121" s="6">
+      <c r="D121" s="5">
         <v>80.680000000000007</v>
       </c>
       <c r="E121" s="6">
@@ -3140,10 +3167,10 @@
       <c r="B122" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C122" s="6">
+      <c r="C122" s="5">
         <v>322.47000000000003</v>
       </c>
-      <c r="D122" s="6">
+      <c r="D122" s="5">
         <v>89.38</v>
       </c>
       <c r="E122" s="6">
@@ -3160,10 +3187,10 @@
       <c r="B123" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C123" s="6">
+      <c r="C123" s="5">
         <v>234.4</v>
       </c>
-      <c r="D123" s="6">
+      <c r="D123" s="5">
         <v>159.22999999999999</v>
       </c>
       <c r="E123" s="6">
@@ -3180,10 +3207,10 @@
       <c r="B124" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C124" s="6">
+      <c r="C124" s="5">
         <v>649.35</v>
       </c>
-      <c r="D124" s="6">
+      <c r="D124" s="5">
         <v>711.77</v>
       </c>
       <c r="E124" s="6">
@@ -3200,10 +3227,10 @@
       <c r="B125" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C125" s="6">
+      <c r="C125" s="5">
         <v>234.14</v>
       </c>
-      <c r="D125" s="6">
+      <c r="D125" s="5">
         <v>4.96</v>
       </c>
       <c r="E125" s="6">
@@ -3220,10 +3247,10 @@
       <c r="B126" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C126" s="6">
+      <c r="C126" s="5">
         <v>649.04</v>
       </c>
-      <c r="D126" s="6">
+      <c r="D126" s="5">
         <v>59.58</v>
       </c>
       <c r="E126" s="6">
@@ -3240,10 +3267,10 @@
       <c r="B127" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C127" s="6">
+      <c r="C127" s="5">
         <v>480.63</v>
       </c>
-      <c r="D127" s="6">
+      <c r="D127" s="5">
         <v>160.21</v>
       </c>
       <c r="E127" s="6">
@@ -3260,10 +3287,10 @@
       <c r="B128" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C128" s="6">
+      <c r="C128" s="5">
         <v>175.04</v>
       </c>
-      <c r="D128" s="6">
+      <c r="D128" s="5">
         <v>98.34</v>
       </c>
       <c r="E128" s="6">
@@ -3280,10 +3307,10 @@
       <c r="B129" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C129" s="6">
+      <c r="C129" s="5">
         <v>462.97</v>
       </c>
-      <c r="D129" s="6">
+      <c r="D129" s="5">
         <v>81.02</v>
       </c>
       <c r="E129" s="6">
@@ -3300,10 +3327,10 @@
       <c r="B130" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C130" s="6">
+      <c r="C130" s="5">
         <v>467.44</v>
       </c>
-      <c r="D130" s="6">
+      <c r="D130" s="5">
         <v>45.39</v>
       </c>
       <c r="E130" s="6">
@@ -3320,10 +3347,10 @@
       <c r="B131" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C131" s="6">
+      <c r="C131" s="5">
         <v>291.45999999999998</v>
       </c>
-      <c r="D131" s="6">
+      <c r="D131" s="5">
         <v>80.78</v>
       </c>
       <c r="E131" s="6">
@@ -3340,10 +3367,10 @@
       <c r="B132" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C132" s="6">
+      <c r="C132" s="5">
         <v>333.26</v>
       </c>
-      <c r="D132" s="6">
+      <c r="D132" s="5">
         <v>16.579999999999998</v>
       </c>
       <c r="E132" s="6">
@@ -3360,10 +3387,10 @@
       <c r="B133" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C133" s="6">
+      <c r="C133" s="5">
         <v>599.1</v>
       </c>
-      <c r="D133" s="6">
+      <c r="D133" s="5">
         <v>299.41000000000003</v>
       </c>
       <c r="E133" s="6">
@@ -3380,10 +3407,10 @@
       <c r="B134" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C134" s="6">
+      <c r="C134" s="5">
         <v>222.54</v>
       </c>
-      <c r="D134" s="6">
+      <c r="D134" s="5">
         <v>20.58</v>
       </c>
       <c r="E134" s="6">
@@ -3400,10 +3427,10 @@
       <c r="B135" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C135" s="6">
+      <c r="C135" s="5">
         <v>525.9</v>
       </c>
-      <c r="D135" s="6">
+      <c r="D135" s="5">
         <v>59.68</v>
       </c>
       <c r="E135" s="6">
@@ -3420,10 +3447,10 @@
       <c r="B136" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C136" s="6">
+      <c r="C136" s="5">
         <v>790.6</v>
       </c>
-      <c r="D136" s="6">
+      <c r="D136" s="5">
         <v>56.79</v>
       </c>
       <c r="E136" s="6">
@@ -3440,10 +3467,10 @@
       <c r="B137" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C137" s="6">
+      <c r="C137" s="5">
         <v>1113.31</v>
       </c>
-      <c r="D137" s="6">
+      <c r="D137" s="5">
         <v>677.47</v>
       </c>
       <c r="E137" s="6">
@@ -3460,10 +3487,10 @@
       <c r="B138" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C138" s="6">
+      <c r="C138" s="5">
         <v>788</v>
       </c>
-      <c r="D138" s="6">
+      <c r="D138" s="5">
         <v>116.55</v>
       </c>
       <c r="E138" s="6">
@@ -3480,10 +3507,10 @@
       <c r="B139" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C139" s="6">
+      <c r="C139" s="5">
         <v>500</v>
       </c>
-      <c r="D139" s="6">
+      <c r="D139" s="5">
         <v>63.36</v>
       </c>
       <c r="E139" s="6">
@@ -3500,10 +3527,10 @@
       <c r="B140" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C140" s="6">
+      <c r="C140" s="5">
         <v>500</v>
       </c>
-      <c r="D140" s="6">
+      <c r="D140" s="5">
         <v>37.89</v>
       </c>
       <c r="E140" s="6">
@@ -3520,10 +3547,10 @@
       <c r="B141" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C141" s="6">
+      <c r="C141" s="5">
         <v>590</v>
       </c>
-      <c r="D141" s="6">
+      <c r="D141" s="5">
         <v>409.79</v>
       </c>
       <c r="E141" s="6">
@@ -3540,10 +3567,10 @@
       <c r="B142" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C142" s="6">
+      <c r="C142" s="5">
         <v>450.15</v>
       </c>
-      <c r="D142" s="6">
+      <c r="D142" s="5">
         <v>90.02</v>
       </c>
       <c r="E142" s="6">
@@ -3560,10 +3587,10 @@
       <c r="B143" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C143" s="6">
+      <c r="C143" s="5">
         <v>476.34</v>
       </c>
-      <c r="D143" s="6">
+      <c r="D143" s="5">
         <v>158.78</v>
       </c>
       <c r="E143" s="6">
@@ -3580,10 +3607,10 @@
       <c r="B144" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C144" s="6">
+      <c r="C144" s="5">
         <v>466.86</v>
       </c>
-      <c r="D144" s="6">
+      <c r="D144" s="5">
         <v>59.16</v>
       </c>
       <c r="E144" s="6">
@@ -3600,10 +3627,10 @@
       <c r="B145" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C145" s="6">
+      <c r="C145" s="5">
         <v>489.57</v>
       </c>
-      <c r="D145" s="6">
+      <c r="D145" s="5">
         <v>37.1</v>
       </c>
       <c r="E145" s="6">
@@ -3620,13 +3647,13 @@
       <c r="B146" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C146" s="6">
+      <c r="C146" s="5">
         <v>1000</v>
       </c>
-      <c r="D146" s="6">
+      <c r="D146" s="5">
         <v>40.119900000000001</v>
       </c>
-      <c r="E146" s="7">
+      <c r="E146" s="6">
         <v>24.925280000000001</v>
       </c>
       <c r="F146" s="2" t="s">
@@ -3640,11 +3667,11 @@
       <c r="B147" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C147" s="6">
+      <c r="C147" s="5">
         <f>D147*E147</f>
         <v>357.59999999999997</v>
       </c>
-      <c r="D147" s="6">
+      <c r="D147" s="5">
         <v>71.52</v>
       </c>
       <c r="E147" s="6">
@@ -3661,10 +3688,10 @@
       <c r="B148" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C148" s="6">
+      <c r="C148" s="5">
         <v>534.99</v>
       </c>
-      <c r="D148" s="6">
+      <c r="D148" s="5">
         <v>74.150000000000006</v>
       </c>
       <c r="E148" s="6">
@@ -3681,10 +3708,10 @@
       <c r="B149" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C149" s="6">
+      <c r="C149" s="5">
         <v>500</v>
       </c>
-      <c r="D149" s="6">
+      <c r="D149" s="5">
         <v>83.33</v>
       </c>
       <c r="E149" s="6">
@@ -3701,10 +3728,10 @@
       <c r="B150" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C150" s="6">
+      <c r="C150" s="5">
         <v>1054.31</v>
       </c>
-      <c r="D150" s="6">
+      <c r="D150" s="5">
         <v>123.39</v>
       </c>
       <c r="E150" s="6">
@@ -3721,10 +3748,10 @@
       <c r="B151" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C151" s="6">
+      <c r="C151" s="5">
         <v>515.58000000000004</v>
       </c>
-      <c r="D151" s="6">
+      <c r="D151" s="5">
         <v>71.459999999999994</v>
       </c>
       <c r="E151" s="6">
@@ -3741,10 +3768,10 @@
       <c r="B152" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C152" s="6">
+      <c r="C152" s="5">
         <v>715.9</v>
       </c>
-      <c r="D152" s="6">
+      <c r="D152" s="5">
         <v>371.51</v>
       </c>
       <c r="E152" s="6">
@@ -3761,10 +3788,10 @@
       <c r="B153" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C153" s="6">
+      <c r="C153" s="5">
         <v>638.77</v>
       </c>
-      <c r="D153" s="6">
+      <c r="D153" s="5">
         <v>86.03</v>
       </c>
       <c r="E153" s="6">
@@ -3781,10 +3808,10 @@
       <c r="B154" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C154" s="6">
+      <c r="C154" s="5">
         <v>525.80999999999995</v>
       </c>
-      <c r="D154" s="6">
+      <c r="D154" s="5">
         <v>175.27</v>
       </c>
       <c r="E154" s="6">
@@ -3801,16 +3828,411 @@
       <c r="B155" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C155" s="6">
+      <c r="C155" s="5">
         <v>353.72</v>
       </c>
-      <c r="D155" s="6">
+      <c r="D155" s="5">
         <v>4.78</v>
       </c>
       <c r="E155" s="6">
         <v>74</v>
       </c>
       <c r="F155" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C156" s="5">
+        <v>500</v>
+      </c>
+      <c r="D156" s="5">
+        <v>83.33</v>
+      </c>
+      <c r="E156" s="6">
+        <v>6</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C157" s="5">
+        <v>715.9</v>
+      </c>
+      <c r="D157" s="5">
+        <v>375.51</v>
+      </c>
+      <c r="E157" s="6">
+        <v>1.92</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C158" s="5">
+        <v>525.80999999999995</v>
+      </c>
+      <c r="D158" s="5">
+        <v>175.27</v>
+      </c>
+      <c r="E158" s="6">
+        <v>3</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C159" s="5">
+        <v>638.77</v>
+      </c>
+      <c r="D159" s="5">
+        <v>86.03</v>
+      </c>
+      <c r="E159" s="6">
+        <v>7.42</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" s="5">
+        <f>D160*E160</f>
+        <v>35.110199999999999</v>
+      </c>
+      <c r="D160" s="5">
+        <v>7.18</v>
+      </c>
+      <c r="E160" s="6">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C161" s="5">
+        <f>D161*E161</f>
+        <v>599.44879999999989</v>
+      </c>
+      <c r="D161" s="5">
+        <v>6.52</v>
+      </c>
+      <c r="E161" s="6">
+        <v>91.94</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C162" s="5">
+        <f>D162*E162</f>
+        <v>1010.506</v>
+      </c>
+      <c r="D162" s="5">
+        <v>40.549999999999997</v>
+      </c>
+      <c r="E162" s="6">
+        <v>24.92</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C163" s="5">
+        <f>D163*E163</f>
+        <v>578.17500000000007</v>
+      </c>
+      <c r="D163" s="5">
+        <v>231.27</v>
+      </c>
+      <c r="E163" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C164" s="5">
+        <f>D164*E164</f>
+        <v>409.69400000000002</v>
+      </c>
+      <c r="D164" s="5">
+        <v>103.72</v>
+      </c>
+      <c r="E164" s="6">
+        <v>3.95</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C165" s="5">
+        <f>D165*E165</f>
+        <v>2422.6028000000001</v>
+      </c>
+      <c r="D165" s="5">
+        <v>992.87</v>
+      </c>
+      <c r="E165" s="6">
+        <v>2.44</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C166" s="5">
+        <f>D166*E166</f>
+        <v>999.24610000000007</v>
+      </c>
+      <c r="D166" s="5">
+        <v>99.23</v>
+      </c>
+      <c r="E166" s="6">
+        <v>10.07</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C167" s="5">
+        <f>D167*E167</f>
+        <v>551.01</v>
+      </c>
+      <c r="D167" s="5">
+        <v>183.67</v>
+      </c>
+      <c r="E167" s="6">
+        <v>3</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C168" s="5">
+        <f>D168*E168</f>
+        <v>890.0447999999999</v>
+      </c>
+      <c r="D168" s="5">
+        <v>383.64</v>
+      </c>
+      <c r="E168" s="6">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>46227</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C169" s="5">
+        <f>D169*E169</f>
+        <v>483.54</v>
+      </c>
+      <c r="D169" s="5">
+        <v>161.18</v>
+      </c>
+      <c r="E169" s="6">
+        <v>3</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" s="5">
+        <f>D170*E170</f>
+        <v>483.2516</v>
+      </c>
+      <c r="D170" s="5">
+        <v>3.98</v>
+      </c>
+      <c r="E170" s="6">
+        <v>121.42</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C171" s="5">
+        <f>D171*E171</f>
+        <v>998.38700000000006</v>
+      </c>
+      <c r="D171" s="5">
+        <v>818.35</v>
+      </c>
+      <c r="E171" s="6">
+        <v>1.22</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C172" s="5">
+        <f>D172*E172</f>
+        <v>580.77499999999998</v>
+      </c>
+      <c r="D172" s="5">
+        <v>232.31</v>
+      </c>
+      <c r="E172" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C173" s="5">
+        <f>D173*E173</f>
+        <v>549.04999999999995</v>
+      </c>
+      <c r="D173" s="5">
+        <v>109.81</v>
+      </c>
+      <c r="E173" s="6">
+        <v>5</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C174" s="5">
+        <f>D174*E174</f>
+        <v>633.54999999999995</v>
+      </c>
+      <c r="D174" s="5">
+        <v>126.71</v>
+      </c>
+      <c r="E174" s="6">
+        <v>5</v>
+      </c>
+      <c r="F174" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7E98F1-68C3-4256-8FD0-860A879BFD06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80A03F6-483A-4AB8-89F2-7B75AAD5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
   <sheets>
-    <sheet name="logs" sheetId="1" r:id="rId1"/>
+    <sheet name="new_logs" sheetId="2" r:id="rId1"/>
+    <sheet name="logs" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">logs!$A$1:$F$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">logs!$A$1:$F$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">new_logs!$A$1:$F$168</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="72">
   <si>
     <t>date</t>
   </si>
@@ -244,6 +246,18 @@
   <si>
     <t>CRM</t>
   </si>
+  <si>
+    <t>date_time</t>
+  </si>
+  <si>
+    <t>ticker</t>
+  </si>
+  <si>
+    <t>Buy</t>
+  </si>
+  <si>
+    <t>Sell</t>
+  </si>
 </sst>
 </file>
 
@@ -253,9 +267,9 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -276,6 +290,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -299,7 +319,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -316,17 +336,23 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -662,6 +688,3555 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E503C2-5372-44CA-920E-B8461526100B}">
+  <dimension ref="A1:F168"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="12.625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="12.625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
+        <v>45903.43472222222</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2">
+        <v>63.42</v>
+      </c>
+      <c r="D2" s="6">
+        <v>3.15</v>
+      </c>
+      <c r="E2" s="6">
+        <f>IF(F2="Sell",-C2*D2,C2*D2)</f>
+        <v>199.773</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>45903.435416666667</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>33.61</v>
+      </c>
+      <c r="D3" s="6">
+        <v>5.94</v>
+      </c>
+      <c r="E3" s="6">
+        <f>IF(F3="Sell",-C3*D3,C3*D3)</f>
+        <v>199.64340000000001</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
+        <v>45903.436111111114</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>317.19</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.63053000000000003</v>
+      </c>
+      <c r="E4" s="6">
+        <f>IF(F4="Sell",-C4*D4,C4*D4)</f>
+        <v>199.9978107</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="11">
+        <v>45903.436805555553</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2">
+        <v>328.13</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.76188999999999996</v>
+      </c>
+      <c r="E5" s="6">
+        <f>IF(F5="Sell",-C5*D5,C5*D5)</f>
+        <v>249.99896569999999</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>45903.438194444447</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2">
+        <v>131.86000000000001</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.37919000000000003</v>
+      </c>
+      <c r="E6" s="6">
+        <f>IF(F6="Sell",-C6*D6,C6*D6)</f>
+        <v>49.999993400000008</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>45903.438888888886</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2">
+        <v>643.12</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.31097999999999998</v>
+      </c>
+      <c r="E7" s="6">
+        <f>IF(F7="Sell",-C7*D7,C7*D7)</f>
+        <v>199.99745759999999</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <v>45903.440972222219</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2">
+        <v>9.14</v>
+      </c>
+      <c r="D8" s="6">
+        <v>5.46</v>
+      </c>
+      <c r="E8" s="6">
+        <f>IF(F8="Sell",-C8*D8,C8*D8)</f>
+        <v>49.904400000000003</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
+        <v>45903.445138888892</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2">
+        <v>45.22</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.44206000000000001</v>
+      </c>
+      <c r="E9" s="6">
+        <f>IF(F9="Sell",-C9*D9,C9*D9)</f>
+        <v>19.989953199999999</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>45903.445833333331</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2">
+        <v>39.6</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.50480000000000003</v>
+      </c>
+      <c r="E10" s="6">
+        <f>IF(F10="Sell",-C10*D10,C10*D10)</f>
+        <v>19.990080000000003</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
+        <v>45903.448611111111</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2">
+        <v>5.26</v>
+      </c>
+      <c r="D11" s="6">
+        <v>4.75</v>
+      </c>
+      <c r="E11" s="6">
+        <f>IF(F11="Sell",-C11*D11,C11*D11)</f>
+        <v>24.984999999999999</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>45903.455555555556</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2">
+        <v>339.97</v>
+      </c>
+      <c r="D12" s="6">
+        <v>5.8790000000000002E-2</v>
+      </c>
+      <c r="E12" s="6">
+        <f>IF(F12="Sell",-C12*D12,C12*D12)</f>
+        <v>19.986836300000004</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
+        <v>45903.463888888888</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="2">
+        <v>506.14</v>
+      </c>
+      <c r="D13" s="6">
+        <v>3.9489999999999997E-2</v>
+      </c>
+      <c r="E13" s="6">
+        <f>IF(F13="Sell",-C13*D13,C13*D13)</f>
+        <v>19.9874686</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
+        <v>45903.46597222222</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="2">
+        <v>737.72</v>
+      </c>
+      <c r="D14" s="6">
+        <v>2.7089999999999999E-2</v>
+      </c>
+      <c r="E14" s="6">
+        <f>IF(F14="Sell",-C14*D14,C14*D14)</f>
+        <v>19.984834800000002</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="11">
+        <v>45903.467361111114</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="2">
+        <v>236.43</v>
+      </c>
+      <c r="D15" s="6">
+        <v>8.4540000000000004E-2</v>
+      </c>
+      <c r="E15" s="6">
+        <f>IF(F15="Sell",-C15*D15,C15*D15)</f>
+        <v>19.987792200000001</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="11">
+        <v>45903.46875</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="2">
+        <v>230.24</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.21715999999999999</v>
+      </c>
+      <c r="E16" s="6">
+        <f>IF(F16="Sell",-C16*D16,C16*D16)</f>
+        <v>49.998918400000001</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="11">
+        <v>45903.470138888886</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="2">
+        <v>225.92</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.13278000000000001</v>
+      </c>
+      <c r="E17" s="6">
+        <f>IF(F17="Sell",-C17*D17,C17*D17)</f>
+        <v>29.9976576</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
+        <v>45903.474999999999</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="2">
+        <v>61.94</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.48430000000000001</v>
+      </c>
+      <c r="E18" s="6">
+        <f>IF(F18="Sell",-C18*D18,C18*D18)</f>
+        <v>29.997541999999999</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="11">
+        <v>45903.476388888892</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="2">
+        <v>93.52</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1.06</v>
+      </c>
+      <c r="E19" s="6">
+        <f>IF(F19="Sell",-C19*D19,C19*D19)</f>
+        <v>99.131200000000007</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="11">
+        <v>45903.479861111111</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2">
+        <v>121.82</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.41039999999999999</v>
+      </c>
+      <c r="E20" s="6">
+        <f>IF(F20="Sell",-C20*D20,C20*D20)</f>
+        <v>49.994927999999994</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
+        <v>45903.480555555558</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="2">
+        <v>111.61</v>
+      </c>
+      <c r="D21" s="6">
+        <v>8.9590000000000003E-2</v>
+      </c>
+      <c r="E21" s="6">
+        <f>IF(F21="Sell",-C21*D21,C21*D21)</f>
+        <v>9.9991398999999994</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="11">
+        <v>45903.493750000001</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="2">
+        <v>74.92</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0.40042</v>
+      </c>
+      <c r="E22" s="6">
+        <f>IF(F22="Sell",-C22*D22,C22*D22)</f>
+        <v>29.999466399999999</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="11">
+        <v>45903.494444444441</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1.42</v>
+      </c>
+      <c r="E23" s="6">
+        <f>IF(F23="Sell",-C23*D23,C23*D23)</f>
+        <v>24.849999999999998</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="11">
+        <v>45903.494444444441</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2">
+        <v>37.47</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="E24" s="6">
+        <f>IF(F24="Sell",-C24*D24,C24*D24)</f>
+        <v>49.835100000000004</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="11">
+        <v>45903.495138888888</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="2">
+        <v>13</v>
+      </c>
+      <c r="D25" s="6">
+        <v>1.53</v>
+      </c>
+      <c r="E25" s="6">
+        <f>IF(F25="Sell",-C25*D25,C25*D25)</f>
+        <v>19.89</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="11">
+        <v>45903.504861111112</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="2">
+        <v>158.88999999999999</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.12581000000000001</v>
+      </c>
+      <c r="E26" s="6">
+        <f>IF(F26="Sell",-C26*D26,C26*D26)</f>
+        <v>19.9899509</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
+        <v>45904.404861111114</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="2">
+        <v>49.57</v>
+      </c>
+      <c r="D27" s="6">
+        <v>1</v>
+      </c>
+      <c r="E27" s="6">
+        <f>IF(F27="Sell",-C27*D27,C27*D27)</f>
+        <v>49.57</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="11">
+        <v>45904.406944444447</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="2">
+        <v>8.94</v>
+      </c>
+      <c r="D28" s="6">
+        <v>3.35</v>
+      </c>
+      <c r="E28" s="6">
+        <f>IF(F28="Sell",-C28*D28,C28*D28)</f>
+        <v>29.948999999999998</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="11">
+        <v>45904.407638888886</v>
+      </c>
+      <c r="B29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="2">
+        <v>27.16</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0.92030000000000001</v>
+      </c>
+      <c r="E29" s="6">
+        <f>IF(F29="Sell",-C29*D29,C29*D29)</f>
+        <v>24.995348</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
+        <v>45904.412499999999</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="2">
+        <v>74.34</v>
+      </c>
+      <c r="D30" s="6">
+        <v>1.34</v>
+      </c>
+      <c r="E30" s="6">
+        <f>IF(F30="Sell",-C30*D30,C30*D30)</f>
+        <v>99.615600000000015</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11">
+        <v>45904.414583333331</v>
+      </c>
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="2">
+        <v>185.21</v>
+      </c>
+      <c r="D31" s="6">
+        <v>0.16197</v>
+      </c>
+      <c r="E31" s="6">
+        <f>IF(F31="Sell",-C31*D31,C31*D31)</f>
+        <v>29.998463700000002</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11">
+        <v>45904.418749999997</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="2">
+        <v>647.66</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0.15440000000000001</v>
+      </c>
+      <c r="E32" s="6">
+        <f>IF(F32="Sell",-C32*D32,C32*D32)</f>
+        <v>99.998704000000004</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11">
+        <v>45905.408333333333</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="2">
+        <v>6.65</v>
+      </c>
+      <c r="D33" s="6">
+        <v>2.25</v>
+      </c>
+      <c r="E33" s="6">
+        <f>IF(F33="Sell",-C33*D33,C33*D33)</f>
+        <v>14.9625</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
+        <v>45908.665277777778</v>
+      </c>
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="2">
+        <v>61.73</v>
+      </c>
+      <c r="D34" s="6">
+        <v>0.48430000000000001</v>
+      </c>
+      <c r="E34" s="6">
+        <f>IF(F34="Sell",-C34*D34,C34*D34)</f>
+        <v>-29.895838999999999</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="11">
+        <v>45909.415277777778</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="2">
+        <v>6.16</v>
+      </c>
+      <c r="D35" s="6">
+        <v>3</v>
+      </c>
+      <c r="E35" s="6">
+        <f>IF(F35="Sell",-C35*D35,C35*D35)</f>
+        <v>18.48</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="11">
+        <v>45909.418055555558</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2">
+        <v>32.69</v>
+      </c>
+      <c r="D36" s="6">
+        <v>0.38446000000000002</v>
+      </c>
+      <c r="E36" s="6">
+        <f>IF(F36="Sell",-C36*D36,C36*D36)</f>
+        <v>12.567997399999999</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="11">
+        <v>45909.427083333336</v>
+      </c>
+      <c r="B37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="2">
+        <v>72.319999999999993</v>
+      </c>
+      <c r="D37" s="6">
+        <v>1.38</v>
+      </c>
+      <c r="E37" s="6">
+        <f>IF(F37="Sell",-C37*D37,C37*D37)</f>
+        <v>99.801599999999979</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="11">
+        <v>45909.427777777775</v>
+      </c>
+      <c r="B38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2362.94</v>
+      </c>
+      <c r="D38" s="6">
+        <v>8.4499999999999992E-3</v>
+      </c>
+      <c r="E38" s="6">
+        <f>IF(F38="Sell",-C38*D38,C38*D38)</f>
+        <v>19.966842999999997</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="11">
+        <v>45909.431250000001</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="2">
+        <v>335.9</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1</v>
+      </c>
+      <c r="E39" s="6">
+        <f>IF(F39="Sell",-C39*D39,C39*D39)</f>
+        <v>335.9</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="11">
+        <v>45909.43472222222</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="2">
+        <v>648.80999999999995</v>
+      </c>
+      <c r="D40" s="6">
+        <v>0.46235999999999999</v>
+      </c>
+      <c r="E40" s="6">
+        <f>IF(F40="Sell",-C40*D40,C40*D40)</f>
+        <v>299.98379159999996</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="11">
+        <v>45909.439583333333</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="2">
+        <v>9.89</v>
+      </c>
+      <c r="D41" s="6">
+        <v>1.36</v>
+      </c>
+      <c r="E41" s="6">
+        <f>IF(F41="Sell",-C41*D41,C41*D41)</f>
+        <v>13.450400000000002</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="11">
+        <v>45909.589583333334</v>
+      </c>
+      <c r="B42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="2">
+        <v>579.97</v>
+      </c>
+      <c r="D42" s="6">
+        <v>0.17241999999999999</v>
+      </c>
+      <c r="E42" s="6">
+        <f>IF(F42="Sell",-C42*D42,C42*D42)</f>
+        <v>99.998427399999997</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="11">
+        <v>45910.459722222222</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="2">
+        <v>341.71</v>
+      </c>
+      <c r="D43" s="6">
+        <v>5.849E-2</v>
+      </c>
+      <c r="E43" s="6">
+        <f>IF(F43="Sell",-C43*D43,C43*D43)</f>
+        <v>19.986617899999999</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="11">
+        <v>45910.654166666667</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="2">
+        <v>5.69</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1.47</v>
+      </c>
+      <c r="E44" s="6">
+        <f>IF(F44="Sell",-C44*D44,C44*D44)</f>
+        <v>8.3643000000000001</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="11">
+        <v>45911.636805555558</v>
+      </c>
+      <c r="B45" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" s="2">
+        <v>308.70999999999998</v>
+      </c>
+      <c r="D45" s="6">
+        <v>5.849E-2</v>
+      </c>
+      <c r="E45" s="6">
+        <f>IF(F45="Sell",-C45*D45,C45*D45)</f>
+        <v>-18.056447899999998</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="11">
+        <v>45911.637499999997</v>
+      </c>
+      <c r="B46" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="2">
+        <v>73.36</v>
+      </c>
+      <c r="D46" s="6">
+        <v>1.38</v>
+      </c>
+      <c r="E46" s="6">
+        <f>IF(F46="Sell",-C46*D46,C46*D46)</f>
+        <v>-101.23679999999999</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="11">
+        <v>45912.396527777775</v>
+      </c>
+      <c r="B47" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="2">
+        <v>54.9</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1</v>
+      </c>
+      <c r="E47" s="6">
+        <f>IF(F47="Sell",-C47*D47,C47*D47)</f>
+        <v>54.9</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="11">
+        <v>45912.399305555555</v>
+      </c>
+      <c r="B48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C48" s="2">
+        <v>34.49</v>
+      </c>
+      <c r="D48" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="E48" s="6">
+        <f>IF(F48="Sell",-C48*D48,C48*D48)</f>
+        <v>13.796000000000001</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="11">
+        <v>45912.408333333333</v>
+      </c>
+      <c r="B49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" s="2">
+        <v>42.99</v>
+      </c>
+      <c r="D49" s="6">
+        <v>1</v>
+      </c>
+      <c r="E49" s="6">
+        <f>IF(F49="Sell",-C49*D49,C49*D49)</f>
+        <v>42.99</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="11">
+        <v>45912.414583333331</v>
+      </c>
+      <c r="B50" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50" s="2">
+        <v>37.74</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="E50" s="6">
+        <f>IF(F50="Sell",-C50*D50,C50*D50)</f>
+        <v>6.0384000000000002</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="11">
+        <v>45923.460416666669</v>
+      </c>
+      <c r="B51" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="2">
+        <v>68.19</v>
+      </c>
+      <c r="D51" s="6">
+        <v>1</v>
+      </c>
+      <c r="E51" s="6">
+        <f>IF(F51="Sell",-C51*D51,C51*D51)</f>
+        <v>68.19</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="11">
+        <v>45923.463194444441</v>
+      </c>
+      <c r="B52" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="2">
+        <v>251.48</v>
+      </c>
+      <c r="D52" s="6">
+        <v>0.58055999999999996</v>
+      </c>
+      <c r="E52" s="6">
+        <f>IF(F52="Sell",-C52*D52,C52*D52)</f>
+        <v>145.9992288</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="11">
+        <v>45923.489583333336</v>
+      </c>
+      <c r="B53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C53" s="2">
+        <v>170.43</v>
+      </c>
+      <c r="D53" s="6">
+        <v>1</v>
+      </c>
+      <c r="E53" s="6">
+        <f>IF(F53="Sell",-C53*D53,C53*D53)</f>
+        <v>170.43</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="11">
+        <v>45923.515972222223</v>
+      </c>
+      <c r="B54" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="2">
+        <v>765.72</v>
+      </c>
+      <c r="D54" s="6">
+        <v>0.10446999999999999</v>
+      </c>
+      <c r="E54" s="6">
+        <f>IF(F54="Sell",-C54*D54,C54*D54)</f>
+        <v>79.994768399999998</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="11">
+        <v>45923.517361111109</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="2">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="D55" s="6">
+        <v>4.45</v>
+      </c>
+      <c r="E55" s="6">
+        <f>IF(F55="Sell",-C55*D55,C55*D55)</f>
+        <v>35.733499999999999</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="11">
+        <v>45924.42291666667</v>
+      </c>
+      <c r="B56" t="s">
+        <v>37</v>
+      </c>
+      <c r="C56" s="2">
+        <v>666.18</v>
+      </c>
+      <c r="D56" s="6">
+        <v>0.15473000000000001</v>
+      </c>
+      <c r="E56" s="6">
+        <f>IF(F56="Sell",-C56*D56,C56*D56)</f>
+        <v>-103.0780314</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="11">
+        <v>45924.423611111109</v>
+      </c>
+      <c r="B57" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" s="2">
+        <v>48.95</v>
+      </c>
+      <c r="D57" s="6">
+        <v>1</v>
+      </c>
+      <c r="E57" s="6">
+        <f>IF(F57="Sell",-C57*D57,C57*D57)</f>
+        <v>-48.95</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="11">
+        <v>45924.423611111109</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" s="2">
+        <v>121.43</v>
+      </c>
+      <c r="D58" s="6">
+        <v>0.41039999999999999</v>
+      </c>
+      <c r="E58" s="6">
+        <f>IF(F58="Sell",-C58*D58,C58*D58)</f>
+        <v>-49.834872000000004</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="11">
+        <v>45929.46875</v>
+      </c>
+      <c r="B59" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" s="2">
+        <v>327</v>
+      </c>
+      <c r="D59" s="6">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="E59" s="6">
+        <f>IF(F59="Sell",-C59*D59,C59*D59)</f>
+        <v>202.08599999999998</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="11">
+        <v>45937.396527777775</v>
+      </c>
+      <c r="B60" t="s">
+        <v>48</v>
+      </c>
+      <c r="C60" s="2">
+        <v>61.27</v>
+      </c>
+      <c r="D60" s="6">
+        <v>1</v>
+      </c>
+      <c r="E60" s="6">
+        <f>IF(F60="Sell",-C60*D60,C60*D60)</f>
+        <v>61.27</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>45937.398611111108</v>
+      </c>
+      <c r="B61" t="s">
+        <v>34</v>
+      </c>
+      <c r="C61" s="2">
+        <v>33.94</v>
+      </c>
+      <c r="D61" s="6">
+        <v>2</v>
+      </c>
+      <c r="E61" s="6">
+        <f>IF(F61="Sell",-C61*D61,C61*D61)</f>
+        <v>67.88</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="11">
+        <v>45937.4</v>
+      </c>
+      <c r="B62" t="s">
+        <v>33</v>
+      </c>
+      <c r="C62" s="2">
+        <v>12.39</v>
+      </c>
+      <c r="D62" s="6">
+        <v>4</v>
+      </c>
+      <c r="E62" s="6">
+        <f>IF(F62="Sell",-C62*D62,C62*D62)</f>
+        <v>49.56</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="11">
+        <v>45937.40625</v>
+      </c>
+      <c r="B63" t="s">
+        <v>49</v>
+      </c>
+      <c r="C63" s="2">
+        <v>5.32</v>
+      </c>
+      <c r="D63" s="6">
+        <v>5</v>
+      </c>
+      <c r="E63" s="6">
+        <f>IF(F63="Sell",-C63*D63,C63*D63)</f>
+        <v>26.6</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="11">
+        <v>45937.462500000001</v>
+      </c>
+      <c r="B64" t="s">
+        <v>50</v>
+      </c>
+      <c r="C64" s="2">
+        <v>57.48</v>
+      </c>
+      <c r="D64" s="6">
+        <v>2</v>
+      </c>
+      <c r="E64" s="6">
+        <f>IF(F64="Sell",-C64*D64,C64*D64)</f>
+        <v>114.96</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="11">
+        <v>45937.465277777781</v>
+      </c>
+      <c r="B65" t="s">
+        <v>42</v>
+      </c>
+      <c r="C65" s="2">
+        <v>604.97</v>
+      </c>
+      <c r="D65" s="6">
+        <v>0.12198000000000001</v>
+      </c>
+      <c r="E65" s="6">
+        <f>IF(F65="Sell",-C65*D65,C65*D65)</f>
+        <v>73.794240600000009</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="11">
+        <v>45938.413194444445</v>
+      </c>
+      <c r="B66" t="s">
+        <v>50</v>
+      </c>
+      <c r="C66" s="2">
+        <v>59.34</v>
+      </c>
+      <c r="D66" s="6">
+        <v>2</v>
+      </c>
+      <c r="E66" s="6">
+        <f>IF(F66="Sell",-C66*D66,C66*D66)</f>
+        <v>-118.68</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="11">
+        <v>45939.417361111111</v>
+      </c>
+      <c r="B67" t="s">
+        <v>51</v>
+      </c>
+      <c r="C67" s="2">
+        <v>124.22</v>
+      </c>
+      <c r="D67" s="6">
+        <v>0.95403000000000004</v>
+      </c>
+      <c r="E67" s="6">
+        <f>IF(F67="Sell",-C67*D67,C67*D67)</f>
+        <v>118.5096066</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="11">
+        <v>45943.410416666666</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" s="2">
+        <v>112.2</v>
+      </c>
+      <c r="D68" s="6">
+        <v>9.0120000000000006E-2</v>
+      </c>
+      <c r="E68" s="6">
+        <f>IF(F68="Sell",-C68*D68,C68*D68)</f>
+        <v>-10.111464000000002</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="11">
+        <v>45943.411805555559</v>
+      </c>
+      <c r="B69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" s="2">
+        <v>246.88</v>
+      </c>
+      <c r="D69" s="6">
+        <v>8.4540000000000004E-2</v>
+      </c>
+      <c r="E69" s="6">
+        <f>IF(F69="Sell",-C69*D69,C69*D69)</f>
+        <v>-20.871235200000001</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="11">
+        <v>45943.412499999999</v>
+      </c>
+      <c r="B70" t="s">
+        <v>28</v>
+      </c>
+      <c r="C70" s="2">
+        <v>17.309999999999999</v>
+      </c>
+      <c r="D70" s="6">
+        <v>1.42</v>
+      </c>
+      <c r="E70" s="6">
+        <f>IF(F70="Sell",-C70*D70,C70*D70)</f>
+        <v>-24.580199999999998</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="11">
+        <v>45943.413194444445</v>
+      </c>
+      <c r="B71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="2">
+        <v>128.91</v>
+      </c>
+      <c r="D71" s="6">
+        <v>0.37919000000000003</v>
+      </c>
+      <c r="E71" s="6">
+        <f>IF(F71="Sell",-C71*D71,C71*D71)</f>
+        <v>-48.881382900000006</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="11">
+        <v>45943.415277777778</v>
+      </c>
+      <c r="B72" t="s">
+        <v>36</v>
+      </c>
+      <c r="C72" s="2">
+        <v>183.36</v>
+      </c>
+      <c r="D72" s="6">
+        <v>0.16197</v>
+      </c>
+      <c r="E72" s="6">
+        <f>IF(F72="Sell",-C72*D72,C72*D72)</f>
+        <v>-29.698819200000003</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="11">
+        <v>45943.417361111111</v>
+      </c>
+      <c r="B73" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73" s="2">
+        <v>70.52</v>
+      </c>
+      <c r="D73" s="6">
+        <v>0.40042</v>
+      </c>
+      <c r="E73" s="6">
+        <f>IF(F73="Sell",-C73*D73,C73*D73)</f>
+        <v>-28.237618399999999</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="11">
+        <v>45946.399305555555</v>
+      </c>
+      <c r="B74" t="s">
+        <v>52</v>
+      </c>
+      <c r="C74" s="2">
+        <v>41.11</v>
+      </c>
+      <c r="D74" s="6">
+        <v>3.93</v>
+      </c>
+      <c r="E74" s="6">
+        <f>IF(F74="Sell",-C74*D74,C74*D74)</f>
+        <v>161.56229999999999</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="11">
+        <v>45957.457638888889</v>
+      </c>
+      <c r="B75" t="s">
+        <v>47</v>
+      </c>
+      <c r="C75" s="2">
+        <v>192.61</v>
+      </c>
+      <c r="D75" s="6">
+        <v>1</v>
+      </c>
+      <c r="E75" s="6">
+        <f>IF(F75="Sell",-C75*D75,C75*D75)</f>
+        <v>-192.61</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="11">
+        <v>45957.459722222222</v>
+      </c>
+      <c r="B76" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" s="2">
+        <v>10.29</v>
+      </c>
+      <c r="D76" s="6">
+        <v>6.83</v>
+      </c>
+      <c r="E76" s="6">
+        <f>IF(F76="Sell",-C76*D76,C76*D76)</f>
+        <v>-70.280699999999996</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="11">
+        <v>45957.460416666669</v>
+      </c>
+      <c r="B77" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" s="2">
+        <v>12.12</v>
+      </c>
+      <c r="D77" s="6">
+        <v>7.35</v>
+      </c>
+      <c r="E77" s="6">
+        <f>IF(F77="Sell",-C77*D77,C77*D77)</f>
+        <v>-89.081999999999994</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="11">
+        <v>45957.462500000001</v>
+      </c>
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="2">
+        <v>365.94</v>
+      </c>
+      <c r="D78" s="6">
+        <v>1.76</v>
+      </c>
+      <c r="E78" s="6">
+        <f>IF(F78="Sell",-C78*D78,C78*D78)</f>
+        <v>-644.05439999999999</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="11">
+        <v>45957.463194444441</v>
+      </c>
+      <c r="B79" t="s">
+        <v>51</v>
+      </c>
+      <c r="C79" s="2">
+        <v>122.97</v>
+      </c>
+      <c r="D79" s="6">
+        <v>0.95403000000000004</v>
+      </c>
+      <c r="E79" s="6">
+        <f>IF(F79="Sell",-C79*D79,C79*D79)</f>
+        <v>-117.3170691</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="11">
+        <v>45957.463888888888</v>
+      </c>
+      <c r="B80" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" s="2">
+        <v>41.78</v>
+      </c>
+      <c r="D80" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="E80" s="6">
+        <f>IF(F80="Sell",-C80*D80,C80*D80)</f>
+        <v>-55.567400000000006</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="11">
+        <v>45957.464583333334</v>
+      </c>
+      <c r="B81" t="s">
+        <v>30</v>
+      </c>
+      <c r="C81" s="2">
+        <v>12.92</v>
+      </c>
+      <c r="D81" s="6">
+        <v>1.53</v>
+      </c>
+      <c r="E81" s="6">
+        <f>IF(F81="Sell",-C81*D81,C81*D81)</f>
+        <v>-19.767600000000002</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="11">
+        <v>45957.464583333334</v>
+      </c>
+      <c r="B82" t="s">
+        <v>40</v>
+      </c>
+      <c r="C82" s="2">
+        <v>2277.38</v>
+      </c>
+      <c r="D82" s="6">
+        <v>8.4499999999999992E-3</v>
+      </c>
+      <c r="E82" s="6">
+        <f>IF(F82="Sell",-C82*D82,C82*D82)</f>
+        <v>-19.243860999999999</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="11">
+        <v>45957.470833333333</v>
+      </c>
+      <c r="B83" t="s">
+        <v>14</v>
+      </c>
+      <c r="C83" s="2">
+        <v>52.74</v>
+      </c>
+      <c r="D83" s="6">
+        <v>0.44206000000000001</v>
+      </c>
+      <c r="E83" s="6">
+        <f>IF(F83="Sell",-C83*D83,C83*D83)</f>
+        <v>-23.3142444</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="11">
+        <v>45957.470833333333</v>
+      </c>
+      <c r="B84" t="s">
+        <v>49</v>
+      </c>
+      <c r="C84" s="2">
+        <v>4.84</v>
+      </c>
+      <c r="D84" s="6">
+        <v>5</v>
+      </c>
+      <c r="E84" s="6">
+        <f>IF(F84="Sell",-C84*D84,C84*D84)</f>
+        <v>-24.2</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="11">
+        <v>45957.47152777778</v>
+      </c>
+      <c r="B85" t="s">
+        <v>44</v>
+      </c>
+      <c r="C85" s="2">
+        <v>52.95</v>
+      </c>
+      <c r="D85" s="6">
+        <v>1</v>
+      </c>
+      <c r="E85" s="6">
+        <f>IF(F85="Sell",-C85*D85,C85*D85)</f>
+        <v>-52.95</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="11">
+        <v>45958.512499999997</v>
+      </c>
+      <c r="B86" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86" s="2">
+        <v>541.79</v>
+      </c>
+      <c r="D86" s="6">
+        <v>0.96050999999999997</v>
+      </c>
+      <c r="E86" s="6">
+        <f>IF(F86="Sell",-C86*D86,C86*D86)</f>
+        <v>520.39471289999994</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="11">
+        <v>45958.515277777777</v>
+      </c>
+      <c r="B87" t="s">
+        <v>35</v>
+      </c>
+      <c r="C87" s="2">
+        <v>89.79</v>
+      </c>
+      <c r="D87" s="6">
+        <v>2.65</v>
+      </c>
+      <c r="E87" s="6">
+        <f>IF(F87="Sell",-C87*D87,C87*D87)</f>
+        <v>237.9435</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="11">
+        <v>45958.517361111109</v>
+      </c>
+      <c r="B88" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" s="2">
+        <v>266.82</v>
+      </c>
+      <c r="D88" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="E88" s="6">
+        <f>IF(F88="Sell",-C88*D88,C88*D88)</f>
+        <v>320.18399999999997</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="11">
+        <v>45958.520138888889</v>
+      </c>
+      <c r="B89" t="s">
+        <v>31</v>
+      </c>
+      <c r="C89" s="2">
+        <v>188.92</v>
+      </c>
+      <c r="D89" s="6">
+        <v>0.12581000000000001</v>
+      </c>
+      <c r="E89" s="6">
+        <f>IF(F89="Sell",-C89*D89,C89*D89)</f>
+        <v>-23.7680252</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="11">
+        <v>45958.522222222222</v>
+      </c>
+      <c r="B90" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" s="2">
+        <v>465.39</v>
+      </c>
+      <c r="D90" s="6">
+        <v>5.8790000000000002E-2</v>
+      </c>
+      <c r="E90" s="6">
+        <f>IF(F90="Sell",-C90*D90,C90*D90)</f>
+        <v>-27.360278099999999</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="11">
+        <v>45958.522222222222</v>
+      </c>
+      <c r="B91" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" s="2">
+        <v>51.12</v>
+      </c>
+      <c r="D91" s="6">
+        <v>0.55984</v>
+      </c>
+      <c r="E91" s="6">
+        <f>IF(F91="Sell",-C91*D91,C91*D91)</f>
+        <v>-28.619020799999998</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="11">
+        <v>45958.529166666667</v>
+      </c>
+      <c r="B92" t="s">
+        <v>53</v>
+      </c>
+      <c r="C92" s="2">
+        <v>55.54</v>
+      </c>
+      <c r="D92" s="6">
+        <v>3</v>
+      </c>
+      <c r="E92" s="6">
+        <f>IF(F92="Sell",-C92*D92,C92*D92)</f>
+        <v>166.62</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="11">
+        <v>45965.642361111109</v>
+      </c>
+      <c r="B93" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="2">
+        <v>57.69</v>
+      </c>
+      <c r="D93" s="6">
+        <v>1.84</v>
+      </c>
+      <c r="E93" s="6">
+        <f>IF(F93="Sell",-C93*D93,C93*D93)</f>
+        <v>106.14960000000001</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="11">
+        <v>45974.67291666667</v>
+      </c>
+      <c r="B94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="2">
+        <v>55.85</v>
+      </c>
+      <c r="D94" s="6">
+        <v>0.69955000000000001</v>
+      </c>
+      <c r="E94" s="6">
+        <f>IF(F94="Sell",-C94*D94,C94*D94)</f>
+        <v>39.069867500000001</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="11">
+        <v>46002.439583333333</v>
+      </c>
+      <c r="B95" t="s">
+        <v>34</v>
+      </c>
+      <c r="C95" s="2">
+        <v>41.27</v>
+      </c>
+      <c r="D95" s="6">
+        <v>2.08</v>
+      </c>
+      <c r="E95" s="6">
+        <f>IF(F95="Sell",-C95*D95,C95*D95)</f>
+        <v>85.841600000000014</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="11">
+        <v>46002.442361111112</v>
+      </c>
+      <c r="B96" t="s">
+        <v>12</v>
+      </c>
+      <c r="C96" s="2">
+        <v>685.2</v>
+      </c>
+      <c r="D96" s="6">
+        <v>0.72970000000000002</v>
+      </c>
+      <c r="E96" s="6">
+        <f>IF(F96="Sell",-C96*D96,C96*D96)</f>
+        <v>499.99044000000004</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="11">
+        <v>46002.443749999999</v>
+      </c>
+      <c r="B97" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="2">
+        <v>51.34</v>
+      </c>
+      <c r="D97" s="6">
+        <v>2.41</v>
+      </c>
+      <c r="E97" s="6">
+        <f>IF(F97="Sell",-C97*D97,C97*D97)</f>
+        <v>123.72940000000001</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="11">
+        <v>46002.446527777778</v>
+      </c>
+      <c r="B98" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" s="2">
+        <v>24.08</v>
+      </c>
+      <c r="D98" s="6">
+        <v>6.77</v>
+      </c>
+      <c r="E98" s="6">
+        <f>IF(F98="Sell",-C98*D98,C98*D98)</f>
+        <v>163.02159999999998</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="11">
+        <v>46008.648611111108</v>
+      </c>
+      <c r="B99" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" s="2">
+        <v>21.11</v>
+      </c>
+      <c r="D99" s="6">
+        <v>2</v>
+      </c>
+      <c r="E99" s="6">
+        <f>IF(F99="Sell",-C99*D99,C99*D99)</f>
+        <v>42.22</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="11">
+        <v>46008.650694444441</v>
+      </c>
+      <c r="B100" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="2">
+        <v>48.49</v>
+      </c>
+      <c r="D100" s="6">
+        <v>1.79</v>
+      </c>
+      <c r="E100" s="6">
+        <f>IF(F100="Sell",-C100*D100,C100*D100)</f>
+        <v>86.7971</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="11">
+        <v>46020.463888888888</v>
+      </c>
+      <c r="B101" t="s">
+        <v>46</v>
+      </c>
+      <c r="C101" s="2">
+        <v>59.54</v>
+      </c>
+      <c r="D101" s="6">
+        <v>1</v>
+      </c>
+      <c r="E101" s="6">
+        <f>IF(F101="Sell",-C101*D101,C101*D101)</f>
+        <v>-59.54</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="11">
+        <v>46021.472916666666</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" s="2">
+        <v>5.69</v>
+      </c>
+      <c r="D102" s="6">
+        <v>9.9</v>
+      </c>
+      <c r="E102" s="6">
+        <f>IF(F102="Sell",-C102*D102,C102*D102)</f>
+        <v>56.331000000000003</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="11">
+        <v>46027.567361111112</v>
+      </c>
+      <c r="B103" t="s">
+        <v>45</v>
+      </c>
+      <c r="C103" s="2">
+        <v>11.24</v>
+      </c>
+      <c r="D103" s="6">
+        <v>1.56</v>
+      </c>
+      <c r="E103" s="6">
+        <f>IF(F103="Sell",-C103*D103,C103*D103)</f>
+        <v>-17.534400000000002</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="11">
+        <v>46027.568055555559</v>
+      </c>
+      <c r="B104" t="s">
+        <v>22</v>
+      </c>
+      <c r="C104" s="2">
+        <v>233.54</v>
+      </c>
+      <c r="D104" s="6">
+        <v>0.13278000000000001</v>
+      </c>
+      <c r="E104" s="6">
+        <f>IF(F104="Sell",-C104*D104,C104*D104)</f>
+        <v>-31.009441200000001</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="11">
+        <v>46027.568749999999</v>
+      </c>
+      <c r="B105" t="s">
+        <v>48</v>
+      </c>
+      <c r="C105" s="2">
+        <v>36.83</v>
+      </c>
+      <c r="D105" s="6">
+        <v>1</v>
+      </c>
+      <c r="E105" s="6">
+        <f>IF(F105="Sell",-C105*D105,C105*D105)</f>
+        <v>-36.83</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="11">
+        <v>46029.449305555558</v>
+      </c>
+      <c r="B106" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" s="2">
+        <v>100.39</v>
+      </c>
+      <c r="D106" s="6">
+        <v>1.07</v>
+      </c>
+      <c r="E106" s="6">
+        <f>IF(F106="Sell",-C106*D106,C106*D106)</f>
+        <v>-107.41730000000001</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="11">
+        <v>46034.47152777778</v>
+      </c>
+      <c r="B107" t="s">
+        <v>42</v>
+      </c>
+      <c r="C107" s="2">
+        <v>625.9</v>
+      </c>
+      <c r="D107" s="6">
+        <v>0.29479</v>
+      </c>
+      <c r="E107" s="6">
+        <f>IF(F107="Sell",-C107*D107,C107*D107)</f>
+        <v>-184.509061</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="11">
+        <v>46034.47152777778</v>
+      </c>
+      <c r="B108" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" s="2">
+        <v>342</v>
+      </c>
+      <c r="D108" s="6">
+        <v>1.25</v>
+      </c>
+      <c r="E108" s="6">
+        <f>IF(F108="Sell",-C108*D108,C108*D108)</f>
+        <v>-427.5</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="11">
+        <v>46035.44027777778</v>
+      </c>
+      <c r="B109" t="s">
+        <v>34</v>
+      </c>
+      <c r="C109" s="2">
+        <v>49.47</v>
+      </c>
+      <c r="D109" s="6">
+        <v>5.29</v>
+      </c>
+      <c r="E109" s="6">
+        <f>IF(F109="Sell",-C109*D109,C109*D109)</f>
+        <v>261.69630000000001</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="11">
+        <v>46035.441666666666</v>
+      </c>
+      <c r="B110" t="s">
+        <v>52</v>
+      </c>
+      <c r="C110" s="2">
+        <v>56.67</v>
+      </c>
+      <c r="D110" s="6">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="E110" s="6">
+        <f>IF(F110="Sell",-C110*D110,C110*D110)</f>
+        <v>275.4162</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="11">
+        <v>46036.448611111111</v>
+      </c>
+      <c r="B111" t="s">
+        <v>54</v>
+      </c>
+      <c r="C111" s="2">
+        <v>183.13</v>
+      </c>
+      <c r="D111" s="6">
+        <v>1.47</v>
+      </c>
+      <c r="E111" s="6">
+        <f>IF(F111="Sell",-C111*D111,C111*D111)</f>
+        <v>269.2011</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="11">
+        <v>46042.44027777778</v>
+      </c>
+      <c r="B112" t="s">
+        <v>33</v>
+      </c>
+      <c r="C112" s="2">
+        <v>27.75</v>
+      </c>
+      <c r="D112" s="6">
+        <v>10.81</v>
+      </c>
+      <c r="E112" s="6">
+        <f>IF(F112="Sell",-C112*D112,C112*D112)</f>
+        <v>299.97750000000002</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="11">
+        <v>46042.441666666666</v>
+      </c>
+      <c r="B113" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" s="2">
+        <v>14.93</v>
+      </c>
+      <c r="D113" s="6">
+        <v>20.09</v>
+      </c>
+      <c r="E113" s="6">
+        <f>IF(F113="Sell",-C113*D113,C113*D113)</f>
+        <v>299.94369999999998</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="11">
+        <v>46042.45</v>
+      </c>
+      <c r="B114" t="s">
+        <v>55</v>
+      </c>
+      <c r="C114" s="2">
+        <v>376.93</v>
+      </c>
+      <c r="D114" s="6">
+        <v>1</v>
+      </c>
+      <c r="E114" s="6">
+        <f>IF(F114="Sell",-C114*D114,C114*D114)</f>
+        <v>376.93</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="11">
+        <v>46044.496527777781</v>
+      </c>
+      <c r="B115" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="2">
+        <v>50.4</v>
+      </c>
+      <c r="D115" s="6">
+        <v>9.9</v>
+      </c>
+      <c r="E115" s="6">
+        <f>IF(F115="Sell",-C115*D115,C115*D115)</f>
+        <v>-498.96</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="11">
+        <v>46044.49722222222</v>
+      </c>
+      <c r="B116" t="s">
+        <v>8</v>
+      </c>
+      <c r="C116" s="2">
+        <v>22.18</v>
+      </c>
+      <c r="D116" s="6">
+        <v>15.11</v>
+      </c>
+      <c r="E116" s="6">
+        <f>IF(F116="Sell",-C116*D116,C116*D116)</f>
+        <v>-335.13979999999998</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="11">
+        <v>46045.445833333331</v>
+      </c>
+      <c r="B117" t="s">
+        <v>56</v>
+      </c>
+      <c r="C117" s="2">
+        <v>70</v>
+      </c>
+      <c r="D117" s="6">
+        <v>5.71</v>
+      </c>
+      <c r="E117" s="6">
+        <f>IF(F117="Sell",-C117*D117,C117*D117)</f>
+        <v>399.7</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="11">
+        <v>46045.493055555555</v>
+      </c>
+      <c r="B118" t="s">
+        <v>19</v>
+      </c>
+      <c r="C118" s="2">
+        <v>659.79</v>
+      </c>
+      <c r="D118" s="6">
+        <v>0.78064</v>
+      </c>
+      <c r="E118" s="6">
+        <f>IF(F118="Sell",-C118*D118,C118*D118)</f>
+        <v>515.05846559999998</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="11">
+        <v>46048.572222222225</v>
+      </c>
+      <c r="B119" t="s">
+        <v>35</v>
+      </c>
+      <c r="C119" s="2">
+        <v>80.680000000000007</v>
+      </c>
+      <c r="D119" s="6">
+        <v>4</v>
+      </c>
+      <c r="E119" s="6">
+        <f>IF(F119="Sell",-C119*D119,C119*D119)</f>
+        <v>-322.72000000000003</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="11">
+        <v>46049.448611111111</v>
+      </c>
+      <c r="B120" t="s">
+        <v>57</v>
+      </c>
+      <c r="C120" s="2">
+        <v>89.38</v>
+      </c>
+      <c r="D120" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="E120" s="6">
+        <f>IF(F120="Sell",-C120*D120,C120*D120)</f>
+        <v>321.76799999999997</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="11">
+        <v>46050.563888888886</v>
+      </c>
+      <c r="B121" t="s">
+        <v>54</v>
+      </c>
+      <c r="C121" s="2">
+        <v>159.22999999999999</v>
+      </c>
+      <c r="D121" s="6">
+        <v>1.47</v>
+      </c>
+      <c r="E121" s="6">
+        <f>IF(F121="Sell",-C121*D121,C121*D121)</f>
+        <v>-234.06809999999999</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="11">
+        <v>46055.650694444441</v>
+      </c>
+      <c r="B122" t="s">
+        <v>19</v>
+      </c>
+      <c r="C122" s="2">
+        <v>711.77</v>
+      </c>
+      <c r="D122" s="6">
+        <v>0.91229000000000005</v>
+      </c>
+      <c r="E122" s="6">
+        <f>IF(F122="Sell",-C122*D122,C122*D122)</f>
+        <v>-649.34065329999999</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="11">
+        <v>46055.652083333334</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" s="2">
+        <v>4.96</v>
+      </c>
+      <c r="D123" s="6">
+        <v>47.2</v>
+      </c>
+      <c r="E123" s="6">
+        <f>IF(F123="Sell",-C123*D123,C123*D123)</f>
+        <v>234.11200000000002</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="11">
+        <v>46059.484722222223</v>
+      </c>
+      <c r="B124" t="s">
+        <v>53</v>
+      </c>
+      <c r="C124" s="2">
+        <v>59.58</v>
+      </c>
+      <c r="D124" s="6">
+        <v>10.89</v>
+      </c>
+      <c r="E124" s="6">
+        <f>IF(F124="Sell",-C124*D124,C124*D124)</f>
+        <v>648.82619999999997</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="11">
+        <v>46083.456250000003</v>
+      </c>
+      <c r="B125" t="s">
+        <v>58</v>
+      </c>
+      <c r="C125" s="2">
+        <v>160.21</v>
+      </c>
+      <c r="D125" s="6">
+        <v>3</v>
+      </c>
+      <c r="E125" s="6">
+        <f>IF(F125="Sell",-C125*D125,C125*D125)</f>
+        <v>480.63</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="11">
+        <v>46086.664583333331</v>
+      </c>
+      <c r="B126" t="s">
+        <v>27</v>
+      </c>
+      <c r="C126" s="2">
+        <v>98.34</v>
+      </c>
+      <c r="D126" s="6">
+        <v>1.77</v>
+      </c>
+      <c r="E126" s="6">
+        <f>IF(F126="Sell",-C126*D126,C126*D126)</f>
+        <v>174.06180000000001</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="11">
+        <v>46087.525000000001</v>
+      </c>
+      <c r="B127" t="s">
+        <v>33</v>
+      </c>
+      <c r="C127" s="2">
+        <v>20.58</v>
+      </c>
+      <c r="D127" s="6">
+        <v>10.81</v>
+      </c>
+      <c r="E127" s="6">
+        <f>IF(F127="Sell",-C127*D127,C127*D127)</f>
+        <v>-222.46979999999999</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="11">
+        <v>46087.525694444441</v>
+      </c>
+      <c r="B128" t="s">
+        <v>57</v>
+      </c>
+      <c r="C128" s="2">
+        <v>80.78</v>
+      </c>
+      <c r="D128" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="E128" s="6">
+        <f>IF(F128="Sell",-C128*D128,C128*D128)</f>
+        <v>-290.80799999999999</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="11">
+        <v>46087.526388888888</v>
+      </c>
+      <c r="B129" t="s">
+        <v>56</v>
+      </c>
+      <c r="C129" s="2">
+        <v>81.02</v>
+      </c>
+      <c r="D129" s="6">
+        <v>5.71</v>
+      </c>
+      <c r="E129" s="6">
+        <f>IF(F129="Sell",-C129*D129,C129*D129)</f>
+        <v>-462.62419999999997</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="11">
+        <v>46087.527777777781</v>
+      </c>
+      <c r="B130" t="s">
+        <v>52</v>
+      </c>
+      <c r="C130" s="2">
+        <v>59.68</v>
+      </c>
+      <c r="D130" s="6">
+        <v>8.81</v>
+      </c>
+      <c r="E130" s="6">
+        <f>IF(F130="Sell",-C130*D130,C130*D130)</f>
+        <v>-525.7808</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="11">
+        <v>46087.52847222222</v>
+      </c>
+      <c r="B131" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" s="2">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="D131" s="6">
+        <v>20.09</v>
+      </c>
+      <c r="E131" s="6">
+        <f>IF(F131="Sell",-C131*D131,C131*D131)</f>
+        <v>-333.09219999999999</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="11">
+        <v>46087.52847222222</v>
+      </c>
+      <c r="B132" t="s">
+        <v>34</v>
+      </c>
+      <c r="C132" s="2">
+        <v>45.39</v>
+      </c>
+      <c r="D132" s="6">
+        <v>10.29</v>
+      </c>
+      <c r="E132" s="6">
+        <f>IF(F132="Sell",-C132*D132,C132*D132)</f>
+        <v>-467.06309999999996</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="11">
+        <v>46087.529166666667</v>
+      </c>
+      <c r="B133" t="s">
+        <v>21</v>
+      </c>
+      <c r="C133" s="2">
+        <v>299.41000000000003</v>
+      </c>
+      <c r="D133" s="6">
+        <v>2</v>
+      </c>
+      <c r="E133" s="6">
+        <f>IF(F133="Sell",-C133*D133,C133*D133)</f>
+        <v>-598.82000000000005</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="11">
+        <v>46090.397916666669</v>
+      </c>
+      <c r="B134" t="s">
+        <v>53</v>
+      </c>
+      <c r="C134" s="2">
+        <v>56.81</v>
+      </c>
+      <c r="D134" s="6">
+        <v>13.92</v>
+      </c>
+      <c r="E134" s="6">
+        <f>IF(F134="Sell",-C134*D134,C134*D134)</f>
+        <v>-790.79520000000002</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="11">
+        <v>46090.400000000001</v>
+      </c>
+      <c r="B135" t="s">
+        <v>27</v>
+      </c>
+      <c r="C135" s="2">
+        <v>116.49</v>
+      </c>
+      <c r="D135" s="6">
+        <v>6.76</v>
+      </c>
+      <c r="E135" s="6">
+        <f>IF(F135="Sell",-C135*D135,C135*D135)</f>
+        <v>787.47239999999999</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="11">
+        <v>46090.401388888888</v>
+      </c>
+      <c r="B136" t="s">
+        <v>60</v>
+      </c>
+      <c r="C136" s="2">
+        <v>37.89</v>
+      </c>
+      <c r="D136" s="6">
+        <v>13.19</v>
+      </c>
+      <c r="E136" s="6">
+        <f>IF(F136="Sell",-C136*D136,C136*D136)</f>
+        <v>499.76909999999998</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="11">
+        <v>46090.402083333334</v>
+      </c>
+      <c r="B137" t="s">
+        <v>59</v>
+      </c>
+      <c r="C137" s="2">
+        <v>63.36</v>
+      </c>
+      <c r="D137" s="6">
+        <v>7.89</v>
+      </c>
+      <c r="E137" s="6">
+        <f>IF(F137="Sell",-C137*D137,C137*D137)</f>
+        <v>499.91039999999998</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="11">
+        <v>46090.65347222222</v>
+      </c>
+      <c r="B138" t="s">
+        <v>12</v>
+      </c>
+      <c r="C138" s="2">
+        <v>677.47</v>
+      </c>
+      <c r="D138" s="6">
+        <v>1.64</v>
+      </c>
+      <c r="E138" s="6">
+        <f>IF(F138="Sell",-C138*D138,C138*D138)</f>
+        <v>1111.0508</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="11">
+        <v>46091.431944444441</v>
+      </c>
+      <c r="B139" t="s">
+        <v>58</v>
+      </c>
+      <c r="C139" s="2">
+        <v>158.78</v>
+      </c>
+      <c r="D139" s="6">
+        <v>3</v>
+      </c>
+      <c r="E139" s="6">
+        <f>IF(F139="Sell",-C139*D139,C139*D139)</f>
+        <v>-476.34000000000003</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="11">
+        <v>46091.434027777781</v>
+      </c>
+      <c r="B140" t="s">
+        <v>60</v>
+      </c>
+      <c r="C140" s="2">
+        <v>37.1</v>
+      </c>
+      <c r="D140" s="6">
+        <v>13.19</v>
+      </c>
+      <c r="E140" s="6">
+        <f>IF(F140="Sell",-C140*D140,C140*D140)</f>
+        <v>-489.34899999999999</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="11">
+        <v>46091.436805555553</v>
+      </c>
+      <c r="B141" t="s">
+        <v>55</v>
+      </c>
+      <c r="C141" s="2">
+        <v>410</v>
+      </c>
+      <c r="D141" s="6">
+        <v>1.43</v>
+      </c>
+      <c r="E141" s="6">
+        <f>IF(F141="Sell",-C141*D141,C141*D141)</f>
+        <v>586.29999999999995</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="11">
+        <v>46091.449305555558</v>
+      </c>
+      <c r="B142" t="s">
+        <v>61</v>
+      </c>
+      <c r="C142" s="2">
+        <v>90.02</v>
+      </c>
+      <c r="D142" s="6">
+        <v>5</v>
+      </c>
+      <c r="E142" s="6">
+        <f>IF(F142="Sell",-C142*D142,C142*D142)</f>
+        <v>450.09999999999997</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="11">
+        <v>46091.54583333333</v>
+      </c>
+      <c r="B143" t="s">
+        <v>59</v>
+      </c>
+      <c r="C143" s="2">
+        <v>59.09</v>
+      </c>
+      <c r="D143" s="6">
+        <v>7.89</v>
+      </c>
+      <c r="E143" s="6">
+        <f>IF(F143="Sell",-C143*D143,C143*D143)</f>
+        <v>-466.2201</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="11">
+        <v>46092.438194444447</v>
+      </c>
+      <c r="B144" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" s="2">
+        <v>40.11</v>
+      </c>
+      <c r="D144" s="6">
+        <v>24.92</v>
+      </c>
+      <c r="E144" s="6">
+        <f>IF(F144="Sell",-C144*D144,C144*D144)</f>
+        <v>999.5412</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="11">
+        <v>46100.508333333331</v>
+      </c>
+      <c r="B145" t="s">
+        <v>61</v>
+      </c>
+      <c r="C145" s="2">
+        <v>71.52</v>
+      </c>
+      <c r="D145" s="6">
+        <v>5</v>
+      </c>
+      <c r="E145" s="6">
+        <f>IF(F145="Sell",-C145*D145,C145*D145)</f>
+        <v>-357.59999999999997</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="11">
+        <v>46100.509027777778</v>
+      </c>
+      <c r="B146" t="s">
+        <v>59</v>
+      </c>
+      <c r="C146" s="2">
+        <v>74.150000000000006</v>
+      </c>
+      <c r="D146" s="6">
+        <v>7.21</v>
+      </c>
+      <c r="E146" s="6">
+        <f>IF(F146="Sell",-C146*D146,C146*D146)</f>
+        <v>534.62150000000008</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="11">
+        <v>46113.460416666669</v>
+      </c>
+      <c r="B147" t="s">
+        <v>27</v>
+      </c>
+      <c r="C147" s="2">
+        <v>123.39</v>
+      </c>
+      <c r="D147" s="6">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="E147" s="6">
+        <f>IF(F147="Sell",-C147*D147,C147*D147)</f>
+        <v>-1053.7505999999998</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="11">
+        <v>46113.463194444441</v>
+      </c>
+      <c r="B148" t="s">
+        <v>59</v>
+      </c>
+      <c r="C148" s="2">
+        <v>71.459999999999994</v>
+      </c>
+      <c r="D148" s="6">
+        <v>7.21</v>
+      </c>
+      <c r="E148" s="6">
+        <f>IF(F148="Sell",-C148*D148,C148*D148)</f>
+        <v>-515.22659999999996</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="11">
+        <v>46113.464583333334</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" s="2">
+        <v>4.78</v>
+      </c>
+      <c r="D149" s="6">
+        <v>74</v>
+      </c>
+      <c r="E149" s="6">
+        <f>IF(F149="Sell",-C149*D149,C149*D149)</f>
+        <v>353.72</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="11">
+        <v>46113.46597222222</v>
+      </c>
+      <c r="B150" t="s">
+        <v>61</v>
+      </c>
+      <c r="C150" s="2">
+        <v>83.33</v>
+      </c>
+      <c r="D150" s="6">
+        <v>6</v>
+      </c>
+      <c r="E150" s="6">
+        <f>IF(F150="Sell",-C150*D150,C150*D150)</f>
+        <v>499.98</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="11">
+        <v>46128.462500000001</v>
+      </c>
+      <c r="B151" t="s">
+        <v>43</v>
+      </c>
+      <c r="C151" s="2">
+        <v>175.27</v>
+      </c>
+      <c r="D151" s="6">
+        <v>3</v>
+      </c>
+      <c r="E151" s="6">
+        <f>IF(F151="Sell",-C151*D151,C151*D151)</f>
+        <v>525.81000000000006</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="11">
+        <v>46128.463888888888</v>
+      </c>
+      <c r="B152" t="s">
+        <v>62</v>
+      </c>
+      <c r="C152" s="2">
+        <v>86.03</v>
+      </c>
+      <c r="D152" s="6">
+        <v>7.42</v>
+      </c>
+      <c r="E152" s="6">
+        <f>IF(F152="Sell",-C152*D152,C152*D152)</f>
+        <v>638.34259999999995</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="11">
+        <v>46150.423611111109</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" s="2">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="D153" s="6">
+        <v>7.18</v>
+      </c>
+      <c r="E153" s="6">
+        <f>IF(F153="Sell",-C153*D153,C153*D153)</f>
+        <v>35.110199999999999</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="11">
+        <v>46153.446527777778</v>
+      </c>
+      <c r="B154" t="s">
+        <v>63</v>
+      </c>
+      <c r="C154" s="2">
+        <v>91.94</v>
+      </c>
+      <c r="D154" s="6">
+        <v>6.52</v>
+      </c>
+      <c r="E154" s="6">
+        <f>IF(F154="Sell",-C154*D154,C154*D154)</f>
+        <v>599.44879999999989</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="11">
+        <v>46174.410416666666</v>
+      </c>
+      <c r="B155" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" s="2">
+        <v>40.549999999999997</v>
+      </c>
+      <c r="D155" s="6">
+        <v>24.92</v>
+      </c>
+      <c r="E155" s="6">
+        <f>IF(F155="Sell",-C155*D155,C155*D155)</f>
+        <v>-1010.506</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="11">
+        <v>46175.486111111109</v>
+      </c>
+      <c r="B156" t="s">
+        <v>64</v>
+      </c>
+      <c r="C156" s="2">
+        <v>231.27</v>
+      </c>
+      <c r="D156" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="E156" s="6">
+        <f>IF(F156="Sell",-C156*D156,C156*D156)</f>
+        <v>578.17500000000007</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="11">
+        <v>46175.487500000003</v>
+      </c>
+      <c r="B157" t="s">
+        <v>65</v>
+      </c>
+      <c r="C157" s="2">
+        <v>103.72</v>
+      </c>
+      <c r="D157" s="6">
+        <v>3.95</v>
+      </c>
+      <c r="E157" s="6">
+        <f>IF(F157="Sell",-C157*D157,C157*D157)</f>
+        <v>409.69400000000002</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="11">
+        <v>46177.450694444444</v>
+      </c>
+      <c r="B158" t="s">
+        <v>55</v>
+      </c>
+      <c r="C158" s="2">
+        <v>992.87</v>
+      </c>
+      <c r="D158" s="6">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="E158" s="6">
+        <f>IF(F158="Sell",-C158*D158,C158*D158)</f>
+        <v>-2412.6741000000002</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="11">
+        <v>46181.434027777781</v>
+      </c>
+      <c r="B159" t="s">
+        <v>66</v>
+      </c>
+      <c r="C159" s="2">
+        <v>99.23</v>
+      </c>
+      <c r="D159" s="6">
+        <v>10.07</v>
+      </c>
+      <c r="E159" s="6">
+        <f>IF(F159="Sell",-C159*D159,C159*D159)</f>
+        <v>999.24610000000007</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="11">
+        <v>46181.43472222222</v>
+      </c>
+      <c r="B160" t="s">
+        <v>67</v>
+      </c>
+      <c r="C160" s="2">
+        <v>183.67</v>
+      </c>
+      <c r="D160" s="6">
+        <v>3</v>
+      </c>
+      <c r="E160" s="6">
+        <f>IF(F160="Sell",-C160*D160,C160*D160)</f>
+        <v>551.01</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="11">
+        <v>46204.443055555559</v>
+      </c>
+      <c r="B161" t="s">
+        <v>18</v>
+      </c>
+      <c r="C161" s="2">
+        <v>383.64</v>
+      </c>
+      <c r="D161" s="6">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="E161" s="6">
+        <f>IF(F161="Sell",-C161*D161,C161*D161)</f>
+        <v>890.0447999999999</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="11">
+        <v>46227.419444444444</v>
+      </c>
+      <c r="B162" t="s">
+        <v>67</v>
+      </c>
+      <c r="C162" s="2">
+        <v>161.18</v>
+      </c>
+      <c r="D162" s="6">
+        <v>3</v>
+      </c>
+      <c r="E162" s="6">
+        <f>IF(F162="Sell",-C162*D162,C162*D162)</f>
+        <v>-483.54</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="11">
+        <v>46230.398611111108</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" s="2">
+        <v>3.98</v>
+      </c>
+      <c r="D163" s="6">
+        <v>121.42</v>
+      </c>
+      <c r="E163" s="6">
+        <f>IF(F163="Sell",-C163*D163,C163*D163)</f>
+        <v>483.2516</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="11">
+        <v>46233.619444444441</v>
+      </c>
+      <c r="B164" t="s">
+        <v>64</v>
+      </c>
+      <c r="C164" s="2">
+        <v>232.31</v>
+      </c>
+      <c r="D164" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="E164" s="6">
+        <f>IF(F164="Sell",-C164*D164,C164*D164)</f>
+        <v>-580.77499999999998</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="11">
+        <v>46233.624305555553</v>
+      </c>
+      <c r="B165" t="s">
+        <v>63</v>
+      </c>
+      <c r="C165" s="2">
+        <v>109.81</v>
+      </c>
+      <c r="D165" s="6">
+        <v>5</v>
+      </c>
+      <c r="E165" s="6">
+        <f>IF(F165="Sell",-C165*D165,C165*D165)</f>
+        <v>549.04999999999995</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="11">
+        <v>46233.625</v>
+      </c>
+      <c r="B166" t="s">
+        <v>43</v>
+      </c>
+      <c r="C166" s="2">
+        <v>126.71</v>
+      </c>
+      <c r="D166" s="6">
+        <v>5</v>
+      </c>
+      <c r="E166" s="6">
+        <f>IF(F166="Sell",-C166*D166,C166*D166)</f>
+        <v>633.54999999999995</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="11">
+        <v>46237.402777777781</v>
+      </c>
+      <c r="B167" t="s">
+        <v>55</v>
+      </c>
+      <c r="C167" s="2">
+        <v>779.13</v>
+      </c>
+      <c r="D167" s="6">
+        <v>1.28</v>
+      </c>
+      <c r="E167" s="6">
+        <f>IF(F167="Sell",-C167*D167,C167*D167)</f>
+        <v>997.28640000000007</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="11">
+        <v>46114.560416666667</v>
+      </c>
+      <c r="B168" t="s">
+        <v>18</v>
+      </c>
+      <c r="C168" s="2">
+        <v>371.51</v>
+      </c>
+      <c r="D168" s="6">
+        <v>1.92</v>
+      </c>
+      <c r="E168" s="6">
+        <f>IF(F168="Sell",-C168*D168,C168*D168)</f>
+        <v>713.29919999999993</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F168" xr:uid="{C1E503C2-5372-44CA-920E-B8461526100B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F167">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
   <dimension ref="A1:F174"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -3929,7 +7504,7 @@
         <v>16</v>
       </c>
       <c r="C160" s="5">
-        <f>D160*E160</f>
+        <f t="shared" ref="C160:C174" si="3">D160*E160</f>
         <v>35.110199999999999</v>
       </c>
       <c r="D160" s="5">
@@ -3950,7 +7525,7 @@
         <v>63</v>
       </c>
       <c r="C161" s="5">
-        <f>D161*E161</f>
+        <f t="shared" si="3"/>
         <v>599.44879999999989</v>
       </c>
       <c r="D161" s="5">
@@ -3971,7 +7546,7 @@
         <v>6</v>
       </c>
       <c r="C162" s="5">
-        <f>D162*E162</f>
+        <f t="shared" si="3"/>
         <v>1010.506</v>
       </c>
       <c r="D162" s="5">
@@ -3992,7 +7567,7 @@
         <v>64</v>
       </c>
       <c r="C163" s="5">
-        <f>D163*E163</f>
+        <f t="shared" si="3"/>
         <v>578.17500000000007</v>
       </c>
       <c r="D163" s="5">
@@ -4013,7 +7588,7 @@
         <v>65</v>
       </c>
       <c r="C164" s="5">
-        <f>D164*E164</f>
+        <f t="shared" si="3"/>
         <v>409.69400000000002</v>
       </c>
       <c r="D164" s="5">
@@ -4034,7 +7609,7 @@
         <v>55</v>
       </c>
       <c r="C165" s="5">
-        <f>D165*E165</f>
+        <f t="shared" si="3"/>
         <v>2422.6028000000001</v>
       </c>
       <c r="D165" s="5">
@@ -4055,7 +7630,7 @@
         <v>66</v>
       </c>
       <c r="C166" s="5">
-        <f>D166*E166</f>
+        <f t="shared" si="3"/>
         <v>999.24610000000007</v>
       </c>
       <c r="D166" s="5">
@@ -4076,7 +7651,7 @@
         <v>67</v>
       </c>
       <c r="C167" s="5">
-        <f>D167*E167</f>
+        <f t="shared" si="3"/>
         <v>551.01</v>
       </c>
       <c r="D167" s="5">
@@ -4097,7 +7672,7 @@
         <v>18</v>
       </c>
       <c r="C168" s="5">
-        <f>D168*E168</f>
+        <f t="shared" si="3"/>
         <v>890.0447999999999</v>
       </c>
       <c r="D168" s="5">
@@ -4118,7 +7693,7 @@
         <v>67</v>
       </c>
       <c r="C169" s="5">
-        <f>D169*E169</f>
+        <f t="shared" si="3"/>
         <v>483.54</v>
       </c>
       <c r="D169" s="5">
@@ -4139,7 +7714,7 @@
         <v>16</v>
       </c>
       <c r="C170" s="5">
-        <f>D170*E170</f>
+        <f t="shared" si="3"/>
         <v>483.2516</v>
       </c>
       <c r="D170" s="5">
@@ -4160,7 +7735,7 @@
         <v>55</v>
       </c>
       <c r="C171" s="5">
-        <f>D171*E171</f>
+        <f t="shared" si="3"/>
         <v>998.38700000000006</v>
       </c>
       <c r="D171" s="5">
@@ -4181,7 +7756,7 @@
         <v>64</v>
       </c>
       <c r="C172" s="5">
-        <f>D172*E172</f>
+        <f t="shared" si="3"/>
         <v>580.77499999999998</v>
       </c>
       <c r="D172" s="5">
@@ -4202,7 +7777,7 @@
         <v>63</v>
       </c>
       <c r="C173" s="5">
-        <f>D173*E173</f>
+        <f t="shared" si="3"/>
         <v>549.04999999999995</v>
       </c>
       <c r="D173" s="5">
@@ -4223,7 +7798,7 @@
         <v>43</v>
       </c>
       <c r="C174" s="5">
-        <f>D174*E174</f>
+        <f t="shared" si="3"/>
         <v>633.54999999999995</v>
       </c>
       <c r="D174" s="5">

--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johanrosa/Desktop/r_projects/personal/finance_portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80A03F6-483A-4AB8-89F2-7B75AAD5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6D5F34-5100-C940-A527-CB0000573BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
   <sheets>
     <sheet name="new_logs" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">logs!$A$1:$F$155</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">new_logs!$A$1:$F$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">new_logs!$A$1:$F$169</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="73">
   <si>
     <t>date</t>
   </si>
@@ -258,6 +258,9 @@
   <si>
     <t>Sell</t>
   </si>
+  <si>
+    <t>OKLO</t>
+  </si>
 </sst>
 </file>
 
@@ -269,7 +272,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -319,7 +322,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -353,6 +356,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -689,3547 +695,3842 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E503C2-5372-44CA-920E-B8461526100B}">
-  <dimension ref="A1:F168"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F182"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="14.375" style="11" customWidth="1"/>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="12.625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="12.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="10" t="s">
         <v>68</v>
       </c>
       <c r="B1" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="12" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="11">
         <v>45903.43472222222</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="12">
         <v>63.42</v>
       </c>
       <c r="D2" s="6">
         <v>3.15</v>
       </c>
-      <c r="E2" s="6">
-        <f>IF(F2="Sell",-C2*D2,C2*D2)</f>
+      <c r="E2" s="12">
+        <f>IF(F2="Sell",D2*C2*-1,D2*C2)</f>
         <v>199.773</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="11">
         <v>45903.435416666667</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="12">
         <v>33.61</v>
       </c>
       <c r="D3" s="6">
         <v>5.94</v>
       </c>
-      <c r="E3" s="6">
-        <f>IF(F3="Sell",-C3*D3,C3*D3)</f>
+      <c r="E3" s="12">
+        <f>IF(F3="Sell",D3*C3*-1,D3*C3)</f>
         <v>199.64340000000001</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" s="11">
         <v>45903.436111111114</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="12">
         <v>317.19</v>
       </c>
       <c r="D4" s="6">
         <v>0.63053000000000003</v>
       </c>
-      <c r="E4" s="6">
-        <f>IF(F4="Sell",-C4*D4,C4*D4)</f>
+      <c r="E4" s="12">
+        <f>IF(F4="Sell",D4*C4*-1,D4*C4)</f>
         <v>199.9978107</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="11">
         <v>45903.436805555553</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="12">
         <v>328.13</v>
       </c>
       <c r="D5" s="6">
         <v>0.76188999999999996</v>
       </c>
-      <c r="E5" s="6">
-        <f>IF(F5="Sell",-C5*D5,C5*D5)</f>
+      <c r="E5" s="12">
+        <f>IF(F5="Sell",D5*C5*-1,D5*C5)</f>
         <v>249.99896569999999</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="11">
         <v>45903.438194444447</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="12">
         <v>131.86000000000001</v>
       </c>
       <c r="D6" s="6">
         <v>0.37919000000000003</v>
       </c>
-      <c r="E6" s="6">
-        <f>IF(F6="Sell",-C6*D6,C6*D6)</f>
+      <c r="E6" s="12">
+        <f>IF(F6="Sell",D6*C6*-1,D6*C6)</f>
         <v>49.999993400000008</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="11">
         <v>45903.438888888886</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="12">
         <v>643.12</v>
       </c>
       <c r="D7" s="6">
         <v>0.31097999999999998</v>
       </c>
-      <c r="E7" s="6">
-        <f>IF(F7="Sell",-C7*D7,C7*D7)</f>
+      <c r="E7" s="12">
+        <f>IF(F7="Sell",D7*C7*-1,D7*C7)</f>
         <v>199.99745759999999</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="11">
         <v>45903.440972222219</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="12">
         <v>9.14</v>
       </c>
       <c r="D8" s="6">
         <v>5.46</v>
       </c>
-      <c r="E8" s="6">
-        <f>IF(F8="Sell",-C8*D8,C8*D8)</f>
+      <c r="E8" s="12">
+        <f>IF(F8="Sell",D8*C8*-1,D8*C8)</f>
         <v>49.904400000000003</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="11">
         <v>45903.445138888892</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="12">
         <v>45.22</v>
       </c>
       <c r="D9" s="6">
         <v>0.44206000000000001</v>
       </c>
-      <c r="E9" s="6">
-        <f>IF(F9="Sell",-C9*D9,C9*D9)</f>
+      <c r="E9" s="12">
+        <f>IF(F9="Sell",D9*C9*-1,D9*C9)</f>
         <v>19.989953199999999</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="11">
         <v>45903.445833333331</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="12">
         <v>39.6</v>
       </c>
       <c r="D10" s="6">
         <v>0.50480000000000003</v>
       </c>
-      <c r="E10" s="6">
-        <f>IF(F10="Sell",-C10*D10,C10*D10)</f>
+      <c r="E10" s="12">
+        <f>IF(F10="Sell",D10*C10*-1,D10*C10)</f>
         <v>19.990080000000003</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" s="11">
         <v>45903.448611111111</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="12">
         <v>5.26</v>
       </c>
       <c r="D11" s="6">
         <v>4.75</v>
       </c>
-      <c r="E11" s="6">
-        <f>IF(F11="Sell",-C11*D11,C11*D11)</f>
+      <c r="E11" s="12">
+        <f>IF(F11="Sell",D11*C11*-1,D11*C11)</f>
         <v>24.984999999999999</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12" s="11">
         <v>45903.455555555556</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="12">
         <v>339.97</v>
       </c>
       <c r="D12" s="6">
         <v>5.8790000000000002E-2</v>
       </c>
-      <c r="E12" s="6">
-        <f>IF(F12="Sell",-C12*D12,C12*D12)</f>
+      <c r="E12" s="12">
+        <f>IF(F12="Sell",D12*C12*-1,D12*C12)</f>
         <v>19.986836300000004</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" s="11">
         <v>45903.463888888888</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="12">
         <v>506.14</v>
       </c>
       <c r="D13" s="6">
         <v>3.9489999999999997E-2</v>
       </c>
-      <c r="E13" s="6">
-        <f>IF(F13="Sell",-C13*D13,C13*D13)</f>
+      <c r="E13" s="12">
+        <f>IF(F13="Sell",D13*C13*-1,D13*C13)</f>
         <v>19.9874686</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14" s="11">
         <v>45903.46597222222</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="12">
         <v>737.72</v>
       </c>
       <c r="D14" s="6">
         <v>2.7089999999999999E-2</v>
       </c>
-      <c r="E14" s="6">
-        <f>IF(F14="Sell",-C14*D14,C14*D14)</f>
+      <c r="E14" s="12">
+        <f>IF(F14="Sell",D14*C14*-1,D14*C14)</f>
         <v>19.984834800000002</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" s="11">
         <v>45903.467361111114</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="12">
         <v>236.43</v>
       </c>
       <c r="D15" s="6">
         <v>8.4540000000000004E-2</v>
       </c>
-      <c r="E15" s="6">
-        <f>IF(F15="Sell",-C15*D15,C15*D15)</f>
+      <c r="E15" s="12">
+        <f>IF(F15="Sell",D15*C15*-1,D15*C15)</f>
         <v>19.987792200000001</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16" s="11">
         <v>45903.46875</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="12">
         <v>230.24</v>
       </c>
       <c r="D16" s="6">
         <v>0.21715999999999999</v>
       </c>
-      <c r="E16" s="6">
-        <f>IF(F16="Sell",-C16*D16,C16*D16)</f>
+      <c r="E16" s="12">
+        <f>IF(F16="Sell",D16*C16*-1,D16*C16)</f>
         <v>49.998918400000001</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="11">
         <v>45903.470138888886</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="12">
         <v>225.92</v>
       </c>
       <c r="D17" s="6">
         <v>0.13278000000000001</v>
       </c>
-      <c r="E17" s="6">
-        <f>IF(F17="Sell",-C17*D17,C17*D17)</f>
+      <c r="E17" s="12">
+        <f>IF(F17="Sell",D17*C17*-1,D17*C17)</f>
         <v>29.9976576</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" s="11">
         <v>45903.474999999999</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="12">
         <v>61.94</v>
       </c>
       <c r="D18" s="6">
         <v>0.48430000000000001</v>
       </c>
-      <c r="E18" s="6">
-        <f>IF(F18="Sell",-C18*D18,C18*D18)</f>
+      <c r="E18" s="12">
+        <f>IF(F18="Sell",D18*C18*-1,D18*C18)</f>
         <v>29.997541999999999</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" s="11">
         <v>45903.476388888892</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="12">
         <v>93.52</v>
       </c>
       <c r="D19" s="6">
         <v>1.06</v>
       </c>
-      <c r="E19" s="6">
-        <f>IF(F19="Sell",-C19*D19,C19*D19)</f>
+      <c r="E19" s="12">
+        <f>IF(F19="Sell",D19*C19*-1,D19*C19)</f>
         <v>99.131200000000007</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" s="11">
         <v>45903.479861111111</v>
       </c>
       <c r="B20" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="12">
         <v>121.82</v>
       </c>
       <c r="D20" s="6">
         <v>0.41039999999999999</v>
       </c>
-      <c r="E20" s="6">
-        <f>IF(F20="Sell",-C20*D20,C20*D20)</f>
+      <c r="E20" s="12">
+        <f>IF(F20="Sell",D20*C20*-1,D20*C20)</f>
         <v>49.994927999999994</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" s="11">
         <v>45903.480555555558</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="12">
         <v>111.61</v>
       </c>
       <c r="D21" s="6">
         <v>8.9590000000000003E-2</v>
       </c>
-      <c r="E21" s="6">
-        <f>IF(F21="Sell",-C21*D21,C21*D21)</f>
+      <c r="E21" s="12">
+        <f>IF(F21="Sell",D21*C21*-1,D21*C21)</f>
         <v>9.9991398999999994</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" s="11">
         <v>45903.493750000001</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="12">
         <v>74.92</v>
       </c>
       <c r="D22" s="6">
         <v>0.40042</v>
       </c>
-      <c r="E22" s="6">
-        <f>IF(F22="Sell",-C22*D22,C22*D22)</f>
+      <c r="E22" s="12">
+        <f>IF(F22="Sell",D22*C22*-1,D22*C22)</f>
         <v>29.999466399999999</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" s="11">
         <v>45903.494444444441</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="12">
         <v>17.5</v>
       </c>
       <c r="D23" s="6">
         <v>1.42</v>
       </c>
-      <c r="E23" s="6">
-        <f>IF(F23="Sell",-C23*D23,C23*D23)</f>
+      <c r="E23" s="12">
+        <f>IF(F23="Sell",D23*C23*-1,D23*C23)</f>
         <v>24.849999999999998</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" s="11">
         <v>45903.494444444441</v>
       </c>
       <c r="B24" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="12">
         <v>37.47</v>
       </c>
       <c r="D24" s="6">
         <v>1.33</v>
       </c>
-      <c r="E24" s="6">
-        <f>IF(F24="Sell",-C24*D24,C24*D24)</f>
+      <c r="E24" s="12">
+        <f>IF(F24="Sell",D24*C24*-1,D24*C24)</f>
         <v>49.835100000000004</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" s="11">
         <v>45903.495138888888</v>
       </c>
       <c r="B25" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="12">
         <v>13</v>
       </c>
       <c r="D25" s="6">
         <v>1.53</v>
       </c>
-      <c r="E25" s="6">
-        <f>IF(F25="Sell",-C25*D25,C25*D25)</f>
+      <c r="E25" s="12">
+        <f>IF(F25="Sell",D25*C25*-1,D25*C25)</f>
         <v>19.89</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" s="11">
         <v>45903.504861111112</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="12">
         <v>158.88999999999999</v>
       </c>
       <c r="D26" s="6">
         <v>0.12581000000000001</v>
       </c>
-      <c r="E26" s="6">
-        <f>IF(F26="Sell",-C26*D26,C26*D26)</f>
+      <c r="E26" s="12">
+        <f>IF(F26="Sell",D26*C26*-1,D26*C26)</f>
         <v>19.9899509</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" s="11">
         <v>45904.404861111114</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="12">
         <v>49.57</v>
       </c>
       <c r="D27" s="6">
         <v>1</v>
       </c>
-      <c r="E27" s="6">
-        <f>IF(F27="Sell",-C27*D27,C27*D27)</f>
+      <c r="E27" s="12">
+        <f>IF(F27="Sell",D27*C27*-1,D27*C27)</f>
         <v>49.57</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" s="11">
         <v>45904.406944444447</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="12">
         <v>8.94</v>
       </c>
       <c r="D28" s="6">
         <v>3.35</v>
       </c>
-      <c r="E28" s="6">
-        <f>IF(F28="Sell",-C28*D28,C28*D28)</f>
+      <c r="E28" s="12">
+        <f>IF(F28="Sell",D28*C28*-1,D28*C28)</f>
         <v>29.948999999999998</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" s="11">
         <v>45904.407638888886</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="12">
         <v>27.16</v>
       </c>
       <c r="D29" s="6">
         <v>0.92030000000000001</v>
       </c>
-      <c r="E29" s="6">
-        <f>IF(F29="Sell",-C29*D29,C29*D29)</f>
+      <c r="E29" s="12">
+        <f>IF(F29="Sell",D29*C29*-1,D29*C29)</f>
         <v>24.995348</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" s="11">
         <v>45904.412499999999</v>
       </c>
       <c r="B30" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="12">
         <v>74.34</v>
       </c>
       <c r="D30" s="6">
         <v>1.34</v>
       </c>
-      <c r="E30" s="6">
-        <f>IF(F30="Sell",-C30*D30,C30*D30)</f>
+      <c r="E30" s="12">
+        <f>IF(F30="Sell",D30*C30*-1,D30*C30)</f>
         <v>99.615600000000015</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" s="11">
         <v>45904.414583333331</v>
       </c>
       <c r="B31" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="12">
         <v>185.21</v>
       </c>
       <c r="D31" s="6">
         <v>0.16197</v>
       </c>
-      <c r="E31" s="6">
-        <f>IF(F31="Sell",-C31*D31,C31*D31)</f>
+      <c r="E31" s="12">
+        <f>IF(F31="Sell",D31*C31*-1,D31*C31)</f>
         <v>29.998463700000002</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" s="11">
         <v>45904.418749999997</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="12">
         <v>647.66</v>
       </c>
       <c r="D32" s="6">
         <v>0.15440000000000001</v>
       </c>
-      <c r="E32" s="6">
-        <f>IF(F32="Sell",-C32*D32,C32*D32)</f>
+      <c r="E32" s="12">
+        <f>IF(F32="Sell",D32*C32*-1,D32*C32)</f>
         <v>99.998704000000004</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33" s="11">
         <v>45905.408333333333</v>
       </c>
       <c r="B33" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="12">
         <v>6.65</v>
       </c>
       <c r="D33" s="6">
         <v>2.25</v>
       </c>
-      <c r="E33" s="6">
-        <f>IF(F33="Sell",-C33*D33,C33*D33)</f>
+      <c r="E33" s="12">
+        <f>IF(F33="Sell",D33*C33*-1,D33*C33)</f>
         <v>14.9625</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="A34" s="11">
         <v>45908.665277777778</v>
       </c>
       <c r="B34" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="12">
         <v>61.73</v>
       </c>
       <c r="D34" s="6">
         <v>0.48430000000000001</v>
       </c>
-      <c r="E34" s="6">
-        <f>IF(F34="Sell",-C34*D34,C34*D34)</f>
+      <c r="E34" s="12">
+        <f>IF(F34="Sell",D34*C34*-1,D34*C34)</f>
         <v>-29.895838999999999</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6">
       <c r="A35" s="11">
         <v>45909.415277777778</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="12">
         <v>6.16</v>
       </c>
       <c r="D35" s="6">
         <v>3</v>
       </c>
-      <c r="E35" s="6">
-        <f>IF(F35="Sell",-C35*D35,C35*D35)</f>
+      <c r="E35" s="12">
+        <f>IF(F35="Sell",D35*C35*-1,D35*C35)</f>
         <v>18.48</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36" s="11">
         <v>45909.418055555558</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="12">
         <v>32.69</v>
       </c>
       <c r="D36" s="6">
         <v>0.38446000000000002</v>
       </c>
-      <c r="E36" s="6">
-        <f>IF(F36="Sell",-C36*D36,C36*D36)</f>
+      <c r="E36" s="12">
+        <f>IF(F36="Sell",D36*C36*-1,D36*C36)</f>
         <v>12.567997399999999</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6">
       <c r="A37" s="11">
         <v>45909.427083333336</v>
       </c>
       <c r="B37" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="12">
         <v>72.319999999999993</v>
       </c>
       <c r="D37" s="6">
         <v>1.38</v>
       </c>
-      <c r="E37" s="6">
-        <f>IF(F37="Sell",-C37*D37,C37*D37)</f>
+      <c r="E37" s="12">
+        <f>IF(F37="Sell",D37*C37*-1,D37*C37)</f>
         <v>99.801599999999979</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6">
       <c r="A38" s="11">
         <v>45909.427777777775</v>
       </c>
       <c r="B38" t="s">
         <v>40</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="12">
         <v>2362.94</v>
       </c>
       <c r="D38" s="6">
         <v>8.4499999999999992E-3</v>
       </c>
-      <c r="E38" s="6">
-        <f>IF(F38="Sell",-C38*D38,C38*D38)</f>
+      <c r="E38" s="12">
+        <f>IF(F38="Sell",D38*C38*-1,D38*C38)</f>
         <v>19.966842999999997</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="A39" s="11">
         <v>45909.431250000001</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="12">
         <v>335.9</v>
       </c>
       <c r="D39" s="6">
         <v>1</v>
       </c>
-      <c r="E39" s="6">
-        <f>IF(F39="Sell",-C39*D39,C39*D39)</f>
+      <c r="E39" s="12">
+        <f>IF(F39="Sell",D39*C39*-1,D39*C39)</f>
         <v>335.9</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="A40" s="11">
         <v>45909.43472222222</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="12">
         <v>648.80999999999995</v>
       </c>
       <c r="D40" s="6">
         <v>0.46235999999999999</v>
       </c>
-      <c r="E40" s="6">
-        <f>IF(F40="Sell",-C40*D40,C40*D40)</f>
+      <c r="E40" s="12">
+        <f>IF(F40="Sell",D40*C40*-1,D40*C40)</f>
         <v>299.98379159999996</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6">
       <c r="A41" s="11">
         <v>45909.439583333333</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="12">
         <v>9.89</v>
       </c>
       <c r="D41" s="6">
         <v>1.36</v>
       </c>
-      <c r="E41" s="6">
-        <f>IF(F41="Sell",-C41*D41,C41*D41)</f>
+      <c r="E41" s="12">
+        <f>IF(F41="Sell",D41*C41*-1,D41*C41)</f>
         <v>13.450400000000002</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6">
       <c r="A42" s="11">
         <v>45909.589583333334</v>
       </c>
       <c r="B42" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="12">
         <v>579.97</v>
       </c>
       <c r="D42" s="6">
         <v>0.17241999999999999</v>
       </c>
-      <c r="E42" s="6">
-        <f>IF(F42="Sell",-C42*D42,C42*D42)</f>
+      <c r="E42" s="12">
+        <f>IF(F42="Sell",D42*C42*-1,D42*C42)</f>
         <v>99.998427399999997</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6">
       <c r="A43" s="11">
         <v>45910.459722222222</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="12">
         <v>341.71</v>
       </c>
       <c r="D43" s="6">
         <v>5.849E-2</v>
       </c>
-      <c r="E43" s="6">
-        <f>IF(F43="Sell",-C43*D43,C43*D43)</f>
+      <c r="E43" s="12">
+        <f>IF(F43="Sell",D43*C43*-1,D43*C43)</f>
         <v>19.986617899999999</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6">
       <c r="A44" s="11">
         <v>45910.654166666667</v>
       </c>
       <c r="B44" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="12">
         <v>5.69</v>
       </c>
       <c r="D44" s="6">
         <v>1.47</v>
       </c>
-      <c r="E44" s="6">
-        <f>IF(F44="Sell",-C44*D44,C44*D44)</f>
+      <c r="E44" s="12">
+        <f>IF(F44="Sell",D44*C44*-1,D44*C44)</f>
         <v>8.3643000000000001</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6">
       <c r="A45" s="11">
         <v>45911.636805555558</v>
       </c>
       <c r="B45" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="12">
         <v>308.70999999999998</v>
       </c>
       <c r="D45" s="6">
         <v>5.849E-2</v>
       </c>
-      <c r="E45" s="6">
-        <f>IF(F45="Sell",-C45*D45,C45*D45)</f>
+      <c r="E45" s="12">
+        <f>IF(F45="Sell",D45*C45*-1,D45*C45)</f>
         <v>-18.056447899999998</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6">
       <c r="A46" s="11">
         <v>45911.637499999997</v>
       </c>
       <c r="B46" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="12">
         <v>73.36</v>
       </c>
       <c r="D46" s="6">
         <v>1.38</v>
       </c>
-      <c r="E46" s="6">
-        <f>IF(F46="Sell",-C46*D46,C46*D46)</f>
+      <c r="E46" s="12">
+        <f>IF(F46="Sell",D46*C46*-1,D46*C46)</f>
         <v>-101.23679999999999</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6">
       <c r="A47" s="11">
         <v>45912.396527777775</v>
       </c>
       <c r="B47" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="12">
         <v>54.9</v>
       </c>
       <c r="D47" s="6">
         <v>1</v>
       </c>
-      <c r="E47" s="6">
-        <f>IF(F47="Sell",-C47*D47,C47*D47)</f>
+      <c r="E47" s="12">
+        <f>IF(F47="Sell",D47*C47*-1,D47*C47)</f>
         <v>54.9</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6">
       <c r="A48" s="11">
         <v>45912.399305555555</v>
       </c>
       <c r="B48" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="12">
         <v>34.49</v>
       </c>
       <c r="D48" s="6">
         <v>0.4</v>
       </c>
-      <c r="E48" s="6">
-        <f>IF(F48="Sell",-C48*D48,C48*D48)</f>
+      <c r="E48" s="12">
+        <f>IF(F48="Sell",D48*C48*-1,D48*C48)</f>
         <v>13.796000000000001</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6">
       <c r="A49" s="11">
         <v>45912.408333333333</v>
       </c>
       <c r="B49" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="12">
         <v>42.99</v>
       </c>
       <c r="D49" s="6">
         <v>1</v>
       </c>
-      <c r="E49" s="6">
-        <f>IF(F49="Sell",-C49*D49,C49*D49)</f>
+      <c r="E49" s="12">
+        <f>IF(F49="Sell",D49*C49*-1,D49*C49)</f>
         <v>42.99</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6">
       <c r="A50" s="11">
         <v>45912.414583333331</v>
       </c>
       <c r="B50" t="s">
         <v>45</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="12">
         <v>37.74</v>
       </c>
       <c r="D50" s="6">
         <v>0.16</v>
       </c>
-      <c r="E50" s="6">
-        <f>IF(F50="Sell",-C50*D50,C50*D50)</f>
+      <c r="E50" s="12">
+        <f>IF(F50="Sell",D50*C50*-1,D50*C50)</f>
         <v>6.0384000000000002</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6">
       <c r="A51" s="11">
         <v>45923.460416666669</v>
       </c>
       <c r="B51" t="s">
         <v>46</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="12">
         <v>68.19</v>
       </c>
       <c r="D51" s="6">
         <v>1</v>
       </c>
-      <c r="E51" s="6">
-        <f>IF(F51="Sell",-C51*D51,C51*D51)</f>
+      <c r="E51" s="12">
+        <f>IF(F51="Sell",D51*C51*-1,D51*C51)</f>
         <v>68.19</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6">
       <c r="A52" s="11">
         <v>45923.463194444441</v>
       </c>
       <c r="B52" t="s">
         <v>21</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="12">
         <v>251.48</v>
       </c>
       <c r="D52" s="6">
         <v>0.58055999999999996</v>
       </c>
-      <c r="E52" s="6">
-        <f>IF(F52="Sell",-C52*D52,C52*D52)</f>
+      <c r="E52" s="12">
+        <f>IF(F52="Sell",D52*C52*-1,D52*C52)</f>
         <v>145.9992288</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6">
       <c r="A53" s="11">
         <v>45923.489583333336</v>
       </c>
       <c r="B53" t="s">
         <v>47</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="12">
         <v>170.43</v>
       </c>
       <c r="D53" s="6">
         <v>1</v>
       </c>
-      <c r="E53" s="6">
-        <f>IF(F53="Sell",-C53*D53,C53*D53)</f>
+      <c r="E53" s="12">
+        <f>IF(F53="Sell",D53*C53*-1,D53*C53)</f>
         <v>170.43</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6">
       <c r="A54" s="11">
         <v>45923.515972222223</v>
       </c>
       <c r="B54" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="12">
         <v>765.72</v>
       </c>
       <c r="D54" s="6">
         <v>0.10446999999999999</v>
       </c>
-      <c r="E54" s="6">
-        <f>IF(F54="Sell",-C54*D54,C54*D54)</f>
+      <c r="E54" s="12">
+        <f>IF(F54="Sell",D54*C54*-1,D54*C54)</f>
         <v>79.994768399999998</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6">
       <c r="A55" s="11">
         <v>45923.517361111109</v>
       </c>
       <c r="B55" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="12">
         <v>8.0299999999999994</v>
       </c>
       <c r="D55" s="6">
         <v>4.45</v>
       </c>
-      <c r="E55" s="6">
-        <f>IF(F55="Sell",-C55*D55,C55*D55)</f>
+      <c r="E55" s="12">
+        <f>IF(F55="Sell",D55*C55*-1,D55*C55)</f>
         <v>35.733499999999999</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6">
       <c r="A56" s="11">
         <v>45924.42291666667</v>
       </c>
       <c r="B56" t="s">
         <v>37</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="12">
         <v>666.18</v>
       </c>
       <c r="D56" s="6">
         <v>0.15473000000000001</v>
       </c>
-      <c r="E56" s="6">
-        <f>IF(F56="Sell",-C56*D56,C56*D56)</f>
+      <c r="E56" s="12">
+        <f>IF(F56="Sell",D56*C56*-1,D56*C56)</f>
         <v>-103.0780314</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6">
       <c r="A57" s="11">
         <v>45924.423611111109</v>
       </c>
       <c r="B57" t="s">
         <v>32</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="12">
         <v>48.95</v>
       </c>
       <c r="D57" s="6">
         <v>1</v>
       </c>
-      <c r="E57" s="6">
-        <f>IF(F57="Sell",-C57*D57,C57*D57)</f>
+      <c r="E57" s="12">
+        <f>IF(F57="Sell",D57*C57*-1,D57*C57)</f>
         <v>-48.95</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6">
       <c r="A58" s="11">
         <v>45924.423611111109</v>
       </c>
       <c r="B58" t="s">
         <v>25</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="12">
         <v>121.43</v>
       </c>
       <c r="D58" s="6">
         <v>0.41039999999999999</v>
       </c>
-      <c r="E58" s="6">
-        <f>IF(F58="Sell",-C58*D58,C58*D58)</f>
+      <c r="E58" s="12">
+        <f>IF(F58="Sell",D58*C58*-1,D58*C58)</f>
         <v>-49.834872000000004</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6">
       <c r="A59" s="11">
         <v>45929.46875</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="12">
         <v>327</v>
       </c>
       <c r="D59" s="6">
         <v>0.61799999999999999</v>
       </c>
-      <c r="E59" s="6">
-        <f>IF(F59="Sell",-C59*D59,C59*D59)</f>
+      <c r="E59" s="12">
+        <f>IF(F59="Sell",D59*C59*-1,D59*C59)</f>
         <v>202.08599999999998</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6">
       <c r="A60" s="11">
         <v>45937.396527777775</v>
       </c>
       <c r="B60" t="s">
         <v>48</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="12">
         <v>61.27</v>
       </c>
       <c r="D60" s="6">
         <v>1</v>
       </c>
-      <c r="E60" s="6">
-        <f>IF(F60="Sell",-C60*D60,C60*D60)</f>
+      <c r="E60" s="12">
+        <f>IF(F60="Sell",D60*C60*-1,D60*C60)</f>
         <v>61.27</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6">
       <c r="A61" s="11">
         <v>45937.398611111108</v>
       </c>
       <c r="B61" t="s">
         <v>34</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="12">
         <v>33.94</v>
       </c>
       <c r="D61" s="6">
         <v>2</v>
       </c>
-      <c r="E61" s="6">
-        <f>IF(F61="Sell",-C61*D61,C61*D61)</f>
+      <c r="E61" s="12">
+        <f>IF(F61="Sell",D61*C61*-1,D61*C61)</f>
         <v>67.88</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6">
       <c r="A62" s="11">
         <v>45937.4</v>
       </c>
       <c r="B62" t="s">
         <v>33</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="12">
         <v>12.39</v>
       </c>
       <c r="D62" s="6">
         <v>4</v>
       </c>
-      <c r="E62" s="6">
-        <f>IF(F62="Sell",-C62*D62,C62*D62)</f>
+      <c r="E62" s="12">
+        <f>IF(F62="Sell",D62*C62*-1,D62*C62)</f>
         <v>49.56</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6">
       <c r="A63" s="11">
         <v>45937.40625</v>
       </c>
       <c r="B63" t="s">
         <v>49</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="12">
         <v>5.32</v>
       </c>
       <c r="D63" s="6">
         <v>5</v>
       </c>
-      <c r="E63" s="6">
-        <f>IF(F63="Sell",-C63*D63,C63*D63)</f>
+      <c r="E63" s="12">
+        <f>IF(F63="Sell",D63*C63*-1,D63*C63)</f>
         <v>26.6</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6">
       <c r="A64" s="11">
         <v>45937.462500000001</v>
       </c>
       <c r="B64" t="s">
         <v>50</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64" s="12">
         <v>57.48</v>
       </c>
       <c r="D64" s="6">
         <v>2</v>
       </c>
-      <c r="E64" s="6">
-        <f>IF(F64="Sell",-C64*D64,C64*D64)</f>
+      <c r="E64" s="12">
+        <f>IF(F64="Sell",D64*C64*-1,D64*C64)</f>
         <v>114.96</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6">
       <c r="A65" s="11">
         <v>45937.465277777781</v>
       </c>
       <c r="B65" t="s">
         <v>42</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65" s="12">
         <v>604.97</v>
       </c>
       <c r="D65" s="6">
         <v>0.12198000000000001</v>
       </c>
-      <c r="E65" s="6">
-        <f>IF(F65="Sell",-C65*D65,C65*D65)</f>
+      <c r="E65" s="12">
+        <f>IF(F65="Sell",D65*C65*-1,D65*C65)</f>
         <v>73.794240600000009</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6">
       <c r="A66" s="11">
         <v>45938.413194444445</v>
       </c>
       <c r="B66" t="s">
         <v>50</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C66" s="12">
         <v>59.34</v>
       </c>
       <c r="D66" s="6">
         <v>2</v>
       </c>
-      <c r="E66" s="6">
-        <f>IF(F66="Sell",-C66*D66,C66*D66)</f>
+      <c r="E66" s="12">
+        <f>IF(F66="Sell",D66*C66*-1,D66*C66)</f>
         <v>-118.68</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6">
       <c r="A67" s="11">
         <v>45939.417361111111</v>
       </c>
       <c r="B67" t="s">
         <v>51</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="12">
         <v>124.22</v>
       </c>
       <c r="D67" s="6">
         <v>0.95403000000000004</v>
       </c>
-      <c r="E67" s="6">
-        <f>IF(F67="Sell",-C67*D67,C67*D67)</f>
+      <c r="E67" s="12">
+        <f>IF(F67="Sell",D67*C67*-1,D67*C67)</f>
         <v>118.5096066</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6">
       <c r="A68" s="11">
         <v>45943.410416666666</v>
       </c>
       <c r="B68" t="s">
         <v>26</v>
       </c>
-      <c r="C68" s="2">
+      <c r="C68" s="12">
         <v>112.2</v>
       </c>
       <c r="D68" s="6">
         <v>9.0120000000000006E-2</v>
       </c>
-      <c r="E68" s="6">
-        <f>IF(F68="Sell",-C68*D68,C68*D68)</f>
+      <c r="E68" s="12">
+        <f>IF(F68="Sell",D68*C68*-1,D68*C68)</f>
         <v>-10.111464000000002</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6">
       <c r="A69" s="11">
         <v>45943.411805555559</v>
       </c>
       <c r="B69" t="s">
         <v>20</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69" s="12">
         <v>246.88</v>
       </c>
       <c r="D69" s="6">
         <v>8.4540000000000004E-2</v>
       </c>
-      <c r="E69" s="6">
-        <f>IF(F69="Sell",-C69*D69,C69*D69)</f>
+      <c r="E69" s="12">
+        <f>IF(F69="Sell",D69*C69*-1,D69*C69)</f>
         <v>-20.871235200000001</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6">
       <c r="A70" s="11">
         <v>45943.412499999999</v>
       </c>
       <c r="B70" t="s">
         <v>28</v>
       </c>
-      <c r="C70" s="2">
+      <c r="C70" s="12">
         <v>17.309999999999999</v>
       </c>
       <c r="D70" s="6">
         <v>1.42</v>
       </c>
-      <c r="E70" s="6">
-        <f>IF(F70="Sell",-C70*D70,C70*D70)</f>
+      <c r="E70" s="12">
+        <f>IF(F70="Sell",D70*C70*-1,D70*C70)</f>
         <v>-24.580199999999998</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6">
       <c r="A71" s="11">
         <v>45943.413194444445</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71" s="12">
         <v>128.91</v>
       </c>
       <c r="D71" s="6">
         <v>0.37919000000000003</v>
       </c>
-      <c r="E71" s="6">
-        <f>IF(F71="Sell",-C71*D71,C71*D71)</f>
+      <c r="E71" s="12">
+        <f>IF(F71="Sell",D71*C71*-1,D71*C71)</f>
         <v>-48.881382900000006</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6">
       <c r="A72" s="11">
         <v>45943.415277777778</v>
       </c>
       <c r="B72" t="s">
         <v>36</v>
       </c>
-      <c r="C72" s="2">
+      <c r="C72" s="12">
         <v>183.36</v>
       </c>
       <c r="D72" s="6">
         <v>0.16197</v>
       </c>
-      <c r="E72" s="6">
-        <f>IF(F72="Sell",-C72*D72,C72*D72)</f>
+      <c r="E72" s="12">
+        <f>IF(F72="Sell",D72*C72*-1,D72*C72)</f>
         <v>-29.698819200000003</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6">
       <c r="A73" s="11">
         <v>45943.417361111111</v>
       </c>
       <c r="B73" t="s">
         <v>27</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C73" s="12">
         <v>70.52</v>
       </c>
       <c r="D73" s="6">
         <v>0.40042</v>
       </c>
-      <c r="E73" s="6">
-        <f>IF(F73="Sell",-C73*D73,C73*D73)</f>
+      <c r="E73" s="12">
+        <f>IF(F73="Sell",D73*C73*-1,D73*C73)</f>
         <v>-28.237618399999999</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6">
       <c r="A74" s="11">
         <v>45946.399305555555</v>
       </c>
       <c r="B74" t="s">
         <v>52</v>
       </c>
-      <c r="C74" s="2">
+      <c r="C74" s="12">
         <v>41.11</v>
       </c>
       <c r="D74" s="6">
         <v>3.93</v>
       </c>
-      <c r="E74" s="6">
-        <f>IF(F74="Sell",-C74*D74,C74*D74)</f>
+      <c r="E74" s="12">
+        <f>IF(F74="Sell",D74*C74*-1,D74*C74)</f>
         <v>161.56229999999999</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6">
       <c r="A75" s="11">
         <v>45957.457638888889</v>
       </c>
       <c r="B75" t="s">
         <v>47</v>
       </c>
-      <c r="C75" s="2">
+      <c r="C75" s="12">
         <v>192.61</v>
       </c>
       <c r="D75" s="6">
         <v>1</v>
       </c>
-      <c r="E75" s="6">
-        <f>IF(F75="Sell",-C75*D75,C75*D75)</f>
+      <c r="E75" s="12">
+        <f>IF(F75="Sell",D75*C75*-1,D75*C75)</f>
         <v>-192.61</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6">
       <c r="A76" s="11">
         <v>45957.459722222222</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C76" s="12">
         <v>10.29</v>
       </c>
       <c r="D76" s="6">
         <v>6.83</v>
       </c>
-      <c r="E76" s="6">
-        <f>IF(F76="Sell",-C76*D76,C76*D76)</f>
+      <c r="E76" s="12">
+        <f>IF(F76="Sell",D76*C76*-1,D76*C76)</f>
         <v>-70.280699999999996</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6">
       <c r="A77" s="11">
         <v>45957.460416666669</v>
       </c>
       <c r="B77" t="s">
         <v>33</v>
       </c>
-      <c r="C77" s="2">
+      <c r="C77" s="12">
         <v>12.12</v>
       </c>
       <c r="D77" s="6">
         <v>7.35</v>
       </c>
-      <c r="E77" s="6">
-        <f>IF(F77="Sell",-C77*D77,C77*D77)</f>
+      <c r="E77" s="12">
+        <f>IF(F77="Sell",D77*C77*-1,D77*C77)</f>
         <v>-89.081999999999994</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6">
       <c r="A78" s="11">
         <v>45957.462500000001</v>
       </c>
       <c r="B78" t="s">
         <v>10</v>
       </c>
-      <c r="C78" s="2">
+      <c r="C78" s="12">
         <v>365.94</v>
       </c>
       <c r="D78" s="6">
         <v>1.76</v>
       </c>
-      <c r="E78" s="6">
-        <f>IF(F78="Sell",-C78*D78,C78*D78)</f>
+      <c r="E78" s="12">
+        <f>IF(F78="Sell",D78*C78*-1,D78*C78)</f>
         <v>-644.05439999999999</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6">
       <c r="A79" s="11">
         <v>45957.463194444441</v>
       </c>
       <c r="B79" t="s">
         <v>51</v>
       </c>
-      <c r="C79" s="2">
+      <c r="C79" s="12">
         <v>122.97</v>
       </c>
       <c r="D79" s="6">
         <v>0.95403000000000004</v>
       </c>
-      <c r="E79" s="6">
-        <f>IF(F79="Sell",-C79*D79,C79*D79)</f>
+      <c r="E79" s="12">
+        <f>IF(F79="Sell",D79*C79*-1,D79*C79)</f>
         <v>-117.3170691</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6">
       <c r="A80" s="11">
         <v>45957.463888888888</v>
       </c>
       <c r="B80" t="s">
         <v>29</v>
       </c>
-      <c r="C80" s="2">
+      <c r="C80" s="12">
         <v>41.78</v>
       </c>
       <c r="D80" s="6">
         <v>1.33</v>
       </c>
-      <c r="E80" s="6">
-        <f>IF(F80="Sell",-C80*D80,C80*D80)</f>
+      <c r="E80" s="12">
+        <f>IF(F80="Sell",D80*C80*-1,D80*C80)</f>
         <v>-55.567400000000006</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" s="11">
         <v>45957.464583333334</v>
       </c>
       <c r="B81" t="s">
         <v>30</v>
       </c>
-      <c r="C81" s="2">
+      <c r="C81" s="12">
         <v>12.92</v>
       </c>
       <c r="D81" s="6">
         <v>1.53</v>
       </c>
-      <c r="E81" s="6">
-        <f>IF(F81="Sell",-C81*D81,C81*D81)</f>
+      <c r="E81" s="12">
+        <f>IF(F81="Sell",D81*C81*-1,D81*C81)</f>
         <v>-19.767600000000002</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82" s="11">
         <v>45957.464583333334</v>
       </c>
       <c r="B82" t="s">
         <v>40</v>
       </c>
-      <c r="C82" s="2">
+      <c r="C82" s="12">
         <v>2277.38</v>
       </c>
       <c r="D82" s="6">
         <v>8.4499999999999992E-3</v>
       </c>
-      <c r="E82" s="6">
-        <f>IF(F82="Sell",-C82*D82,C82*D82)</f>
+      <c r="E82" s="12">
+        <f>IF(F82="Sell",D82*C82*-1,D82*C82)</f>
         <v>-19.243860999999999</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" s="11">
         <v>45957.470833333333</v>
       </c>
       <c r="B83" t="s">
         <v>14</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83" s="12">
         <v>52.74</v>
       </c>
       <c r="D83" s="6">
         <v>0.44206000000000001</v>
       </c>
-      <c r="E83" s="6">
-        <f>IF(F83="Sell",-C83*D83,C83*D83)</f>
+      <c r="E83" s="12">
+        <f>IF(F83="Sell",D83*C83*-1,D83*C83)</f>
         <v>-23.3142444</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84" s="11">
         <v>45957.470833333333</v>
       </c>
       <c r="B84" t="s">
         <v>49</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84" s="12">
         <v>4.84</v>
       </c>
       <c r="D84" s="6">
         <v>5</v>
       </c>
-      <c r="E84" s="6">
-        <f>IF(F84="Sell",-C84*D84,C84*D84)</f>
+      <c r="E84" s="12">
+        <f>IF(F84="Sell",D84*C84*-1,D84*C84)</f>
         <v>-24.2</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85" s="11">
         <v>45957.47152777778</v>
       </c>
       <c r="B85" t="s">
         <v>44</v>
       </c>
-      <c r="C85" s="2">
+      <c r="C85" s="12">
         <v>52.95</v>
       </c>
       <c r="D85" s="6">
         <v>1</v>
       </c>
-      <c r="E85" s="6">
-        <f>IF(F85="Sell",-C85*D85,C85*D85)</f>
+      <c r="E85" s="12">
+        <f>IF(F85="Sell",D85*C85*-1,D85*C85)</f>
         <v>-52.95</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6">
       <c r="A86" s="11">
         <v>45958.512499999997</v>
       </c>
       <c r="B86" t="s">
         <v>18</v>
       </c>
-      <c r="C86" s="2">
+      <c r="C86" s="12">
         <v>541.79</v>
       </c>
       <c r="D86" s="6">
         <v>0.96050999999999997</v>
       </c>
-      <c r="E86" s="6">
-        <f>IF(F86="Sell",-C86*D86,C86*D86)</f>
+      <c r="E86" s="12">
+        <f>IF(F86="Sell",D86*C86*-1,D86*C86)</f>
         <v>520.39471289999994</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6">
       <c r="A87" s="11">
         <v>45958.515277777777</v>
       </c>
       <c r="B87" t="s">
         <v>35</v>
       </c>
-      <c r="C87" s="2">
+      <c r="C87" s="12">
         <v>89.79</v>
       </c>
       <c r="D87" s="6">
         <v>2.65</v>
       </c>
-      <c r="E87" s="6">
-        <f>IF(F87="Sell",-C87*D87,C87*D87)</f>
+      <c r="E87" s="12">
+        <f>IF(F87="Sell",D87*C87*-1,D87*C87)</f>
         <v>237.9435</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6">
       <c r="A88" s="11">
         <v>45958.517361111109</v>
       </c>
       <c r="B88" t="s">
         <v>21</v>
       </c>
-      <c r="C88" s="2">
+      <c r="C88" s="12">
         <v>266.82</v>
       </c>
       <c r="D88" s="6">
         <v>1.2</v>
       </c>
-      <c r="E88" s="6">
-        <f>IF(F88="Sell",-C88*D88,C88*D88)</f>
+      <c r="E88" s="12">
+        <f>IF(F88="Sell",D88*C88*-1,D88*C88)</f>
         <v>320.18399999999997</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89" s="11">
         <v>45958.520138888889</v>
       </c>
       <c r="B89" t="s">
         <v>31</v>
       </c>
-      <c r="C89" s="2">
+      <c r="C89" s="12">
         <v>188.92</v>
       </c>
       <c r="D89" s="6">
         <v>0.12581000000000001</v>
       </c>
-      <c r="E89" s="6">
-        <f>IF(F89="Sell",-C89*D89,C89*D89)</f>
+      <c r="E89" s="12">
+        <f>IF(F89="Sell",D89*C89*-1,D89*C89)</f>
         <v>-23.7680252</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90" s="11">
         <v>45958.522222222222</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
       </c>
-      <c r="C90" s="2">
+      <c r="C90" s="12">
         <v>465.39</v>
       </c>
       <c r="D90" s="6">
         <v>5.8790000000000002E-2</v>
       </c>
-      <c r="E90" s="6">
-        <f>IF(F90="Sell",-C90*D90,C90*D90)</f>
+      <c r="E90" s="12">
+        <f>IF(F90="Sell",D90*C90*-1,D90*C90)</f>
         <v>-27.360278099999999</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91" s="11">
         <v>45958.522222222222</v>
       </c>
       <c r="B91" t="s">
         <v>15</v>
       </c>
-      <c r="C91" s="2">
+      <c r="C91" s="12">
         <v>51.12</v>
       </c>
       <c r="D91" s="6">
         <v>0.55984</v>
       </c>
-      <c r="E91" s="6">
-        <f>IF(F91="Sell",-C91*D91,C91*D91)</f>
+      <c r="E91" s="12">
+        <f>IF(F91="Sell",D91*C91*-1,D91*C91)</f>
         <v>-28.619020799999998</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92" s="11">
         <v>45958.529166666667</v>
       </c>
       <c r="B92" t="s">
         <v>53</v>
       </c>
-      <c r="C92" s="2">
+      <c r="C92" s="12">
         <v>55.54</v>
       </c>
       <c r="D92" s="6">
         <v>3</v>
       </c>
-      <c r="E92" s="6">
-        <f>IF(F92="Sell",-C92*D92,C92*D92)</f>
+      <c r="E92" s="12">
+        <f>IF(F92="Sell",D92*C92*-1,D92*C92)</f>
         <v>166.62</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93" s="11">
         <v>45965.642361111109</v>
       </c>
       <c r="B93" t="s">
         <v>6</v>
       </c>
-      <c r="C93" s="2">
+      <c r="C93" s="12">
         <v>57.69</v>
       </c>
       <c r="D93" s="6">
         <v>1.84</v>
       </c>
-      <c r="E93" s="6">
-        <f>IF(F93="Sell",-C93*D93,C93*D93)</f>
+      <c r="E93" s="12">
+        <f>IF(F93="Sell",D93*C93*-1,D93*C93)</f>
         <v>106.14960000000001</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94" s="11">
         <v>45974.67291666667</v>
       </c>
       <c r="B94" t="s">
         <v>6</v>
       </c>
-      <c r="C94" s="2">
+      <c r="C94" s="12">
         <v>55.85</v>
       </c>
       <c r="D94" s="6">
         <v>0.69955000000000001</v>
       </c>
-      <c r="E94" s="6">
-        <f>IF(F94="Sell",-C94*D94,C94*D94)</f>
+      <c r="E94" s="12">
+        <f>IF(F94="Sell",D94*C94*-1,D94*C94)</f>
         <v>39.069867500000001</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95" s="11">
         <v>46002.439583333333</v>
       </c>
       <c r="B95" t="s">
         <v>34</v>
       </c>
-      <c r="C95" s="2">
+      <c r="C95" s="12">
         <v>41.27</v>
       </c>
       <c r="D95" s="6">
         <v>2.08</v>
       </c>
-      <c r="E95" s="6">
-        <f>IF(F95="Sell",-C95*D95,C95*D95)</f>
+      <c r="E95" s="12">
+        <f>IF(F95="Sell",D95*C95*-1,D95*C95)</f>
         <v>85.841600000000014</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96" s="11">
         <v>46002.442361111112</v>
       </c>
       <c r="B96" t="s">
         <v>12</v>
       </c>
-      <c r="C96" s="2">
+      <c r="C96" s="12">
         <v>685.2</v>
       </c>
       <c r="D96" s="6">
         <v>0.72970000000000002</v>
       </c>
-      <c r="E96" s="6">
-        <f>IF(F96="Sell",-C96*D96,C96*D96)</f>
+      <c r="E96" s="12">
+        <f>IF(F96="Sell",D96*C96*-1,D96*C96)</f>
         <v>499.99044000000004</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97" s="11">
         <v>46002.443749999999</v>
       </c>
       <c r="B97" t="s">
         <v>6</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97" s="12">
         <v>51.34</v>
       </c>
       <c r="D97" s="6">
         <v>2.41</v>
       </c>
-      <c r="E97" s="6">
-        <f>IF(F97="Sell",-C97*D97,C97*D97)</f>
+      <c r="E97" s="12">
+        <f>IF(F97="Sell",D97*C97*-1,D97*C97)</f>
         <v>123.72940000000001</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98" s="11">
         <v>46002.446527777778</v>
       </c>
       <c r="B98" t="s">
         <v>8</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98" s="12">
         <v>24.08</v>
       </c>
       <c r="D98" s="6">
         <v>6.77</v>
       </c>
-      <c r="E98" s="6">
-        <f>IF(F98="Sell",-C98*D98,C98*D98)</f>
+      <c r="E98" s="12">
+        <f>IF(F98="Sell",D98*C98*-1,D98*C98)</f>
         <v>163.02159999999998</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99" s="11">
         <v>46008.648611111108</v>
       </c>
       <c r="B99" t="s">
         <v>8</v>
       </c>
-      <c r="C99" s="2">
+      <c r="C99" s="12">
         <v>21.11</v>
       </c>
       <c r="D99" s="6">
         <v>2</v>
       </c>
-      <c r="E99" s="6">
-        <f>IF(F99="Sell",-C99*D99,C99*D99)</f>
+      <c r="E99" s="12">
+        <f>IF(F99="Sell",D99*C99*-1,D99*C99)</f>
         <v>42.22</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100" s="11">
         <v>46008.650694444441</v>
       </c>
       <c r="B100" t="s">
         <v>6</v>
       </c>
-      <c r="C100" s="2">
+      <c r="C100" s="12">
         <v>48.49</v>
       </c>
       <c r="D100" s="6">
         <v>1.79</v>
       </c>
-      <c r="E100" s="6">
-        <f>IF(F100="Sell",-C100*D100,C100*D100)</f>
+      <c r="E100" s="12">
+        <f>IF(F100="Sell",D100*C100*-1,D100*C100)</f>
         <v>86.7971</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101" s="11">
         <v>46020.463888888888</v>
       </c>
       <c r="B101" t="s">
         <v>46</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101" s="12">
         <v>59.54</v>
       </c>
       <c r="D101" s="6">
         <v>1</v>
       </c>
-      <c r="E101" s="6">
-        <f>IF(F101="Sell",-C101*D101,C101*D101)</f>
+      <c r="E101" s="12">
+        <f>IF(F101="Sell",D101*C101*-1,D101*C101)</f>
         <v>-59.54</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102" s="11">
         <v>46021.472916666666</v>
       </c>
       <c r="B102" t="s">
         <v>16</v>
       </c>
-      <c r="C102" s="2">
+      <c r="C102" s="12">
         <v>5.69</v>
       </c>
       <c r="D102" s="6">
         <v>9.9</v>
       </c>
-      <c r="E102" s="6">
-        <f>IF(F102="Sell",-C102*D102,C102*D102)</f>
+      <c r="E102" s="12">
+        <f>IF(F102="Sell",D102*C102*-1,D102*C102)</f>
         <v>56.331000000000003</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103" s="11">
         <v>46027.567361111112</v>
       </c>
       <c r="B103" t="s">
         <v>45</v>
       </c>
-      <c r="C103" s="2">
+      <c r="C103" s="12">
         <v>11.24</v>
       </c>
       <c r="D103" s="6">
         <v>1.56</v>
       </c>
-      <c r="E103" s="6">
-        <f>IF(F103="Sell",-C103*D103,C103*D103)</f>
+      <c r="E103" s="12">
+        <f>IF(F103="Sell",D103*C103*-1,D103*C103)</f>
         <v>-17.534400000000002</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104" s="11">
         <v>46027.568055555559</v>
       </c>
       <c r="B104" t="s">
         <v>22</v>
       </c>
-      <c r="C104" s="2">
+      <c r="C104" s="12">
         <v>233.54</v>
       </c>
       <c r="D104" s="6">
         <v>0.13278000000000001</v>
       </c>
-      <c r="E104" s="6">
-        <f>IF(F104="Sell",-C104*D104,C104*D104)</f>
+      <c r="E104" s="12">
+        <f>IF(F104="Sell",D104*C104*-1,D104*C104)</f>
         <v>-31.009441200000001</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105" s="11">
         <v>46027.568749999999</v>
       </c>
       <c r="B105" t="s">
         <v>48</v>
       </c>
-      <c r="C105" s="2">
+      <c r="C105" s="12">
         <v>36.83</v>
       </c>
       <c r="D105" s="6">
         <v>1</v>
       </c>
-      <c r="E105" s="6">
-        <f>IF(F105="Sell",-C105*D105,C105*D105)</f>
+      <c r="E105" s="12">
+        <f>IF(F105="Sell",D105*C105*-1,D105*C105)</f>
         <v>-36.83</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106" s="11">
         <v>46029.449305555558</v>
       </c>
       <c r="B106" t="s">
         <v>24</v>
       </c>
-      <c r="C106" s="2">
+      <c r="C106" s="12">
         <v>100.39</v>
       </c>
       <c r="D106" s="6">
         <v>1.07</v>
       </c>
-      <c r="E106" s="6">
-        <f>IF(F106="Sell",-C106*D106,C106*D106)</f>
+      <c r="E106" s="12">
+        <f>IF(F106="Sell",D106*C106*-1,D106*C106)</f>
         <v>-107.41730000000001</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107" s="11">
         <v>46034.47152777778</v>
       </c>
       <c r="B107" t="s">
         <v>42</v>
       </c>
-      <c r="C107" s="2">
+      <c r="C107" s="12">
         <v>625.9</v>
       </c>
       <c r="D107" s="6">
         <v>0.29479</v>
       </c>
-      <c r="E107" s="6">
-        <f>IF(F107="Sell",-C107*D107,C107*D107)</f>
+      <c r="E107" s="12">
+        <f>IF(F107="Sell",D107*C107*-1,D107*C107)</f>
         <v>-184.509061</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6">
       <c r="A108" s="11">
         <v>46034.47152777778</v>
       </c>
       <c r="B108" t="s">
         <v>9</v>
       </c>
-      <c r="C108" s="2">
+      <c r="C108" s="12">
         <v>342</v>
       </c>
       <c r="D108" s="6">
         <v>1.25</v>
       </c>
-      <c r="E108" s="6">
-        <f>IF(F108="Sell",-C108*D108,C108*D108)</f>
+      <c r="E108" s="12">
+        <f>IF(F108="Sell",D108*C108*-1,D108*C108)</f>
         <v>-427.5</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109" s="11">
         <v>46035.44027777778</v>
       </c>
       <c r="B109" t="s">
         <v>34</v>
       </c>
-      <c r="C109" s="2">
+      <c r="C109" s="12">
         <v>49.47</v>
       </c>
       <c r="D109" s="6">
         <v>5.29</v>
       </c>
-      <c r="E109" s="6">
-        <f>IF(F109="Sell",-C109*D109,C109*D109)</f>
+      <c r="E109" s="12">
+        <f>IF(F109="Sell",D109*C109*-1,D109*C109)</f>
         <v>261.69630000000001</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110" s="11">
         <v>46035.441666666666</v>
       </c>
       <c r="B110" t="s">
         <v>52</v>
       </c>
-      <c r="C110" s="2">
+      <c r="C110" s="12">
         <v>56.67</v>
       </c>
       <c r="D110" s="6">
         <v>4.8600000000000003</v>
       </c>
-      <c r="E110" s="6">
-        <f>IF(F110="Sell",-C110*D110,C110*D110)</f>
+      <c r="E110" s="12">
+        <f>IF(F110="Sell",D110*C110*-1,D110*C110)</f>
         <v>275.4162</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111" s="11">
         <v>46036.448611111111</v>
       </c>
       <c r="B111" t="s">
         <v>54</v>
       </c>
-      <c r="C111" s="2">
+      <c r="C111" s="12">
         <v>183.13</v>
       </c>
       <c r="D111" s="6">
         <v>1.47</v>
       </c>
-      <c r="E111" s="6">
-        <f>IF(F111="Sell",-C111*D111,C111*D111)</f>
+      <c r="E111" s="12">
+        <f>IF(F111="Sell",D111*C111*-1,D111*C111)</f>
         <v>269.2011</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112" s="11">
         <v>46042.44027777778</v>
       </c>
       <c r="B112" t="s">
         <v>33</v>
       </c>
-      <c r="C112" s="2">
+      <c r="C112" s="12">
         <v>27.75</v>
       </c>
       <c r="D112" s="6">
         <v>10.81</v>
       </c>
-      <c r="E112" s="6">
-        <f>IF(F112="Sell",-C112*D112,C112*D112)</f>
+      <c r="E112" s="12">
+        <f>IF(F112="Sell",D112*C112*-1,D112*C112)</f>
         <v>299.97750000000002</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6">
       <c r="A113" s="11">
         <v>46042.441666666666</v>
       </c>
       <c r="B113" t="s">
         <v>13</v>
       </c>
-      <c r="C113" s="2">
+      <c r="C113" s="12">
         <v>14.93</v>
       </c>
       <c r="D113" s="6">
         <v>20.09</v>
       </c>
-      <c r="E113" s="6">
-        <f>IF(F113="Sell",-C113*D113,C113*D113)</f>
+      <c r="E113" s="12">
+        <f>IF(F113="Sell",D113*C113*-1,D113*C113)</f>
         <v>299.94369999999998</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6">
       <c r="A114" s="11">
         <v>46042.45</v>
       </c>
       <c r="B114" t="s">
         <v>55</v>
       </c>
-      <c r="C114" s="2">
+      <c r="C114" s="12">
         <v>376.93</v>
       </c>
       <c r="D114" s="6">
         <v>1</v>
       </c>
-      <c r="E114" s="6">
-        <f>IF(F114="Sell",-C114*D114,C114*D114)</f>
+      <c r="E114" s="12">
+        <f>IF(F114="Sell",D114*C114*-1,D114*C114)</f>
         <v>376.93</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6">
       <c r="A115" s="11">
         <v>46044.496527777781</v>
       </c>
       <c r="B115" t="s">
         <v>6</v>
       </c>
-      <c r="C115" s="2">
+      <c r="C115" s="12">
         <v>50.4</v>
       </c>
       <c r="D115" s="6">
         <v>9.9</v>
       </c>
-      <c r="E115" s="6">
-        <f>IF(F115="Sell",-C115*D115,C115*D115)</f>
+      <c r="E115" s="12">
+        <f>IF(F115="Sell",D115*C115*-1,D115*C115)</f>
         <v>-498.96</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6">
       <c r="A116" s="11">
         <v>46044.49722222222</v>
       </c>
       <c r="B116" t="s">
         <v>8</v>
       </c>
-      <c r="C116" s="2">
+      <c r="C116" s="12">
         <v>22.18</v>
       </c>
       <c r="D116" s="6">
         <v>15.11</v>
       </c>
-      <c r="E116" s="6">
-        <f>IF(F116="Sell",-C116*D116,C116*D116)</f>
+      <c r="E116" s="12">
+        <f>IF(F116="Sell",D116*C116*-1,D116*C116)</f>
         <v>-335.13979999999998</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6">
       <c r="A117" s="11">
         <v>46045.445833333331</v>
       </c>
       <c r="B117" t="s">
         <v>56</v>
       </c>
-      <c r="C117" s="2">
+      <c r="C117" s="12">
         <v>70</v>
       </c>
       <c r="D117" s="6">
         <v>5.71</v>
       </c>
-      <c r="E117" s="6">
-        <f>IF(F117="Sell",-C117*D117,C117*D117)</f>
+      <c r="E117" s="12">
+        <f>IF(F117="Sell",D117*C117*-1,D117*C117)</f>
         <v>399.7</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6">
       <c r="A118" s="11">
         <v>46045.493055555555</v>
       </c>
       <c r="B118" t="s">
         <v>19</v>
       </c>
-      <c r="C118" s="2">
+      <c r="C118" s="12">
         <v>659.79</v>
       </c>
       <c r="D118" s="6">
         <v>0.78064</v>
       </c>
-      <c r="E118" s="6">
-        <f>IF(F118="Sell",-C118*D118,C118*D118)</f>
+      <c r="E118" s="12">
+        <f>IF(F118="Sell",D118*C118*-1,D118*C118)</f>
         <v>515.05846559999998</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6">
       <c r="A119" s="11">
         <v>46048.572222222225</v>
       </c>
       <c r="B119" t="s">
         <v>35</v>
       </c>
-      <c r="C119" s="2">
+      <c r="C119" s="12">
         <v>80.680000000000007</v>
       </c>
       <c r="D119" s="6">
         <v>4</v>
       </c>
-      <c r="E119" s="6">
-        <f>IF(F119="Sell",-C119*D119,C119*D119)</f>
+      <c r="E119" s="12">
+        <f>IF(F119="Sell",D119*C119*-1,D119*C119)</f>
         <v>-322.72000000000003</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6">
       <c r="A120" s="11">
         <v>46049.448611111111</v>
       </c>
       <c r="B120" t="s">
         <v>57</v>
       </c>
-      <c r="C120" s="2">
+      <c r="C120" s="12">
         <v>89.38</v>
       </c>
       <c r="D120" s="6">
         <v>3.6</v>
       </c>
-      <c r="E120" s="6">
-        <f>IF(F120="Sell",-C120*D120,C120*D120)</f>
+      <c r="E120" s="12">
+        <f>IF(F120="Sell",D120*C120*-1,D120*C120)</f>
         <v>321.76799999999997</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6">
       <c r="A121" s="11">
         <v>46050.563888888886</v>
       </c>
       <c r="B121" t="s">
         <v>54</v>
       </c>
-      <c r="C121" s="2">
+      <c r="C121" s="12">
         <v>159.22999999999999</v>
       </c>
       <c r="D121" s="6">
         <v>1.47</v>
       </c>
-      <c r="E121" s="6">
-        <f>IF(F121="Sell",-C121*D121,C121*D121)</f>
+      <c r="E121" s="12">
+        <f>IF(F121="Sell",D121*C121*-1,D121*C121)</f>
         <v>-234.06809999999999</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6">
       <c r="A122" s="11">
         <v>46055.650694444441</v>
       </c>
       <c r="B122" t="s">
         <v>19</v>
       </c>
-      <c r="C122" s="2">
+      <c r="C122" s="12">
         <v>711.77</v>
       </c>
       <c r="D122" s="6">
         <v>0.91229000000000005</v>
       </c>
-      <c r="E122" s="6">
-        <f>IF(F122="Sell",-C122*D122,C122*D122)</f>
+      <c r="E122" s="12">
+        <f>IF(F122="Sell",D122*C122*-1,D122*C122)</f>
         <v>-649.34065329999999</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6">
       <c r="A123" s="11">
         <v>46055.652083333334</v>
       </c>
       <c r="B123" t="s">
         <v>16</v>
       </c>
-      <c r="C123" s="2">
+      <c r="C123" s="12">
         <v>4.96</v>
       </c>
       <c r="D123" s="6">
         <v>47.2</v>
       </c>
-      <c r="E123" s="6">
-        <f>IF(F123="Sell",-C123*D123,C123*D123)</f>
+      <c r="E123" s="12">
+        <f>IF(F123="Sell",D123*C123*-1,D123*C123)</f>
         <v>234.11200000000002</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6">
       <c r="A124" s="11">
         <v>46059.484722222223</v>
       </c>
       <c r="B124" t="s">
         <v>53</v>
       </c>
-      <c r="C124" s="2">
+      <c r="C124" s="12">
         <v>59.58</v>
       </c>
       <c r="D124" s="6">
         <v>10.89</v>
       </c>
-      <c r="E124" s="6">
-        <f>IF(F124="Sell",-C124*D124,C124*D124)</f>
+      <c r="E124" s="12">
+        <f>IF(F124="Sell",D124*C124*-1,D124*C124)</f>
         <v>648.82619999999997</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6">
       <c r="A125" s="11">
         <v>46083.456250000003</v>
       </c>
       <c r="B125" t="s">
         <v>58</v>
       </c>
-      <c r="C125" s="2">
+      <c r="C125" s="12">
         <v>160.21</v>
       </c>
       <c r="D125" s="6">
         <v>3</v>
       </c>
-      <c r="E125" s="6">
-        <f>IF(F125="Sell",-C125*D125,C125*D125)</f>
+      <c r="E125" s="12">
+        <f>IF(F125="Sell",D125*C125*-1,D125*C125)</f>
         <v>480.63</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6">
       <c r="A126" s="11">
         <v>46086.664583333331</v>
       </c>
       <c r="B126" t="s">
         <v>27</v>
       </c>
-      <c r="C126" s="2">
+      <c r="C126" s="12">
         <v>98.34</v>
       </c>
       <c r="D126" s="6">
         <v>1.77</v>
       </c>
-      <c r="E126" s="6">
-        <f>IF(F126="Sell",-C126*D126,C126*D126)</f>
+      <c r="E126" s="12">
+        <f>IF(F126="Sell",D126*C126*-1,D126*C126)</f>
         <v>174.06180000000001</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6">
       <c r="A127" s="11">
         <v>46087.525000000001</v>
       </c>
       <c r="B127" t="s">
         <v>33</v>
       </c>
-      <c r="C127" s="2">
+      <c r="C127" s="12">
         <v>20.58</v>
       </c>
       <c r="D127" s="6">
         <v>10.81</v>
       </c>
-      <c r="E127" s="6">
-        <f>IF(F127="Sell",-C127*D127,C127*D127)</f>
+      <c r="E127" s="12">
+        <f>IF(F127="Sell",D127*C127*-1,D127*C127)</f>
         <v>-222.46979999999999</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6">
       <c r="A128" s="11">
         <v>46087.525694444441</v>
       </c>
       <c r="B128" t="s">
         <v>57</v>
       </c>
-      <c r="C128" s="2">
+      <c r="C128" s="12">
         <v>80.78</v>
       </c>
       <c r="D128" s="6">
         <v>3.6</v>
       </c>
-      <c r="E128" s="6">
-        <f>IF(F128="Sell",-C128*D128,C128*D128)</f>
+      <c r="E128" s="12">
+        <f>IF(F128="Sell",D128*C128*-1,D128*C128)</f>
         <v>-290.80799999999999</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6">
       <c r="A129" s="11">
         <v>46087.526388888888</v>
       </c>
       <c r="B129" t="s">
         <v>56</v>
       </c>
-      <c r="C129" s="2">
+      <c r="C129" s="12">
         <v>81.02</v>
       </c>
       <c r="D129" s="6">
         <v>5.71</v>
       </c>
-      <c r="E129" s="6">
-        <f>IF(F129="Sell",-C129*D129,C129*D129)</f>
+      <c r="E129" s="12">
+        <f>IF(F129="Sell",D129*C129*-1,D129*C129)</f>
         <v>-462.62419999999997</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6">
       <c r="A130" s="11">
         <v>46087.527777777781</v>
       </c>
       <c r="B130" t="s">
         <v>52</v>
       </c>
-      <c r="C130" s="2">
+      <c r="C130" s="12">
         <v>59.68</v>
       </c>
       <c r="D130" s="6">
         <v>8.81</v>
       </c>
-      <c r="E130" s="6">
-        <f>IF(F130="Sell",-C130*D130,C130*D130)</f>
+      <c r="E130" s="12">
+        <f>IF(F130="Sell",D130*C130*-1,D130*C130)</f>
         <v>-525.7808</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6">
       <c r="A131" s="11">
         <v>46087.52847222222</v>
       </c>
       <c r="B131" t="s">
         <v>13</v>
       </c>
-      <c r="C131" s="2">
+      <c r="C131" s="12">
         <v>16.579999999999998</v>
       </c>
       <c r="D131" s="6">
         <v>20.09</v>
       </c>
-      <c r="E131" s="6">
-        <f>IF(F131="Sell",-C131*D131,C131*D131)</f>
+      <c r="E131" s="12">
+        <f>IF(F131="Sell",D131*C131*-1,D131*C131)</f>
         <v>-333.09219999999999</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6">
       <c r="A132" s="11">
         <v>46087.52847222222</v>
       </c>
       <c r="B132" t="s">
         <v>34</v>
       </c>
-      <c r="C132" s="2">
+      <c r="C132" s="12">
         <v>45.39</v>
       </c>
       <c r="D132" s="6">
         <v>10.29</v>
       </c>
-      <c r="E132" s="6">
-        <f>IF(F132="Sell",-C132*D132,C132*D132)</f>
+      <c r="E132" s="12">
+        <f>IF(F132="Sell",D132*C132*-1,D132*C132)</f>
         <v>-467.06309999999996</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6">
       <c r="A133" s="11">
         <v>46087.529166666667</v>
       </c>
       <c r="B133" t="s">
         <v>21</v>
       </c>
-      <c r="C133" s="2">
+      <c r="C133" s="12">
         <v>299.41000000000003</v>
       </c>
       <c r="D133" s="6">
         <v>2</v>
       </c>
-      <c r="E133" s="6">
-        <f>IF(F133="Sell",-C133*D133,C133*D133)</f>
+      <c r="E133" s="12">
+        <f>IF(F133="Sell",D133*C133*-1,D133*C133)</f>
         <v>-598.82000000000005</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6">
       <c r="A134" s="11">
         <v>46090.397916666669</v>
       </c>
       <c r="B134" t="s">
         <v>53</v>
       </c>
-      <c r="C134" s="2">
+      <c r="C134" s="12">
         <v>56.81</v>
       </c>
       <c r="D134" s="6">
         <v>13.92</v>
       </c>
-      <c r="E134" s="6">
-        <f>IF(F134="Sell",-C134*D134,C134*D134)</f>
+      <c r="E134" s="12">
+        <f>IF(F134="Sell",D134*C134*-1,D134*C134)</f>
         <v>-790.79520000000002</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6">
       <c r="A135" s="11">
         <v>46090.400000000001</v>
       </c>
       <c r="B135" t="s">
         <v>27</v>
       </c>
-      <c r="C135" s="2">
+      <c r="C135" s="12">
         <v>116.49</v>
       </c>
       <c r="D135" s="6">
         <v>6.76</v>
       </c>
-      <c r="E135" s="6">
-        <f>IF(F135="Sell",-C135*D135,C135*D135)</f>
+      <c r="E135" s="12">
+        <f>IF(F135="Sell",D135*C135*-1,D135*C135)</f>
         <v>787.47239999999999</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6">
       <c r="A136" s="11">
         <v>46090.401388888888</v>
       </c>
       <c r="B136" t="s">
         <v>60</v>
       </c>
-      <c r="C136" s="2">
+      <c r="C136" s="12">
         <v>37.89</v>
       </c>
       <c r="D136" s="6">
         <v>13.19</v>
       </c>
-      <c r="E136" s="6">
-        <f>IF(F136="Sell",-C136*D136,C136*D136)</f>
+      <c r="E136" s="12">
+        <f>IF(F136="Sell",D136*C136*-1,D136*C136)</f>
         <v>499.76909999999998</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6">
       <c r="A137" s="11">
         <v>46090.402083333334</v>
       </c>
       <c r="B137" t="s">
         <v>59</v>
       </c>
-      <c r="C137" s="2">
+      <c r="C137" s="12">
         <v>63.36</v>
       </c>
       <c r="D137" s="6">
         <v>7.89</v>
       </c>
-      <c r="E137" s="6">
-        <f>IF(F137="Sell",-C137*D137,C137*D137)</f>
+      <c r="E137" s="12">
+        <f>IF(F137="Sell",D137*C137*-1,D137*C137)</f>
         <v>499.91039999999998</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6">
       <c r="A138" s="11">
         <v>46090.65347222222</v>
       </c>
       <c r="B138" t="s">
         <v>12</v>
       </c>
-      <c r="C138" s="2">
+      <c r="C138" s="12">
         <v>677.47</v>
       </c>
       <c r="D138" s="6">
         <v>1.64</v>
       </c>
-      <c r="E138" s="6">
-        <f>IF(F138="Sell",-C138*D138,C138*D138)</f>
+      <c r="E138" s="12">
+        <f>IF(F138="Sell",D138*C138*-1,D138*C138)</f>
         <v>1111.0508</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6">
       <c r="A139" s="11">
         <v>46091.431944444441</v>
       </c>
       <c r="B139" t="s">
         <v>58</v>
       </c>
-      <c r="C139" s="2">
+      <c r="C139" s="12">
         <v>158.78</v>
       </c>
       <c r="D139" s="6">
         <v>3</v>
       </c>
-      <c r="E139" s="6">
-        <f>IF(F139="Sell",-C139*D139,C139*D139)</f>
+      <c r="E139" s="12">
+        <f>IF(F139="Sell",D139*C139*-1,D139*C139)</f>
         <v>-476.34000000000003</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6">
       <c r="A140" s="11">
         <v>46091.434027777781</v>
       </c>
       <c r="B140" t="s">
         <v>60</v>
       </c>
-      <c r="C140" s="2">
+      <c r="C140" s="12">
         <v>37.1</v>
       </c>
       <c r="D140" s="6">
         <v>13.19</v>
       </c>
-      <c r="E140" s="6">
-        <f>IF(F140="Sell",-C140*D140,C140*D140)</f>
+      <c r="E140" s="12">
+        <f>IF(F140="Sell",D140*C140*-1,D140*C140)</f>
         <v>-489.34899999999999</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6">
       <c r="A141" s="11">
         <v>46091.436805555553</v>
       </c>
       <c r="B141" t="s">
         <v>55</v>
       </c>
-      <c r="C141" s="2">
+      <c r="C141" s="12">
         <v>410</v>
       </c>
       <c r="D141" s="6">
         <v>1.43</v>
       </c>
-      <c r="E141" s="6">
-        <f>IF(F141="Sell",-C141*D141,C141*D141)</f>
+      <c r="E141" s="12">
+        <f>IF(F141="Sell",D141*C141*-1,D141*C141)</f>
         <v>586.29999999999995</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6">
       <c r="A142" s="11">
         <v>46091.449305555558</v>
       </c>
       <c r="B142" t="s">
         <v>61</v>
       </c>
-      <c r="C142" s="2">
+      <c r="C142" s="12">
         <v>90.02</v>
       </c>
       <c r="D142" s="6">
         <v>5</v>
       </c>
-      <c r="E142" s="6">
-        <f>IF(F142="Sell",-C142*D142,C142*D142)</f>
+      <c r="E142" s="12">
+        <f>IF(F142="Sell",D142*C142*-1,D142*C142)</f>
         <v>450.09999999999997</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6">
       <c r="A143" s="11">
         <v>46091.54583333333</v>
       </c>
       <c r="B143" t="s">
         <v>59</v>
       </c>
-      <c r="C143" s="2">
+      <c r="C143" s="12">
         <v>59.09</v>
       </c>
       <c r="D143" s="6">
         <v>7.89</v>
       </c>
-      <c r="E143" s="6">
-        <f>IF(F143="Sell",-C143*D143,C143*D143)</f>
+      <c r="E143" s="12">
+        <f>IF(F143="Sell",D143*C143*-1,D143*C143)</f>
         <v>-466.2201</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6">
       <c r="A144" s="11">
         <v>46092.438194444447</v>
       </c>
       <c r="B144" t="s">
         <v>6</v>
       </c>
-      <c r="C144" s="2">
+      <c r="C144" s="12">
         <v>40.11</v>
       </c>
       <c r="D144" s="6">
         <v>24.92</v>
       </c>
-      <c r="E144" s="6">
-        <f>IF(F144="Sell",-C144*D144,C144*D144)</f>
+      <c r="E144" s="12">
+        <f>IF(F144="Sell",D144*C144*-1,D144*C144)</f>
         <v>999.5412</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6">
       <c r="A145" s="11">
         <v>46100.508333333331</v>
       </c>
       <c r="B145" t="s">
         <v>61</v>
       </c>
-      <c r="C145" s="2">
+      <c r="C145" s="12">
         <v>71.52</v>
       </c>
       <c r="D145" s="6">
         <v>5</v>
       </c>
-      <c r="E145" s="6">
-        <f>IF(F145="Sell",-C145*D145,C145*D145)</f>
+      <c r="E145" s="12">
+        <f>IF(F145="Sell",D145*C145*-1,D145*C145)</f>
         <v>-357.59999999999997</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6">
       <c r="A146" s="11">
         <v>46100.509027777778</v>
       </c>
       <c r="B146" t="s">
         <v>59</v>
       </c>
-      <c r="C146" s="2">
+      <c r="C146" s="12">
         <v>74.150000000000006</v>
       </c>
       <c r="D146" s="6">
         <v>7.21</v>
       </c>
-      <c r="E146" s="6">
-        <f>IF(F146="Sell",-C146*D146,C146*D146)</f>
+      <c r="E146" s="12">
+        <f>IF(F146="Sell",D146*C146*-1,D146*C146)</f>
         <v>534.62150000000008</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6">
       <c r="A147" s="11">
         <v>46113.460416666669</v>
       </c>
       <c r="B147" t="s">
         <v>27</v>
       </c>
-      <c r="C147" s="2">
+      <c r="C147" s="12">
         <v>123.39</v>
       </c>
       <c r="D147" s="6">
         <v>8.5399999999999991</v>
       </c>
-      <c r="E147" s="6">
-        <f>IF(F147="Sell",-C147*D147,C147*D147)</f>
+      <c r="E147" s="12">
+        <f>IF(F147="Sell",D147*C147*-1,D147*C147)</f>
         <v>-1053.7505999999998</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6">
       <c r="A148" s="11">
         <v>46113.463194444441</v>
       </c>
       <c r="B148" t="s">
         <v>59</v>
       </c>
-      <c r="C148" s="2">
+      <c r="C148" s="12">
         <v>71.459999999999994</v>
       </c>
       <c r="D148" s="6">
         <v>7.21</v>
       </c>
-      <c r="E148" s="6">
-        <f>IF(F148="Sell",-C148*D148,C148*D148)</f>
+      <c r="E148" s="12">
+        <f>IF(F148="Sell",D148*C148*-1,D148*C148)</f>
         <v>-515.22659999999996</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6">
       <c r="A149" s="11">
         <v>46113.464583333334</v>
       </c>
       <c r="B149" t="s">
         <v>16</v>
       </c>
-      <c r="C149" s="2">
+      <c r="C149" s="12">
         <v>4.78</v>
       </c>
       <c r="D149" s="6">
         <v>74</v>
       </c>
-      <c r="E149" s="6">
-        <f>IF(F149="Sell",-C149*D149,C149*D149)</f>
+      <c r="E149" s="12">
+        <f>IF(F149="Sell",D149*C149*-1,D149*C149)</f>
         <v>353.72</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6">
       <c r="A150" s="11">
         <v>46113.46597222222</v>
       </c>
       <c r="B150" t="s">
         <v>61</v>
       </c>
-      <c r="C150" s="2">
+      <c r="C150" s="12">
         <v>83.33</v>
       </c>
       <c r="D150" s="6">
         <v>6</v>
       </c>
-      <c r="E150" s="6">
-        <f>IF(F150="Sell",-C150*D150,C150*D150)</f>
+      <c r="E150" s="12">
+        <f>IF(F150="Sell",D150*C150*-1,D150*C150)</f>
         <v>499.98</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6">
       <c r="A151" s="11">
+        <v>46114.560416666667</v>
+      </c>
+      <c r="B151" t="s">
+        <v>18</v>
+      </c>
+      <c r="C151" s="12">
+        <v>371.51</v>
+      </c>
+      <c r="D151" s="6">
+        <v>1.92</v>
+      </c>
+      <c r="E151" s="12">
+        <f>IF(F151="Sell",D151*C151*-1,D151*C151)</f>
+        <v>713.29919999999993</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="11">
         <v>46128.462500000001</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B152" t="s">
         <v>43</v>
       </c>
-      <c r="C151" s="2">
+      <c r="C152" s="12">
         <v>175.27</v>
       </c>
-      <c r="D151" s="6">
+      <c r="D152" s="6">
         <v>3</v>
       </c>
-      <c r="E151" s="6">
-        <f>IF(F151="Sell",-C151*D151,C151*D151)</f>
+      <c r="E152" s="12">
+        <f>IF(F152="Sell",D152*C152*-1,D152*C152)</f>
         <v>525.81000000000006</v>
       </c>
-      <c r="F151" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="11">
+      <c r="F152" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="11">
         <v>46128.463888888888</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B153" t="s">
         <v>62</v>
       </c>
-      <c r="C152" s="2">
+      <c r="C153" s="12">
         <v>86.03</v>
       </c>
-      <c r="D152" s="6">
+      <c r="D153" s="6">
         <v>7.42</v>
       </c>
-      <c r="E152" s="6">
-        <f>IF(F152="Sell",-C152*D152,C152*D152)</f>
+      <c r="E153" s="12">
+        <f>IF(F153="Sell",D153*C153*-1,D153*C153)</f>
         <v>638.34259999999995</v>
       </c>
-      <c r="F152" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="11">
+      <c r="F153" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="11">
         <v>46150.423611111109</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B154" t="s">
         <v>16</v>
       </c>
-      <c r="C153" s="2">
+      <c r="C154" s="12">
         <v>4.8899999999999997</v>
       </c>
-      <c r="D153" s="6">
+      <c r="D154" s="6">
         <v>7.18</v>
       </c>
-      <c r="E153" s="6">
-        <f>IF(F153="Sell",-C153*D153,C153*D153)</f>
+      <c r="E154" s="12">
+        <f>IF(F154="Sell",D154*C154*-1,D154*C154)</f>
         <v>35.110199999999999</v>
       </c>
-      <c r="F153" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" s="11">
+      <c r="F154" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="11">
         <v>46153.446527777778</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B155" t="s">
         <v>63</v>
       </c>
-      <c r="C154" s="2">
+      <c r="C155" s="12">
         <v>91.94</v>
       </c>
-      <c r="D154" s="6">
+      <c r="D155" s="6">
         <v>6.52</v>
       </c>
-      <c r="E154" s="6">
-        <f>IF(F154="Sell",-C154*D154,C154*D154)</f>
+      <c r="E155" s="12">
+        <f>IF(F155="Sell",D155*C155*-1,D155*C155)</f>
         <v>599.44879999999989</v>
       </c>
-      <c r="F154" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="11">
+      <c r="F155" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" s="11">
         <v>46174.410416666666</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B156" t="s">
         <v>6</v>
       </c>
-      <c r="C155" s="2">
+      <c r="C156" s="12">
         <v>40.549999999999997</v>
       </c>
-      <c r="D155" s="6">
+      <c r="D156" s="6">
         <v>24.92</v>
       </c>
-      <c r="E155" s="6">
-        <f>IF(F155="Sell",-C155*D155,C155*D155)</f>
+      <c r="E156" s="12">
+        <f>IF(F156="Sell",D156*C156*-1,D156*C156)</f>
         <v>-1010.506</v>
       </c>
-      <c r="F155" s="2" t="s">
+      <c r="F156" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" s="11">
+    <row r="157" spans="1:6">
+      <c r="A157" s="11">
         <v>46175.486111111109</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B157" t="s">
         <v>64</v>
       </c>
-      <c r="C156" s="2">
+      <c r="C157" s="12">
         <v>231.27</v>
       </c>
-      <c r="D156" s="6">
+      <c r="D157" s="6">
         <v>2.5</v>
       </c>
-      <c r="E156" s="6">
-        <f>IF(F156="Sell",-C156*D156,C156*D156)</f>
+      <c r="E157" s="12">
+        <f>IF(F157="Sell",D157*C157*-1,D157*C157)</f>
         <v>578.17500000000007</v>
       </c>
-      <c r="F156" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" s="11">
+      <c r="F157" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" s="11">
         <v>46175.487500000003</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B158" t="s">
         <v>65</v>
       </c>
-      <c r="C157" s="2">
+      <c r="C158" s="12">
         <v>103.72</v>
       </c>
-      <c r="D157" s="6">
+      <c r="D158" s="6">
         <v>3.95</v>
       </c>
-      <c r="E157" s="6">
-        <f>IF(F157="Sell",-C157*D157,C157*D157)</f>
+      <c r="E158" s="12">
+        <f>IF(F158="Sell",D158*C158*-1,D158*C158)</f>
         <v>409.69400000000002</v>
       </c>
-      <c r="F157" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="11">
+      <c r="F158" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="11">
         <v>46177.450694444444</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B159" t="s">
         <v>55</v>
       </c>
-      <c r="C158" s="2">
+      <c r="C159" s="12">
         <v>992.87</v>
       </c>
-      <c r="D158" s="6">
+      <c r="D159" s="6">
         <v>2.4300000000000002</v>
       </c>
-      <c r="E158" s="6">
-        <f>IF(F158="Sell",-C158*D158,C158*D158)</f>
+      <c r="E159" s="12">
+        <f>IF(F159="Sell",D159*C159*-1,D159*C159)</f>
         <v>-2412.6741000000002</v>
       </c>
-      <c r="F158" s="2" t="s">
+      <c r="F159" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="11">
+    <row r="160" spans="1:6">
+      <c r="A160" s="11">
         <v>46181.434027777781</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B160" t="s">
         <v>66</v>
       </c>
-      <c r="C159" s="2">
+      <c r="C160" s="12">
         <v>99.23</v>
       </c>
-      <c r="D159" s="6">
+      <c r="D160" s="6">
         <v>10.07</v>
       </c>
-      <c r="E159" s="6">
-        <f>IF(F159="Sell",-C159*D159,C159*D159)</f>
+      <c r="E160" s="12">
+        <f>IF(F160="Sell",D160*C160*-1,D160*C160)</f>
         <v>999.24610000000007</v>
       </c>
-      <c r="F159" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="11">
+      <c r="F160" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" s="11">
         <v>46181.43472222222</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B161" t="s">
         <v>67</v>
       </c>
-      <c r="C160" s="2">
+      <c r="C161" s="12">
         <v>183.67</v>
       </c>
-      <c r="D160" s="6">
+      <c r="D161" s="6">
         <v>3</v>
       </c>
-      <c r="E160" s="6">
-        <f>IF(F160="Sell",-C160*D160,C160*D160)</f>
+      <c r="E161" s="12">
+        <f>IF(F161="Sell",D161*C161*-1,D161*C161)</f>
         <v>551.01</v>
       </c>
-      <c r="F160" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="11">
+      <c r="F161" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" s="11">
         <v>46204.443055555559</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B162" t="s">
         <v>18</v>
       </c>
-      <c r="C161" s="2">
+      <c r="C162" s="12">
         <v>383.64</v>
       </c>
-      <c r="D161" s="6">
+      <c r="D162" s="6">
         <v>2.3199999999999998</v>
       </c>
-      <c r="E161" s="6">
-        <f>IF(F161="Sell",-C161*D161,C161*D161)</f>
+      <c r="E162" s="12">
+        <f>IF(F162="Sell",D162*C162*-1,D162*C162)</f>
         <v>890.0447999999999</v>
       </c>
-      <c r="F161" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="11">
+      <c r="F162" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" s="11">
         <v>46227.419444444444</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B163" t="s">
         <v>67</v>
       </c>
-      <c r="C162" s="2">
+      <c r="C163" s="12">
         <v>161.18</v>
       </c>
-      <c r="D162" s="6">
+      <c r="D163" s="6">
         <v>3</v>
       </c>
-      <c r="E162" s="6">
-        <f>IF(F162="Sell",-C162*D162,C162*D162)</f>
+      <c r="E163" s="12">
+        <f>IF(F163="Sell",D163*C163*-1,D163*C163)</f>
         <v>-483.54</v>
       </c>
-      <c r="F162" s="2" t="s">
+      <c r="F163" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="11">
+    <row r="164" spans="1:6">
+      <c r="A164" s="11">
         <v>46230.398611111108</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B164" t="s">
         <v>16</v>
       </c>
-      <c r="C163" s="2">
+      <c r="C164" s="12">
         <v>3.98</v>
       </c>
-      <c r="D163" s="6">
+      <c r="D164" s="6">
         <v>121.42</v>
       </c>
-      <c r="E163" s="6">
-        <f>IF(F163="Sell",-C163*D163,C163*D163)</f>
+      <c r="E164" s="12">
+        <f>IF(F164="Sell",D164*C164*-1,D164*C164)</f>
         <v>483.2516</v>
       </c>
-      <c r="F163" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="11">
+      <c r="F164" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" s="11">
+        <v>46231.45</v>
+      </c>
+      <c r="B165" t="s">
+        <v>55</v>
+      </c>
+      <c r="C165" s="12">
+        <v>818.35</v>
+      </c>
+      <c r="D165" s="6">
+        <v>1.22</v>
+      </c>
+      <c r="E165" s="12">
+        <f>IF(F165="Sell",D165*C165*-1,D165*C165)</f>
+        <v>998.38700000000006</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" s="11">
         <v>46233.619444444441</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B166" t="s">
         <v>64</v>
       </c>
-      <c r="C164" s="2">
+      <c r="C166" s="12">
         <v>232.31</v>
       </c>
-      <c r="D164" s="6">
+      <c r="D166" s="6">
         <v>2.5</v>
       </c>
-      <c r="E164" s="6">
-        <f>IF(F164="Sell",-C164*D164,C164*D164)</f>
+      <c r="E166" s="12">
+        <f>IF(F166="Sell",D166*C166*-1,D166*C166)</f>
         <v>-580.77499999999998</v>
       </c>
-      <c r="F164" s="2" t="s">
+      <c r="F166" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" s="11">
+    <row r="167" spans="1:6">
+      <c r="A167" s="11">
         <v>46233.624305555553</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B167" t="s">
         <v>63</v>
       </c>
-      <c r="C165" s="2">
+      <c r="C167" s="12">
         <v>109.81</v>
       </c>
-      <c r="D165" s="6">
+      <c r="D167" s="6">
         <v>5</v>
       </c>
-      <c r="E165" s="6">
-        <f>IF(F165="Sell",-C165*D165,C165*D165)</f>
+      <c r="E167" s="12">
+        <f>IF(F167="Sell",D167*C167*-1,D167*C167)</f>
         <v>549.04999999999995</v>
       </c>
-      <c r="F165" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" s="11">
+      <c r="F167" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" s="11">
         <v>46233.625</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B168" t="s">
         <v>43</v>
       </c>
-      <c r="C166" s="2">
+      <c r="C168" s="12">
         <v>126.71</v>
       </c>
-      <c r="D166" s="6">
+      <c r="D168" s="6">
         <v>5</v>
       </c>
-      <c r="E166" s="6">
-        <f>IF(F166="Sell",-C166*D166,C166*D166)</f>
+      <c r="E168" s="12">
+        <f>IF(F168="Sell",D168*C168*-1,D168*C168)</f>
         <v>633.54999999999995</v>
       </c>
-      <c r="F166" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="11">
+      <c r="F168" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" s="11">
         <v>46237.402777777781</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B169" t="s">
         <v>55</v>
       </c>
-      <c r="C167" s="2">
+      <c r="C169" s="12">
         <v>779.13</v>
       </c>
-      <c r="D167" s="6">
+      <c r="D169" s="6">
         <v>1.28</v>
       </c>
-      <c r="E167" s="6">
-        <f>IF(F167="Sell",-C167*D167,C167*D167)</f>
+      <c r="E169" s="12">
+        <f>IF(F169="Sell",D169*C169*-1,D169*C169)</f>
         <v>997.28640000000007</v>
       </c>
-      <c r="F167" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="11">
-        <v>46114.560416666667</v>
-      </c>
-      <c r="B168" t="s">
+      <c r="F169" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" s="11">
+        <v>46238.509722222225</v>
+      </c>
+      <c r="B170" t="s">
+        <v>65</v>
+      </c>
+      <c r="C170" s="12">
+        <v>101.28</v>
+      </c>
+      <c r="D170" s="6">
+        <v>3.95</v>
+      </c>
+      <c r="E170" s="12">
+        <f>IF(F170="Sell",D170*C170*-1,D170*C170)</f>
+        <v>-400.05600000000004</v>
+      </c>
+      <c r="F170" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" s="11">
+        <v>46238.561111111114</v>
+      </c>
+      <c r="B171" t="s">
+        <v>61</v>
+      </c>
+      <c r="C171" s="12">
+        <v>67.38</v>
+      </c>
+      <c r="D171" s="6">
+        <v>6.03</v>
+      </c>
+      <c r="E171" s="12">
+        <f>IF(F171="Sell",D171*C171*-1,D171*C171)</f>
+        <v>-406.3014</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" s="11">
+        <v>46238.567361111112</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="D172" s="6">
+        <v>275.64999999999998</v>
+      </c>
+      <c r="E172" s="12">
+        <f>IF(F172="Sell",D172*C172*-1,D172*C172)</f>
+        <v>-1157.73</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" s="11">
+        <v>46238.569444444445</v>
+      </c>
+      <c r="B173" t="s">
+        <v>55</v>
+      </c>
+      <c r="C173" s="12">
+        <v>898.6</v>
+      </c>
+      <c r="D173" s="6">
+        <v>0.50543000000000005</v>
+      </c>
+      <c r="E173" s="12">
+        <f>IF(F173="Sell",D173*C173*-1,D173*C173)</f>
+        <v>-454.17939800000005</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" s="11">
+        <v>46238.570138888892</v>
+      </c>
+      <c r="B174" t="s">
         <v>18</v>
       </c>
-      <c r="C168" s="2">
-        <v>371.51</v>
-      </c>
-      <c r="D168" s="6">
-        <v>1.92</v>
-      </c>
-      <c r="E168" s="6">
-        <f>IF(F168="Sell",-C168*D168,C168*D168)</f>
-        <v>713.29919999999993</v>
-      </c>
-      <c r="F168" s="6" t="s">
+      <c r="C174" s="12">
+        <v>495.53</v>
+      </c>
+      <c r="D174" s="6">
+        <v>0.26284999999999997</v>
+      </c>
+      <c r="E174" s="12">
+        <f>IF(F174="Sell",D174*C174*-1,D174*C174)</f>
+        <v>-130.25006049999999</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" s="11">
+        <v>46238.570833333331</v>
+      </c>
+      <c r="B175" t="s">
+        <v>12</v>
+      </c>
+      <c r="C175" s="12">
+        <v>772.16</v>
+      </c>
+      <c r="D175" s="6">
+        <v>0.16203999999999999</v>
+      </c>
+      <c r="E175" s="12">
+        <f>IF(F175="Sell",D175*C175*-1,D175*C175)</f>
+        <v>-125.12080639999999</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" s="11">
+        <v>46241.428472222222</v>
+      </c>
+      <c r="B176" t="s">
+        <v>12</v>
+      </c>
+      <c r="C176" s="12">
+        <v>770.66</v>
+      </c>
+      <c r="D176" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="E176" s="12">
+        <f>IF(F176="Sell",D176*C176*-1,D176*C176)</f>
+        <v>-1155.99</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" s="11">
+        <v>46241.429861111108</v>
+      </c>
+      <c r="B177" t="s">
+        <v>10</v>
+      </c>
+      <c r="C177" s="12">
+        <v>398.71</v>
+      </c>
+      <c r="D177" s="6">
+        <v>3</v>
+      </c>
+      <c r="E177" s="12">
+        <f>IF(F177="Sell",D177*C177*-1,D177*C177)</f>
+        <v>1196.1299999999999</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" s="11">
+        <v>46241.4375</v>
+      </c>
+      <c r="B178" t="s">
+        <v>13</v>
+      </c>
+      <c r="C178" s="12">
+        <v>11.48</v>
+      </c>
+      <c r="D178" s="6">
+        <v>90</v>
+      </c>
+      <c r="E178" s="12">
+        <f>IF(F178="Sell",D178*C178*-1,D178*C178)</f>
+        <v>1033.2</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" s="11">
+        <v>46241.438888888886</v>
+      </c>
+      <c r="B179" t="s">
+        <v>52</v>
+      </c>
+      <c r="C179" s="12">
+        <v>50.9</v>
+      </c>
+      <c r="D179" s="6">
+        <v>20</v>
+      </c>
+      <c r="E179" s="12">
+        <f>IF(F179="Sell",D179*C179*-1,D179*C179)</f>
+        <v>1018</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" s="11">
+        <v>46241.443749999999</v>
+      </c>
+      <c r="B180" t="s">
+        <v>12</v>
+      </c>
+      <c r="C180" s="12">
+        <v>771.92</v>
+      </c>
+      <c r="D180" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="E180" s="12">
+        <f>IF(F180="Sell",D180*C180*-1,D180*C180)</f>
+        <v>-1157.8799999999999</v>
+      </c>
+      <c r="F180" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" s="11">
+        <v>46247.428472222222</v>
+      </c>
+      <c r="B181" t="s">
+        <v>52</v>
+      </c>
+      <c r="C181" s="12">
+        <v>47.67</v>
+      </c>
+      <c r="D181" s="6">
+        <v>20</v>
+      </c>
+      <c r="E181" s="12">
+        <f>IF(F181="Sell",D181*C181*-1,D181*C181)</f>
+        <v>-953.40000000000009</v>
+      </c>
+      <c r="F181" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" s="11">
+        <v>46247.438194444447</v>
+      </c>
+      <c r="B182" t="s">
+        <v>72</v>
+      </c>
+      <c r="C182" s="12">
+        <v>45.97</v>
+      </c>
+      <c r="D182" s="6">
+        <v>10</v>
+      </c>
+      <c r="E182" s="12">
+        <f>IF(F182="Sell",D182*C182*-1,D182*C182)</f>
+        <v>459.7</v>
+      </c>
+      <c r="F182" s="2" t="s">
         <v>70</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F168" xr:uid="{C1E503C2-5372-44CA-920E-B8461526100B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F167">
-      <sortCondition ref="A1"/>
+  <autoFilter ref="A1:F169" xr:uid="{C1E503C2-5372-44CA-920E-B8461526100B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F182">
+      <sortCondition ref="A1:A182"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4239,17 +4540,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
   <dimension ref="A1:F174"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" style="5" customWidth="1"/>
     <col min="4" max="4" width="21.5" style="5" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="6" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="2"/>
+    <col min="6" max="6" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4269,7 +4570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>45903.418749999997</v>
       </c>
@@ -4290,7 +4591,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>45903.43472222222</v>
       </c>
@@ -4311,7 +4612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>45903.435416666667</v>
       </c>
@@ -4332,7 +4633,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>45903.436111111114</v>
       </c>
@@ -4353,7 +4654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>45903.436805555553</v>
       </c>
@@ -4374,7 +4675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>45903.438194444447</v>
       </c>
@@ -4395,7 +4696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>45903.438888888886</v>
       </c>
@@ -4416,7 +4717,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>45903.445138888892</v>
       </c>
@@ -4437,7 +4738,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>45903.445833333331</v>
       </c>
@@ -4457,7 +4758,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>45903.448611111111</v>
       </c>
@@ -4478,7 +4779,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>45903.455555555556</v>
       </c>
@@ -4499,7 +4800,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>45903.463888888888</v>
       </c>
@@ -4520,7 +4821,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14" s="1">
         <v>45903.46597222222</v>
       </c>
@@ -4541,7 +4842,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" s="1">
         <v>45903.467361111114</v>
       </c>
@@ -4562,7 +4863,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16" s="1">
         <v>45903.46875</v>
       </c>
@@ -4583,7 +4884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <v>45903.470138888886</v>
       </c>
@@ -4604,7 +4905,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <v>45903.474999999999</v>
       </c>
@@ -4625,7 +4926,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" s="1">
         <v>45903.476388888892</v>
       </c>
@@ -4646,7 +4947,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <v>45903.479861111111</v>
       </c>
@@ -4667,7 +4968,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <v>45903.480555555558</v>
       </c>
@@ -4688,7 +4989,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" s="1">
         <v>45903.493750000001</v>
       </c>
@@ -4709,7 +5010,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -4730,7 +5031,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -4751,7 +5052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" s="1">
         <v>45903.495138888888</v>
       </c>
@@ -4772,7 +5073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" s="1">
         <v>45903.504861111112</v>
       </c>
@@ -4793,7 +5094,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" s="1">
         <v>45904.404861111114</v>
       </c>
@@ -4814,7 +5115,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" s="1">
         <v>45904.406944444447</v>
       </c>
@@ -4835,7 +5136,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" s="1">
         <v>45904.407638888886</v>
       </c>
@@ -4856,7 +5157,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" s="1">
         <v>45904.412499999999</v>
       </c>
@@ -4877,7 +5178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" s="1">
         <v>45904.414583333331</v>
       </c>
@@ -4898,7 +5199,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" s="1">
         <v>45904.418749999997</v>
       </c>
@@ -4919,7 +5220,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33" s="1">
         <v>45905.408333333333</v>
       </c>
@@ -4940,7 +5241,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="A34" s="1">
         <v>45908.665277777778</v>
       </c>
@@ -4961,7 +5262,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6">
       <c r="A35" s="1">
         <v>45909.415277777778</v>
       </c>
@@ -4982,7 +5283,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36" s="1">
         <v>45909.418055555558</v>
       </c>
@@ -5003,7 +5304,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6">
       <c r="A37" s="1">
         <v>45909.427083333336</v>
       </c>
@@ -5024,7 +5325,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6">
       <c r="A38" s="1">
         <v>45909.427777777775</v>
       </c>
@@ -5045,7 +5346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="A39" s="1">
         <v>45909.431250000001</v>
       </c>
@@ -5066,7 +5367,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="A40" s="1">
         <v>45909.43472222222</v>
       </c>
@@ -5087,7 +5388,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6">
       <c r="A41" s="1">
         <v>45909.439583333333</v>
       </c>
@@ -5108,7 +5409,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6">
       <c r="A42" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -5129,7 +5430,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6">
       <c r="A43" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -5150,7 +5451,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6">
       <c r="A44" s="1">
         <v>45910</v>
       </c>
@@ -5171,7 +5472,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6">
       <c r="A45" s="1">
         <v>45910</v>
       </c>
@@ -5192,7 +5493,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6">
       <c r="A46" s="1">
         <v>45911</v>
       </c>
@@ -5213,7 +5514,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6">
       <c r="A47" s="1">
         <v>45911</v>
       </c>
@@ -5234,7 +5535,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6">
       <c r="A48" s="1">
         <v>45912</v>
       </c>
@@ -5255,7 +5556,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6">
       <c r="A49" s="1">
         <v>45912</v>
       </c>
@@ -5276,7 +5577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6">
       <c r="A50" s="1">
         <v>45912</v>
       </c>
@@ -5297,7 +5598,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6">
       <c r="A51" s="1">
         <v>45912</v>
       </c>
@@ -5318,7 +5619,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6">
       <c r="A52" s="1">
         <v>45923</v>
       </c>
@@ -5339,7 +5640,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6">
       <c r="A53" s="1">
         <v>45923</v>
       </c>
@@ -5360,7 +5661,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6">
       <c r="A54" s="1">
         <v>45923</v>
       </c>
@@ -5381,7 +5682,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6">
       <c r="A55" s="1">
         <v>45923</v>
       </c>
@@ -5402,7 +5703,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6">
       <c r="A56" s="1">
         <v>45923</v>
       </c>
@@ -5423,7 +5724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6">
       <c r="A57" s="1">
         <v>45923</v>
       </c>
@@ -5444,7 +5745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6">
       <c r="A58" s="1">
         <v>45924</v>
       </c>
@@ -5465,7 +5766,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6">
       <c r="A59" s="1">
         <v>45924</v>
       </c>
@@ -5486,7 +5787,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6">
       <c r="A60" s="1">
         <v>45929</v>
       </c>
@@ -5507,7 +5808,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6">
       <c r="A61" s="1">
         <v>45937</v>
       </c>
@@ -5528,7 +5829,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6">
       <c r="A62" s="1">
         <v>45937</v>
       </c>
@@ -5549,7 +5850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6">
       <c r="A63" s="1">
         <v>45937</v>
       </c>
@@ -5570,7 +5871,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6">
       <c r="A64" s="1">
         <v>45937.40625</v>
       </c>
@@ -5591,7 +5892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6">
       <c r="A65" s="1">
         <v>45937.462500000001</v>
       </c>
@@ -5612,7 +5913,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6">
       <c r="A66" s="1">
         <v>45937.465277777781</v>
       </c>
@@ -5633,7 +5934,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6">
       <c r="A67" s="1">
         <v>45938.413194444445</v>
       </c>
@@ -5653,7 +5954,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6">
       <c r="A68" s="1">
         <v>45939.417361111111</v>
       </c>
@@ -5673,7 +5974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6">
       <c r="A69" s="1">
         <v>45943.410416666666</v>
       </c>
@@ -5693,7 +5994,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6">
       <c r="A70" s="1">
         <v>45943.411805555559</v>
       </c>
@@ -5714,7 +6015,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6">
       <c r="A71" s="1">
         <v>45943.412499999999</v>
       </c>
@@ -5734,7 +6035,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6">
       <c r="A72" s="1">
         <v>45943.413194444445</v>
       </c>
@@ -5754,7 +6055,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6">
       <c r="A73" s="1">
         <v>45943.415277777778</v>
       </c>
@@ -5774,7 +6075,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6">
       <c r="A74" s="1">
         <v>45943.417361111111</v>
       </c>
@@ -5794,7 +6095,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6">
       <c r="A75" s="1">
         <v>45946.399305555555</v>
       </c>
@@ -5814,7 +6115,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6">
       <c r="A76" s="1">
         <v>45957.457638888889</v>
       </c>
@@ -5834,7 +6135,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6">
       <c r="A77" s="1">
         <v>45957.459722222222</v>
       </c>
@@ -5854,7 +6155,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6">
       <c r="A78" s="1">
         <v>45957.460416666669</v>
       </c>
@@ -5874,7 +6175,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6">
       <c r="A79" s="1">
         <v>45957.462500000001</v>
       </c>
@@ -5894,7 +6195,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6">
       <c r="A80" s="1">
         <v>45957.463194444441</v>
       </c>
@@ -5914,7 +6215,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" s="1">
         <v>45957.463888888888</v>
       </c>
@@ -5934,7 +6235,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -5954,7 +6255,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -5974,7 +6275,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -5994,7 +6295,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -6014,7 +6315,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6">
       <c r="A86" s="1">
         <v>45957.47152777778</v>
       </c>
@@ -6034,7 +6335,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6">
       <c r="A87" s="1">
         <v>45958.512499999997</v>
       </c>
@@ -6054,7 +6355,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6">
       <c r="A88" s="1">
         <v>45958.515277777777</v>
       </c>
@@ -6074,7 +6375,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89" s="1">
         <v>45958.517361111109</v>
       </c>
@@ -6094,7 +6395,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90" s="1">
         <v>45958.520138888889</v>
       </c>
@@ -6114,7 +6415,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -6134,7 +6435,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -6154,7 +6455,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93" s="1">
         <v>45958.529166666667</v>
       </c>
@@ -6174,7 +6475,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94" s="1">
         <v>45965.642361111109</v>
       </c>
@@ -6194,7 +6495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95" s="1">
         <v>45974.67291666667</v>
       </c>
@@ -6214,7 +6515,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96" s="1">
         <v>46002</v>
       </c>
@@ -6234,7 +6535,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97" s="1">
         <v>46002.439583333333</v>
       </c>
@@ -6254,7 +6555,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98" s="1">
         <v>46002.443749999999</v>
       </c>
@@ -6274,7 +6575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99" s="1">
         <v>46002.446527777778</v>
       </c>
@@ -6294,7 +6595,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100" s="1">
         <v>46008.648611111108</v>
       </c>
@@ -6314,7 +6615,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101" s="1">
         <v>46008.650694444441</v>
       </c>
@@ -6334,7 +6635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102" s="1">
         <v>46020.463888888888</v>
       </c>
@@ -6354,7 +6655,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103" s="1">
         <v>46021.472916666666</v>
       </c>
@@ -6374,7 +6675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104" s="1">
         <v>46027.567361111112</v>
       </c>
@@ -6394,7 +6695,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105" s="1">
         <v>46027.568055555559</v>
       </c>
@@ -6414,7 +6715,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106" s="1">
         <v>46027.568749999999</v>
       </c>
@@ -6434,7 +6735,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107" s="1">
         <v>46029.449305555558</v>
       </c>
@@ -6454,7 +6755,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6">
       <c r="A108" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -6474,7 +6775,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -6494,7 +6795,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110" s="1">
         <v>46035.44027777778</v>
       </c>
@@ -6514,7 +6815,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111" s="1">
         <v>46035.441666666666</v>
       </c>
@@ -6534,7 +6835,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112" s="1">
         <v>46036.448611111111</v>
       </c>
@@ -6554,7 +6855,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6">
       <c r="A113" s="1">
         <v>46042.44027777778</v>
       </c>
@@ -6574,7 +6875,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6">
       <c r="A114" s="1">
         <v>46042.441666666666</v>
       </c>
@@ -6594,7 +6895,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6">
       <c r="A115" s="1">
         <v>46042.45</v>
       </c>
@@ -6614,7 +6915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6">
       <c r="A116" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -6634,7 +6935,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6">
       <c r="A117" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -6655,7 +6956,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6">
       <c r="A118" s="1">
         <v>46044.49722222222</v>
       </c>
@@ -6675,7 +6976,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6">
       <c r="A119" s="1">
         <v>46045.445833333331</v>
       </c>
@@ -6695,7 +6996,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6">
       <c r="A120" s="1">
         <v>46045.493055555555</v>
       </c>
@@ -6715,7 +7016,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6">
       <c r="A121" s="1">
         <v>46048.572222222225</v>
       </c>
@@ -6735,7 +7036,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6">
       <c r="A122" s="1">
         <v>46049.448611111111</v>
       </c>
@@ -6755,7 +7056,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6">
       <c r="A123" s="1">
         <v>46050.563888888886</v>
       </c>
@@ -6775,7 +7076,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6">
       <c r="A124" s="1">
         <v>46055.650694444441</v>
       </c>
@@ -6795,7 +7096,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6">
       <c r="A125" s="1">
         <v>46055.652083333334</v>
       </c>
@@ -6815,7 +7116,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6">
       <c r="A126" s="1">
         <v>46059</v>
       </c>
@@ -6835,7 +7136,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6">
       <c r="A127" s="1">
         <v>46083.456250000003</v>
       </c>
@@ -6855,7 +7156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6">
       <c r="A128" s="1">
         <v>46086</v>
       </c>
@@ -6875,7 +7176,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6">
       <c r="A129" s="1">
         <v>46087</v>
       </c>
@@ -6895,7 +7196,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6">
       <c r="A130" s="1">
         <v>46087</v>
       </c>
@@ -6915,7 +7216,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6">
       <c r="A131" s="1">
         <v>46087</v>
       </c>
@@ -6935,7 +7236,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6">
       <c r="A132" s="1">
         <v>46087</v>
       </c>
@@ -6955,7 +7256,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6">
       <c r="A133" s="1">
         <v>46087</v>
       </c>
@@ -6975,7 +7276,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6">
       <c r="A134" s="1">
         <v>46087</v>
       </c>
@@ -6995,7 +7296,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6">
       <c r="A135" s="1">
         <v>46087</v>
       </c>
@@ -7015,7 +7316,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6">
       <c r="A136" s="1">
         <v>46090</v>
       </c>
@@ -7035,7 +7336,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6">
       <c r="A137" s="1">
         <v>46090</v>
       </c>
@@ -7055,7 +7356,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6">
       <c r="A138" s="1">
         <v>46090</v>
       </c>
@@ -7075,7 +7376,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6">
       <c r="A139" s="1">
         <v>46090</v>
       </c>
@@ -7095,7 +7396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6">
       <c r="A140" s="1">
         <v>46090</v>
       </c>
@@ -7115,7 +7416,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6">
       <c r="A141" s="1">
         <v>46091</v>
       </c>
@@ -7135,7 +7436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6">
       <c r="A142" s="1">
         <v>46091</v>
       </c>
@@ -7155,7 +7456,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6">
       <c r="A143" s="1">
         <v>46091</v>
       </c>
@@ -7175,7 +7476,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6">
       <c r="A144" s="1">
         <v>46091</v>
       </c>
@@ -7195,7 +7496,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6">
       <c r="A145" s="1">
         <v>46091</v>
       </c>
@@ -7215,7 +7516,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6">
       <c r="A146" s="1">
         <v>46092</v>
       </c>
@@ -7235,7 +7536,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6">
       <c r="A147" s="1">
         <v>46100</v>
       </c>
@@ -7256,7 +7557,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6">
       <c r="A148" s="1">
         <v>46100</v>
       </c>
@@ -7276,7 +7577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6">
       <c r="A149" s="1">
         <v>46113</v>
       </c>
@@ -7296,7 +7597,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6">
       <c r="A150" s="1">
         <v>46113</v>
       </c>
@@ -7316,7 +7617,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6">
       <c r="A151" s="1">
         <v>46113</v>
       </c>
@@ -7336,7 +7637,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6">
       <c r="A152" s="1">
         <v>46114</v>
       </c>
@@ -7356,7 +7657,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6">
       <c r="A153" s="1">
         <v>46128</v>
       </c>
@@ -7376,7 +7677,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6">
       <c r="A154" s="1">
         <v>46128</v>
       </c>
@@ -7396,7 +7697,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6">
       <c r="A155" s="1">
         <v>46113</v>
       </c>
@@ -7416,7 +7717,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6">
       <c r="A156" s="1">
         <v>46113</v>
       </c>
@@ -7436,7 +7737,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6">
       <c r="A157" s="1">
         <v>46114</v>
       </c>
@@ -7456,7 +7757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6">
       <c r="A158" s="1">
         <v>46128</v>
       </c>
@@ -7476,7 +7777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6">
       <c r="A159" s="1">
         <v>46128</v>
       </c>
@@ -7496,7 +7797,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6">
       <c r="A160" s="1">
         <v>46150</v>
       </c>
@@ -7517,7 +7818,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6">
       <c r="A161" s="1">
         <v>46153</v>
       </c>
@@ -7538,7 +7839,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6">
       <c r="A162" s="1">
         <v>46174</v>
       </c>
@@ -7559,7 +7860,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6">
       <c r="A163" s="1">
         <v>46175</v>
       </c>
@@ -7580,7 +7881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6">
       <c r="A164" s="1">
         <v>46175</v>
       </c>
@@ -7601,7 +7902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6">
       <c r="A165" s="1">
         <v>46177</v>
       </c>
@@ -7622,7 +7923,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6">
       <c r="A166" s="1">
         <v>46181</v>
       </c>
@@ -7643,7 +7944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6">
       <c r="A167" s="1">
         <v>46181</v>
       </c>
@@ -7664,7 +7965,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6">
       <c r="A168" s="1">
         <v>46204</v>
       </c>
@@ -7685,7 +7986,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6">
       <c r="A169" s="1">
         <v>46227</v>
       </c>
@@ -7706,7 +8007,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6">
       <c r="A170" s="1">
         <v>46230</v>
       </c>
@@ -7727,7 +8028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6">
       <c r="A171" s="1">
         <v>46231</v>
       </c>
@@ -7748,7 +8049,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6">
       <c r="A172" s="1">
         <v>46233</v>
       </c>
@@ -7769,7 +8070,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6">
       <c r="A173" s="1">
         <v>46233</v>
       </c>
@@ -7790,7 +8091,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6">
       <c r="A174" s="1">
         <v>46233</v>
       </c>

--- a/data/portfolio_activity.xlsx
+++ b/data/portfolio_activity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johanrosa/Desktop/r_projects/personal/finance_portfolio/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2018001\work_desktop\_personal\finance_portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6D5F34-5100-C940-A527-CB0000573BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE6EF8B-C685-415A-A33C-B23314FC97B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22981F44-200C-FA48-B0C7-1CB3C862DEAA}"/>
   </bookViews>
   <sheets>
     <sheet name="new_logs" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">logs!$A$1:$F$155</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">new_logs!$A$1:$F$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">new_logs!$A$1:$E$194</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="76">
   <si>
     <t>date</t>
   </si>
@@ -261,6 +261,15 @@
   <si>
     <t>OKLO</t>
   </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>OKTA</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
 </sst>
 </file>
 
@@ -272,7 +281,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -357,7 +366,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -695,18 +704,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E503C2-5372-44CA-920E-B8461526100B}">
-  <dimension ref="A1:F182"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:E194"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" style="11" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="14.375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="11.125" customWidth="1"/>
+    <col min="3" max="3" width="12.625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="12.625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="12.625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>68</v>
       </c>
@@ -719,14 +727,11 @@
       <c r="D1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>45903.43472222222</v>
       </c>
@@ -739,15 +744,11 @@
       <c r="D2" s="6">
         <v>3.15</v>
       </c>
-      <c r="E2" s="12">
-        <f>IF(F2="Sell",D2*C2*-1,D2*C2)</f>
-        <v>199.773</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="E2" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>45903.435416666667</v>
       </c>
@@ -760,15 +761,11 @@
       <c r="D3" s="6">
         <v>5.94</v>
       </c>
-      <c r="E3" s="12">
-        <f>IF(F3="Sell",D3*C3*-1,D3*C3)</f>
-        <v>199.64340000000001</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="E3" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>45903.436111111114</v>
       </c>
@@ -781,15 +778,11 @@
       <c r="D4" s="6">
         <v>0.63053000000000003</v>
       </c>
-      <c r="E4" s="12">
-        <f>IF(F4="Sell",D4*C4*-1,D4*C4)</f>
-        <v>199.9978107</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="E4" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>45903.436805555553</v>
       </c>
@@ -802,15 +795,11 @@
       <c r="D5" s="6">
         <v>0.76188999999999996</v>
       </c>
-      <c r="E5" s="12">
-        <f>IF(F5="Sell",D5*C5*-1,D5*C5)</f>
-        <v>249.99896569999999</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="E5" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>45903.438194444447</v>
       </c>
@@ -823,15 +812,11 @@
       <c r="D6" s="6">
         <v>0.37919000000000003</v>
       </c>
-      <c r="E6" s="12">
-        <f>IF(F6="Sell",D6*C6*-1,D6*C6)</f>
-        <v>49.999993400000008</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="E6" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>45903.438888888886</v>
       </c>
@@ -844,15 +829,11 @@
       <c r="D7" s="6">
         <v>0.31097999999999998</v>
       </c>
-      <c r="E7" s="12">
-        <f>IF(F7="Sell",D7*C7*-1,D7*C7)</f>
-        <v>199.99745759999999</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="E7" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>45903.440972222219</v>
       </c>
@@ -865,15 +846,11 @@
       <c r="D8" s="6">
         <v>5.46</v>
       </c>
-      <c r="E8" s="12">
-        <f>IF(F8="Sell",D8*C8*-1,D8*C8)</f>
-        <v>49.904400000000003</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="E8" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>45903.445138888892</v>
       </c>
@@ -886,15 +863,11 @@
       <c r="D9" s="6">
         <v>0.44206000000000001</v>
       </c>
-      <c r="E9" s="12">
-        <f>IF(F9="Sell",D9*C9*-1,D9*C9)</f>
-        <v>19.989953199999999</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="E9" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>45903.445833333331</v>
       </c>
@@ -907,15 +880,11 @@
       <c r="D10" s="6">
         <v>0.50480000000000003</v>
       </c>
-      <c r="E10" s="12">
-        <f>IF(F10="Sell",D10*C10*-1,D10*C10)</f>
-        <v>19.990080000000003</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="E10" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>45903.448611111111</v>
       </c>
@@ -928,15 +897,11 @@
       <c r="D11" s="6">
         <v>4.75</v>
       </c>
-      <c r="E11" s="12">
-        <f>IF(F11="Sell",D11*C11*-1,D11*C11)</f>
-        <v>24.984999999999999</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="E11" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>45903.455555555556</v>
       </c>
@@ -949,15 +914,11 @@
       <c r="D12" s="6">
         <v>5.8790000000000002E-2</v>
       </c>
-      <c r="E12" s="12">
-        <f>IF(F12="Sell",D12*C12*-1,D12*C12)</f>
-        <v>19.986836300000004</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="E12" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>45903.463888888888</v>
       </c>
@@ -970,15 +931,11 @@
       <c r="D13" s="6">
         <v>3.9489999999999997E-2</v>
       </c>
-      <c r="E13" s="12">
-        <f>IF(F13="Sell",D13*C13*-1,D13*C13)</f>
-        <v>19.9874686</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="E13" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>45903.46597222222</v>
       </c>
@@ -991,15 +948,11 @@
       <c r="D14" s="6">
         <v>2.7089999999999999E-2</v>
       </c>
-      <c r="E14" s="12">
-        <f>IF(F14="Sell",D14*C14*-1,D14*C14)</f>
-        <v>19.984834800000002</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="E14" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>45903.467361111114</v>
       </c>
@@ -1012,15 +965,11 @@
       <c r="D15" s="6">
         <v>8.4540000000000004E-2</v>
       </c>
-      <c r="E15" s="12">
-        <f>IF(F15="Sell",D15*C15*-1,D15*C15)</f>
-        <v>19.987792200000001</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="E15" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>45903.46875</v>
       </c>
@@ -1033,15 +982,11 @@
       <c r="D16" s="6">
         <v>0.21715999999999999</v>
       </c>
-      <c r="E16" s="12">
-        <f>IF(F16="Sell",D16*C16*-1,D16*C16)</f>
-        <v>49.998918400000001</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="E16" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>45903.470138888886</v>
       </c>
@@ -1054,15 +999,11 @@
       <c r="D17" s="6">
         <v>0.13278000000000001</v>
       </c>
-      <c r="E17" s="12">
-        <f>IF(F17="Sell",D17*C17*-1,D17*C17)</f>
-        <v>29.9976576</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="E17" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>45903.474999999999</v>
       </c>
@@ -1075,15 +1016,11 @@
       <c r="D18" s="6">
         <v>0.48430000000000001</v>
       </c>
-      <c r="E18" s="12">
-        <f>IF(F18="Sell",D18*C18*-1,D18*C18)</f>
-        <v>29.997541999999999</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="E18" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>45903.476388888892</v>
       </c>
@@ -1096,15 +1033,11 @@
       <c r="D19" s="6">
         <v>1.06</v>
       </c>
-      <c r="E19" s="12">
-        <f>IF(F19="Sell",D19*C19*-1,D19*C19)</f>
-        <v>99.131200000000007</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="E19" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>45903.479861111111</v>
       </c>
@@ -1117,15 +1050,11 @@
       <c r="D20" s="6">
         <v>0.41039999999999999</v>
       </c>
-      <c r="E20" s="12">
-        <f>IF(F20="Sell",D20*C20*-1,D20*C20)</f>
-        <v>49.994927999999994</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="E20" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>45903.480555555558</v>
       </c>
@@ -1138,15 +1067,11 @@
       <c r="D21" s="6">
         <v>8.9590000000000003E-2</v>
       </c>
-      <c r="E21" s="12">
-        <f>IF(F21="Sell",D21*C21*-1,D21*C21)</f>
-        <v>9.9991398999999994</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="E21" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>45903.493750000001</v>
       </c>
@@ -1159,15 +1084,11 @@
       <c r="D22" s="6">
         <v>0.40042</v>
       </c>
-      <c r="E22" s="12">
-        <f>IF(F22="Sell",D22*C22*-1,D22*C22)</f>
-        <v>29.999466399999999</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="E22" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>45903.494444444441</v>
       </c>
@@ -1180,15 +1101,11 @@
       <c r="D23" s="6">
         <v>1.42</v>
       </c>
-      <c r="E23" s="12">
-        <f>IF(F23="Sell",D23*C23*-1,D23*C23)</f>
-        <v>24.849999999999998</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="E23" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>45903.494444444441</v>
       </c>
@@ -1201,15 +1118,11 @@
       <c r="D24" s="6">
         <v>1.33</v>
       </c>
-      <c r="E24" s="12">
-        <f>IF(F24="Sell",D24*C24*-1,D24*C24)</f>
-        <v>49.835100000000004</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="E24" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>45903.495138888888</v>
       </c>
@@ -1222,15 +1135,11 @@
       <c r="D25" s="6">
         <v>1.53</v>
       </c>
-      <c r="E25" s="12">
-        <f>IF(F25="Sell",D25*C25*-1,D25*C25)</f>
-        <v>19.89</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="E25" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>45903.504861111112</v>
       </c>
@@ -1243,15 +1152,11 @@
       <c r="D26" s="6">
         <v>0.12581000000000001</v>
       </c>
-      <c r="E26" s="12">
-        <f>IF(F26="Sell",D26*C26*-1,D26*C26)</f>
-        <v>19.9899509</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="E26" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>45904.404861111114</v>
       </c>
@@ -1264,15 +1169,11 @@
       <c r="D27" s="6">
         <v>1</v>
       </c>
-      <c r="E27" s="12">
-        <f>IF(F27="Sell",D27*C27*-1,D27*C27)</f>
-        <v>49.57</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="E27" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>45904.406944444447</v>
       </c>
@@ -1285,15 +1186,11 @@
       <c r="D28" s="6">
         <v>3.35</v>
       </c>
-      <c r="E28" s="12">
-        <f>IF(F28="Sell",D28*C28*-1,D28*C28)</f>
-        <v>29.948999999999998</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="E28" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>45904.407638888886</v>
       </c>
@@ -1306,15 +1203,11 @@
       <c r="D29" s="6">
         <v>0.92030000000000001</v>
       </c>
-      <c r="E29" s="12">
-        <f>IF(F29="Sell",D29*C29*-1,D29*C29)</f>
-        <v>24.995348</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="E29" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>45904.412499999999</v>
       </c>
@@ -1327,15 +1220,11 @@
       <c r="D30" s="6">
         <v>1.34</v>
       </c>
-      <c r="E30" s="12">
-        <f>IF(F30="Sell",D30*C30*-1,D30*C30)</f>
-        <v>99.615600000000015</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="E30" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>45904.414583333331</v>
       </c>
@@ -1348,15 +1237,11 @@
       <c r="D31" s="6">
         <v>0.16197</v>
       </c>
-      <c r="E31" s="12">
-        <f>IF(F31="Sell",D31*C31*-1,D31*C31)</f>
-        <v>29.998463700000002</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="E31" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>45904.418749999997</v>
       </c>
@@ -1369,15 +1254,11 @@
       <c r="D32" s="6">
         <v>0.15440000000000001</v>
       </c>
-      <c r="E32" s="12">
-        <f>IF(F32="Sell",D32*C32*-1,D32*C32)</f>
-        <v>99.998704000000004</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="E32" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>45905.408333333333</v>
       </c>
@@ -1390,15 +1271,11 @@
       <c r="D33" s="6">
         <v>2.25</v>
       </c>
-      <c r="E33" s="12">
-        <f>IF(F33="Sell",D33*C33*-1,D33*C33)</f>
-        <v>14.9625</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="E33" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>45908.665277777778</v>
       </c>
@@ -1411,15 +1288,11 @@
       <c r="D34" s="6">
         <v>0.48430000000000001</v>
       </c>
-      <c r="E34" s="12">
-        <f>IF(F34="Sell",D34*C34*-1,D34*C34)</f>
-        <v>-29.895838999999999</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>45909.415277777778</v>
       </c>
@@ -1432,15 +1305,11 @@
       <c r="D35" s="6">
         <v>3</v>
       </c>
-      <c r="E35" s="12">
-        <f>IF(F35="Sell",D35*C35*-1,D35*C35)</f>
-        <v>18.48</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="E35" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>45909.418055555558</v>
       </c>
@@ -1453,15 +1322,11 @@
       <c r="D36" s="6">
         <v>0.38446000000000002</v>
       </c>
-      <c r="E36" s="12">
-        <f>IF(F36="Sell",D36*C36*-1,D36*C36)</f>
-        <v>12.567997399999999</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="E36" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>45909.427083333336</v>
       </c>
@@ -1474,15 +1339,11 @@
       <c r="D37" s="6">
         <v>1.38</v>
       </c>
-      <c r="E37" s="12">
-        <f>IF(F37="Sell",D37*C37*-1,D37*C37)</f>
-        <v>99.801599999999979</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="E37" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>45909.427777777775</v>
       </c>
@@ -1495,15 +1356,11 @@
       <c r="D38" s="6">
         <v>8.4499999999999992E-3</v>
       </c>
-      <c r="E38" s="12">
-        <f>IF(F38="Sell",D38*C38*-1,D38*C38)</f>
-        <v>19.966842999999997</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="E38" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>45909.431250000001</v>
       </c>
@@ -1516,15 +1373,11 @@
       <c r="D39" s="6">
         <v>1</v>
       </c>
-      <c r="E39" s="12">
-        <f>IF(F39="Sell",D39*C39*-1,D39*C39)</f>
-        <v>335.9</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="E39" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>45909.43472222222</v>
       </c>
@@ -1537,15 +1390,11 @@
       <c r="D40" s="6">
         <v>0.46235999999999999</v>
       </c>
-      <c r="E40" s="12">
-        <f>IF(F40="Sell",D40*C40*-1,D40*C40)</f>
-        <v>299.98379159999996</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="E40" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>45909.439583333333</v>
       </c>
@@ -1558,15 +1407,11 @@
       <c r="D41" s="6">
         <v>1.36</v>
       </c>
-      <c r="E41" s="12">
-        <f>IF(F41="Sell",D41*C41*-1,D41*C41)</f>
-        <v>13.450400000000002</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="E41" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>45909.589583333334</v>
       </c>
@@ -1579,15 +1424,11 @@
       <c r="D42" s="6">
         <v>0.17241999999999999</v>
       </c>
-      <c r="E42" s="12">
-        <f>IF(F42="Sell",D42*C42*-1,D42*C42)</f>
-        <v>99.998427399999997</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="E42" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
         <v>45910.459722222222</v>
       </c>
@@ -1600,15 +1441,11 @@
       <c r="D43" s="6">
         <v>5.849E-2</v>
       </c>
-      <c r="E43" s="12">
-        <f>IF(F43="Sell",D43*C43*-1,D43*C43)</f>
-        <v>19.986617899999999</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="E43" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
         <v>45910.654166666667</v>
       </c>
@@ -1621,15 +1458,11 @@
       <c r="D44" s="6">
         <v>1.47</v>
       </c>
-      <c r="E44" s="12">
-        <f>IF(F44="Sell",D44*C44*-1,D44*C44)</f>
-        <v>8.3643000000000001</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="E44" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
         <v>45911.636805555558</v>
       </c>
@@ -1642,15 +1475,11 @@
       <c r="D45" s="6">
         <v>5.849E-2</v>
       </c>
-      <c r="E45" s="12">
-        <f>IF(F45="Sell",D45*C45*-1,D45*C45)</f>
-        <v>-18.056447899999998</v>
-      </c>
-      <c r="F45" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
         <v>45911.637499999997</v>
       </c>
@@ -1663,15 +1492,11 @@
       <c r="D46" s="6">
         <v>1.38</v>
       </c>
-      <c r="E46" s="12">
-        <f>IF(F46="Sell",D46*C46*-1,D46*C46)</f>
-        <v>-101.23679999999999</v>
-      </c>
-      <c r="F46" s="2" t="s">
+      <c r="E46" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
         <v>45912.396527777775</v>
       </c>
@@ -1684,15 +1509,11 @@
       <c r="D47" s="6">
         <v>1</v>
       </c>
-      <c r="E47" s="12">
-        <f>IF(F47="Sell",D47*C47*-1,D47*C47)</f>
-        <v>54.9</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="E47" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <v>45912.399305555555</v>
       </c>
@@ -1705,15 +1526,11 @@
       <c r="D48" s="6">
         <v>0.4</v>
       </c>
-      <c r="E48" s="12">
-        <f>IF(F48="Sell",D48*C48*-1,D48*C48)</f>
-        <v>13.796000000000001</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="E48" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
         <v>45912.408333333333</v>
       </c>
@@ -1726,15 +1543,11 @@
       <c r="D49" s="6">
         <v>1</v>
       </c>
-      <c r="E49" s="12">
-        <f>IF(F49="Sell",D49*C49*-1,D49*C49)</f>
-        <v>42.99</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="E49" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
         <v>45912.414583333331</v>
       </c>
@@ -1747,15 +1560,11 @@
       <c r="D50" s="6">
         <v>0.16</v>
       </c>
-      <c r="E50" s="12">
-        <f>IF(F50="Sell",D50*C50*-1,D50*C50)</f>
-        <v>6.0384000000000002</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="E50" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
         <v>45923.460416666669</v>
       </c>
@@ -1768,15 +1577,11 @@
       <c r="D51" s="6">
         <v>1</v>
       </c>
-      <c r="E51" s="12">
-        <f>IF(F51="Sell",D51*C51*-1,D51*C51)</f>
-        <v>68.19</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="E51" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
         <v>45923.463194444441</v>
       </c>
@@ -1789,15 +1594,11 @@
       <c r="D52" s="6">
         <v>0.58055999999999996</v>
       </c>
-      <c r="E52" s="12">
-        <f>IF(F52="Sell",D52*C52*-1,D52*C52)</f>
-        <v>145.9992288</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="E52" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
         <v>45923.489583333336</v>
       </c>
@@ -1810,15 +1611,11 @@
       <c r="D53" s="6">
         <v>1</v>
       </c>
-      <c r="E53" s="12">
-        <f>IF(F53="Sell",D53*C53*-1,D53*C53)</f>
-        <v>170.43</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="E53" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
         <v>45923.515972222223</v>
       </c>
@@ -1831,15 +1628,11 @@
       <c r="D54" s="6">
         <v>0.10446999999999999</v>
       </c>
-      <c r="E54" s="12">
-        <f>IF(F54="Sell",D54*C54*-1,D54*C54)</f>
-        <v>79.994768399999998</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="E54" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
         <v>45923.517361111109</v>
       </c>
@@ -1852,15 +1645,11 @@
       <c r="D55" s="6">
         <v>4.45</v>
       </c>
-      <c r="E55" s="12">
-        <f>IF(F55="Sell",D55*C55*-1,D55*C55)</f>
-        <v>35.733499999999999</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="E55" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
         <v>45924.42291666667</v>
       </c>
@@ -1873,15 +1662,11 @@
       <c r="D56" s="6">
         <v>0.15473000000000001</v>
       </c>
-      <c r="E56" s="12">
-        <f>IF(F56="Sell",D56*C56*-1,D56*C56)</f>
-        <v>-103.0780314</v>
-      </c>
-      <c r="F56" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
         <v>45924.423611111109</v>
       </c>
@@ -1894,15 +1679,11 @@
       <c r="D57" s="6">
         <v>1</v>
       </c>
-      <c r="E57" s="12">
-        <f>IF(F57="Sell",D57*C57*-1,D57*C57)</f>
-        <v>-48.95</v>
-      </c>
-      <c r="F57" s="2" t="s">
+      <c r="E57" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
         <v>45924.423611111109</v>
       </c>
@@ -1915,15 +1696,11 @@
       <c r="D58" s="6">
         <v>0.41039999999999999</v>
       </c>
-      <c r="E58" s="12">
-        <f>IF(F58="Sell",D58*C58*-1,D58*C58)</f>
-        <v>-49.834872000000004</v>
-      </c>
-      <c r="F58" s="2" t="s">
+      <c r="E58" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
         <v>45929.46875</v>
       </c>
@@ -1936,15 +1713,11 @@
       <c r="D59" s="6">
         <v>0.61799999999999999</v>
       </c>
-      <c r="E59" s="12">
-        <f>IF(F59="Sell",D59*C59*-1,D59*C59)</f>
-        <v>202.08599999999998</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="E59" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
         <v>45937.396527777775</v>
       </c>
@@ -1957,15 +1730,11 @@
       <c r="D60" s="6">
         <v>1</v>
       </c>
-      <c r="E60" s="12">
-        <f>IF(F60="Sell",D60*C60*-1,D60*C60)</f>
-        <v>61.27</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="E60" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
         <v>45937.398611111108</v>
       </c>
@@ -1978,15 +1747,11 @@
       <c r="D61" s="6">
         <v>2</v>
       </c>
-      <c r="E61" s="12">
-        <f>IF(F61="Sell",D61*C61*-1,D61*C61)</f>
-        <v>67.88</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="E61" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
         <v>45937.4</v>
       </c>
@@ -1999,15 +1764,11 @@
       <c r="D62" s="6">
         <v>4</v>
       </c>
-      <c r="E62" s="12">
-        <f>IF(F62="Sell",D62*C62*-1,D62*C62)</f>
-        <v>49.56</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+      <c r="E62" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="11">
         <v>45937.40625</v>
       </c>
@@ -2020,15 +1781,11 @@
       <c r="D63" s="6">
         <v>5</v>
       </c>
-      <c r="E63" s="12">
-        <f>IF(F63="Sell",D63*C63*-1,D63*C63)</f>
-        <v>26.6</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="E63" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
         <v>45937.462500000001</v>
       </c>
@@ -2041,15 +1798,11 @@
       <c r="D64" s="6">
         <v>2</v>
       </c>
-      <c r="E64" s="12">
-        <f>IF(F64="Sell",D64*C64*-1,D64*C64)</f>
-        <v>114.96</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="E64" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
         <v>45937.465277777781</v>
       </c>
@@ -2062,15 +1815,11 @@
       <c r="D65" s="6">
         <v>0.12198000000000001</v>
       </c>
-      <c r="E65" s="12">
-        <f>IF(F65="Sell",D65*C65*-1,D65*C65)</f>
-        <v>73.794240600000009</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="E65" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
         <v>45938.413194444445</v>
       </c>
@@ -2083,15 +1832,11 @@
       <c r="D66" s="6">
         <v>2</v>
       </c>
-      <c r="E66" s="12">
-        <f>IF(F66="Sell",D66*C66*-1,D66*C66)</f>
-        <v>-118.68</v>
-      </c>
-      <c r="F66" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="11">
         <v>45939.417361111111</v>
       </c>
@@ -2104,15 +1849,11 @@
       <c r="D67" s="6">
         <v>0.95403000000000004</v>
       </c>
-      <c r="E67" s="12">
-        <f>IF(F67="Sell",D67*C67*-1,D67*C67)</f>
-        <v>118.5096066</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="E67" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="11">
         <v>45943.410416666666</v>
       </c>
@@ -2125,15 +1866,11 @@
       <c r="D68" s="6">
         <v>9.0120000000000006E-2</v>
       </c>
-      <c r="E68" s="12">
-        <f>IF(F68="Sell",D68*C68*-1,D68*C68)</f>
-        <v>-10.111464000000002</v>
-      </c>
-      <c r="F68" s="2" t="s">
+      <c r="E68" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="11">
         <v>45943.411805555559</v>
       </c>
@@ -2146,15 +1883,11 @@
       <c r="D69" s="6">
         <v>8.4540000000000004E-2</v>
       </c>
-      <c r="E69" s="12">
-        <f>IF(F69="Sell",D69*C69*-1,D69*C69)</f>
-        <v>-20.871235200000001</v>
-      </c>
-      <c r="F69" s="2" t="s">
+      <c r="E69" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="11">
         <v>45943.412499999999</v>
       </c>
@@ -2167,15 +1900,11 @@
       <c r="D70" s="6">
         <v>1.42</v>
       </c>
-      <c r="E70" s="12">
-        <f>IF(F70="Sell",D70*C70*-1,D70*C70)</f>
-        <v>-24.580199999999998</v>
-      </c>
-      <c r="F70" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="11">
         <v>45943.413194444445</v>
       </c>
@@ -2188,15 +1917,11 @@
       <c r="D71" s="6">
         <v>0.37919000000000003</v>
       </c>
-      <c r="E71" s="12">
-        <f>IF(F71="Sell",D71*C71*-1,D71*C71)</f>
-        <v>-48.881382900000006</v>
-      </c>
-      <c r="F71" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="11">
         <v>45943.415277777778</v>
       </c>
@@ -2209,15 +1934,11 @@
       <c r="D72" s="6">
         <v>0.16197</v>
       </c>
-      <c r="E72" s="12">
-        <f>IF(F72="Sell",D72*C72*-1,D72*C72)</f>
-        <v>-29.698819200000003</v>
-      </c>
-      <c r="F72" s="2" t="s">
+      <c r="E72" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="11">
         <v>45943.417361111111</v>
       </c>
@@ -2230,15 +1951,11 @@
       <c r="D73" s="6">
         <v>0.40042</v>
       </c>
-      <c r="E73" s="12">
-        <f>IF(F73="Sell",D73*C73*-1,D73*C73)</f>
-        <v>-28.237618399999999</v>
-      </c>
-      <c r="F73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="11">
         <v>45946.399305555555</v>
       </c>
@@ -2251,15 +1968,11 @@
       <c r="D74" s="6">
         <v>3.93</v>
       </c>
-      <c r="E74" s="12">
-        <f>IF(F74="Sell",D74*C74*-1,D74*C74)</f>
-        <v>161.56229999999999</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+      <c r="E74" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="11">
         <v>45957.457638888889</v>
       </c>
@@ -2272,15 +1985,11 @@
       <c r="D75" s="6">
         <v>1</v>
       </c>
-      <c r="E75" s="12">
-        <f>IF(F75="Sell",D75*C75*-1,D75*C75)</f>
-        <v>-192.61</v>
-      </c>
-      <c r="F75" s="2" t="s">
+      <c r="E75" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="11">
         <v>45957.459722222222</v>
       </c>
@@ -2293,15 +2002,11 @@
       <c r="D76" s="6">
         <v>6.83</v>
       </c>
-      <c r="E76" s="12">
-        <f>IF(F76="Sell",D76*C76*-1,D76*C76)</f>
-        <v>-70.280699999999996</v>
-      </c>
-      <c r="F76" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="11">
         <v>45957.460416666669</v>
       </c>
@@ -2314,15 +2019,11 @@
       <c r="D77" s="6">
         <v>7.35</v>
       </c>
-      <c r="E77" s="12">
-        <f>IF(F77="Sell",D77*C77*-1,D77*C77)</f>
-        <v>-89.081999999999994</v>
-      </c>
-      <c r="F77" s="2" t="s">
+      <c r="E77" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="11">
         <v>45957.462500000001</v>
       </c>
@@ -2335,15 +2036,11 @@
       <c r="D78" s="6">
         <v>1.76</v>
       </c>
-      <c r="E78" s="12">
-        <f>IF(F78="Sell",D78*C78*-1,D78*C78)</f>
-        <v>-644.05439999999999</v>
-      </c>
-      <c r="F78" s="2" t="s">
+      <c r="E78" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="11">
         <v>45957.463194444441</v>
       </c>
@@ -2356,15 +2053,11 @@
       <c r="D79" s="6">
         <v>0.95403000000000004</v>
       </c>
-      <c r="E79" s="12">
-        <f>IF(F79="Sell",D79*C79*-1,D79*C79)</f>
-        <v>-117.3170691</v>
-      </c>
-      <c r="F79" s="2" t="s">
+      <c r="E79" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="11">
         <v>45957.463888888888</v>
       </c>
@@ -2377,15 +2070,11 @@
       <c r="D80" s="6">
         <v>1.33</v>
       </c>
-      <c r="E80" s="12">
-        <f>IF(F80="Sell",D80*C80*-1,D80*C80)</f>
-        <v>-55.567400000000006</v>
-      </c>
-      <c r="F80" s="2" t="s">
+      <c r="E80" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="11">
         <v>45957.464583333334</v>
       </c>
@@ -2398,15 +2087,11 @@
       <c r="D81" s="6">
         <v>1.53</v>
       </c>
-      <c r="E81" s="12">
-        <f>IF(F81="Sell",D81*C81*-1,D81*C81)</f>
-        <v>-19.767600000000002</v>
-      </c>
-      <c r="F81" s="2" t="s">
+      <c r="E81" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="11">
         <v>45957.464583333334</v>
       </c>
@@ -2419,15 +2104,11 @@
       <c r="D82" s="6">
         <v>8.4499999999999992E-3</v>
       </c>
-      <c r="E82" s="12">
-        <f>IF(F82="Sell",D82*C82*-1,D82*C82)</f>
-        <v>-19.243860999999999</v>
-      </c>
-      <c r="F82" s="2" t="s">
+      <c r="E82" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="11">
         <v>45957.470833333333</v>
       </c>
@@ -2440,15 +2121,11 @@
       <c r="D83" s="6">
         <v>0.44206000000000001</v>
       </c>
-      <c r="E83" s="12">
-        <f>IF(F83="Sell",D83*C83*-1,D83*C83)</f>
-        <v>-23.3142444</v>
-      </c>
-      <c r="F83" s="2" t="s">
+      <c r="E83" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="11">
         <v>45957.470833333333</v>
       </c>
@@ -2461,15 +2138,11 @@
       <c r="D84" s="6">
         <v>5</v>
       </c>
-      <c r="E84" s="12">
-        <f>IF(F84="Sell",D84*C84*-1,D84*C84)</f>
-        <v>-24.2</v>
-      </c>
-      <c r="F84" s="2" t="s">
+      <c r="E84" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="11">
         <v>45957.47152777778</v>
       </c>
@@ -2482,15 +2155,11 @@
       <c r="D85" s="6">
         <v>1</v>
       </c>
-      <c r="E85" s="12">
-        <f>IF(F85="Sell",D85*C85*-1,D85*C85)</f>
-        <v>-52.95</v>
-      </c>
-      <c r="F85" s="2" t="s">
+      <c r="E85" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="11">
         <v>45958.512499999997</v>
       </c>
@@ -2503,15 +2172,11 @@
       <c r="D86" s="6">
         <v>0.96050999999999997</v>
       </c>
-      <c r="E86" s="12">
-        <f>IF(F86="Sell",D86*C86*-1,D86*C86)</f>
-        <v>520.39471289999994</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
+      <c r="E86" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="11">
         <v>45958.515277777777</v>
       </c>
@@ -2524,15 +2189,11 @@
       <c r="D87" s="6">
         <v>2.65</v>
       </c>
-      <c r="E87" s="12">
-        <f>IF(F87="Sell",D87*C87*-1,D87*C87)</f>
-        <v>237.9435</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
+      <c r="E87" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="11">
         <v>45958.517361111109</v>
       </c>
@@ -2545,15 +2206,11 @@
       <c r="D88" s="6">
         <v>1.2</v>
       </c>
-      <c r="E88" s="12">
-        <f>IF(F88="Sell",D88*C88*-1,D88*C88)</f>
-        <v>320.18399999999997</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
+      <c r="E88" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="11">
         <v>45958.520138888889</v>
       </c>
@@ -2566,15 +2223,11 @@
       <c r="D89" s="6">
         <v>0.12581000000000001</v>
       </c>
-      <c r="E89" s="12">
-        <f>IF(F89="Sell",D89*C89*-1,D89*C89)</f>
-        <v>-23.7680252</v>
-      </c>
-      <c r="F89" s="2" t="s">
+      <c r="E89" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="11">
         <v>45958.522222222222</v>
       </c>
@@ -2587,15 +2240,11 @@
       <c r="D90" s="6">
         <v>5.8790000000000002E-2</v>
       </c>
-      <c r="E90" s="12">
-        <f>IF(F90="Sell",D90*C90*-1,D90*C90)</f>
-        <v>-27.360278099999999</v>
-      </c>
-      <c r="F90" s="2" t="s">
+      <c r="E90" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="11">
         <v>45958.522222222222</v>
       </c>
@@ -2608,15 +2257,11 @@
       <c r="D91" s="6">
         <v>0.55984</v>
       </c>
-      <c r="E91" s="12">
-        <f>IF(F91="Sell",D91*C91*-1,D91*C91)</f>
-        <v>-28.619020799999998</v>
-      </c>
-      <c r="F91" s="2" t="s">
+      <c r="E91" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="11">
         <v>45958.529166666667</v>
       </c>
@@ -2629,15 +2274,11 @@
       <c r="D92" s="6">
         <v>3</v>
       </c>
-      <c r="E92" s="12">
-        <f>IF(F92="Sell",D92*C92*-1,D92*C92)</f>
-        <v>166.62</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+      <c r="E92" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="11">
         <v>45965.642361111109</v>
       </c>
@@ -2650,15 +2291,11 @@
       <c r="D93" s="6">
         <v>1.84</v>
       </c>
-      <c r="E93" s="12">
-        <f>IF(F93="Sell",D93*C93*-1,D93*C93)</f>
-        <v>106.14960000000001</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+      <c r="E93" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="11">
         <v>45974.67291666667</v>
       </c>
@@ -2671,15 +2308,11 @@
       <c r="D94" s="6">
         <v>0.69955000000000001</v>
       </c>
-      <c r="E94" s="12">
-        <f>IF(F94="Sell",D94*C94*-1,D94*C94)</f>
-        <v>39.069867500000001</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
+      <c r="E94" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="11">
         <v>46002.439583333333</v>
       </c>
@@ -2692,15 +2325,11 @@
       <c r="D95" s="6">
         <v>2.08</v>
       </c>
-      <c r="E95" s="12">
-        <f>IF(F95="Sell",D95*C95*-1,D95*C95)</f>
-        <v>85.841600000000014</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
+      <c r="E95" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="11">
         <v>46002.442361111112</v>
       </c>
@@ -2713,15 +2342,11 @@
       <c r="D96" s="6">
         <v>0.72970000000000002</v>
       </c>
-      <c r="E96" s="12">
-        <f>IF(F96="Sell",D96*C96*-1,D96*C96)</f>
-        <v>499.99044000000004</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="E96" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="11">
         <v>46002.443749999999</v>
       </c>
@@ -2734,15 +2359,11 @@
       <c r="D97" s="6">
         <v>2.41</v>
       </c>
-      <c r="E97" s="12">
-        <f>IF(F97="Sell",D97*C97*-1,D97*C97)</f>
-        <v>123.72940000000001</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="E97" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="11">
         <v>46002.446527777778</v>
       </c>
@@ -2755,15 +2376,11 @@
       <c r="D98" s="6">
         <v>6.77</v>
       </c>
-      <c r="E98" s="12">
-        <f>IF(F98="Sell",D98*C98*-1,D98*C98)</f>
-        <v>163.02159999999998</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="E98" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="11">
         <v>46008.648611111108</v>
       </c>
@@ -2776,15 +2393,11 @@
       <c r="D99" s="6">
         <v>2</v>
       </c>
-      <c r="E99" s="12">
-        <f>IF(F99="Sell",D99*C99*-1,D99*C99)</f>
-        <v>42.22</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+      <c r="E99" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="11">
         <v>46008.650694444441</v>
       </c>
@@ -2797,15 +2410,11 @@
       <c r="D100" s="6">
         <v>1.79</v>
       </c>
-      <c r="E100" s="12">
-        <f>IF(F100="Sell",D100*C100*-1,D100*C100)</f>
-        <v>86.7971</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+      <c r="E100" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="11">
         <v>46020.463888888888</v>
       </c>
@@ -2818,15 +2427,11 @@
       <c r="D101" s="6">
         <v>1</v>
       </c>
-      <c r="E101" s="12">
-        <f>IF(F101="Sell",D101*C101*-1,D101*C101)</f>
-        <v>-59.54</v>
-      </c>
-      <c r="F101" s="2" t="s">
+      <c r="E101" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="11">
         <v>46021.472916666666</v>
       </c>
@@ -2839,15 +2444,11 @@
       <c r="D102" s="6">
         <v>9.9</v>
       </c>
-      <c r="E102" s="12">
-        <f>IF(F102="Sell",D102*C102*-1,D102*C102)</f>
-        <v>56.331000000000003</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
+      <c r="E102" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="11">
         <v>46027.567361111112</v>
       </c>
@@ -2860,15 +2461,11 @@
       <c r="D103" s="6">
         <v>1.56</v>
       </c>
-      <c r="E103" s="12">
-        <f>IF(F103="Sell",D103*C103*-1,D103*C103)</f>
-        <v>-17.534400000000002</v>
-      </c>
-      <c r="F103" s="2" t="s">
+      <c r="E103" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="11">
         <v>46027.568055555559</v>
       </c>
@@ -2881,15 +2478,11 @@
       <c r="D104" s="6">
         <v>0.13278000000000001</v>
       </c>
-      <c r="E104" s="12">
-        <f>IF(F104="Sell",D104*C104*-1,D104*C104)</f>
-        <v>-31.009441200000001</v>
-      </c>
-      <c r="F104" s="2" t="s">
+      <c r="E104" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="11">
         <v>46027.568749999999</v>
       </c>
@@ -2902,15 +2495,11 @@
       <c r="D105" s="6">
         <v>1</v>
       </c>
-      <c r="E105" s="12">
-        <f>IF(F105="Sell",D105*C105*-1,D105*C105)</f>
-        <v>-36.83</v>
-      </c>
-      <c r="F105" s="2" t="s">
+      <c r="E105" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="11">
         <v>46029.449305555558</v>
       </c>
@@ -2923,15 +2512,11 @@
       <c r="D106" s="6">
         <v>1.07</v>
       </c>
-      <c r="E106" s="12">
-        <f>IF(F106="Sell",D106*C106*-1,D106*C106)</f>
-        <v>-107.41730000000001</v>
-      </c>
-      <c r="F106" s="2" t="s">
+      <c r="E106" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="11">
         <v>46034.47152777778</v>
       </c>
@@ -2944,15 +2529,11 @@
       <c r="D107" s="6">
         <v>0.29479</v>
       </c>
-      <c r="E107" s="12">
-        <f>IF(F107="Sell",D107*C107*-1,D107*C107)</f>
-        <v>-184.509061</v>
-      </c>
-      <c r="F107" s="2" t="s">
+      <c r="E107" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="11">
         <v>46034.47152777778</v>
       </c>
@@ -2965,15 +2546,11 @@
       <c r="D108" s="6">
         <v>1.25</v>
       </c>
-      <c r="E108" s="12">
-        <f>IF(F108="Sell",D108*C108*-1,D108*C108)</f>
-        <v>-427.5</v>
-      </c>
-      <c r="F108" s="2" t="s">
+      <c r="E108" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="11">
         <v>46035.44027777778</v>
       </c>
@@ -2986,15 +2563,11 @@
       <c r="D109" s="6">
         <v>5.29</v>
       </c>
-      <c r="E109" s="12">
-        <f>IF(F109="Sell",D109*C109*-1,D109*C109)</f>
-        <v>261.69630000000001</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
+      <c r="E109" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="11">
         <v>46035.441666666666</v>
       </c>
@@ -3007,15 +2580,11 @@
       <c r="D110" s="6">
         <v>4.8600000000000003</v>
       </c>
-      <c r="E110" s="12">
-        <f>IF(F110="Sell",D110*C110*-1,D110*C110)</f>
-        <v>275.4162</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
+      <c r="E110" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="11">
         <v>46036.448611111111</v>
       </c>
@@ -3028,15 +2597,11 @@
       <c r="D111" s="6">
         <v>1.47</v>
       </c>
-      <c r="E111" s="12">
-        <f>IF(F111="Sell",D111*C111*-1,D111*C111)</f>
-        <v>269.2011</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
+      <c r="E111" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="11">
         <v>46042.44027777778</v>
       </c>
@@ -3049,15 +2614,11 @@
       <c r="D112" s="6">
         <v>10.81</v>
       </c>
-      <c r="E112" s="12">
-        <f>IF(F112="Sell",D112*C112*-1,D112*C112)</f>
-        <v>299.97750000000002</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
+      <c r="E112" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="11">
         <v>46042.441666666666</v>
       </c>
@@ -3070,15 +2631,11 @@
       <c r="D113" s="6">
         <v>20.09</v>
       </c>
-      <c r="E113" s="12">
-        <f>IF(F113="Sell",D113*C113*-1,D113*C113)</f>
-        <v>299.94369999999998</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="E113" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="11">
         <v>46042.45</v>
       </c>
@@ -3091,15 +2648,11 @@
       <c r="D114" s="6">
         <v>1</v>
       </c>
-      <c r="E114" s="12">
-        <f>IF(F114="Sell",D114*C114*-1,D114*C114)</f>
-        <v>376.93</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="E114" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="11">
         <v>46044.496527777781</v>
       </c>
@@ -3112,15 +2665,11 @@
       <c r="D115" s="6">
         <v>9.9</v>
       </c>
-      <c r="E115" s="12">
-        <f>IF(F115="Sell",D115*C115*-1,D115*C115)</f>
-        <v>-498.96</v>
-      </c>
-      <c r="F115" s="2" t="s">
+      <c r="E115" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="11">
         <v>46044.49722222222</v>
       </c>
@@ -3133,15 +2682,11 @@
       <c r="D116" s="6">
         <v>15.11</v>
       </c>
-      <c r="E116" s="12">
-        <f>IF(F116="Sell",D116*C116*-1,D116*C116)</f>
-        <v>-335.13979999999998</v>
-      </c>
-      <c r="F116" s="2" t="s">
+      <c r="E116" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="11">
         <v>46045.445833333331</v>
       </c>
@@ -3154,15 +2699,11 @@
       <c r="D117" s="6">
         <v>5.71</v>
       </c>
-      <c r="E117" s="12">
-        <f>IF(F117="Sell",D117*C117*-1,D117*C117)</f>
-        <v>399.7</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="E117" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="11">
         <v>46045.493055555555</v>
       </c>
@@ -3175,15 +2716,11 @@
       <c r="D118" s="6">
         <v>0.78064</v>
       </c>
-      <c r="E118" s="12">
-        <f>IF(F118="Sell",D118*C118*-1,D118*C118)</f>
-        <v>515.05846559999998</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+      <c r="E118" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="11">
         <v>46048.572222222225</v>
       </c>
@@ -3196,15 +2733,11 @@
       <c r="D119" s="6">
         <v>4</v>
       </c>
-      <c r="E119" s="12">
-        <f>IF(F119="Sell",D119*C119*-1,D119*C119)</f>
-        <v>-322.72000000000003</v>
-      </c>
-      <c r="F119" s="2" t="s">
+      <c r="E119" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="11">
         <v>46049.448611111111</v>
       </c>
@@ -3217,15 +2750,11 @@
       <c r="D120" s="6">
         <v>3.6</v>
       </c>
-      <c r="E120" s="12">
-        <f>IF(F120="Sell",D120*C120*-1,D120*C120)</f>
-        <v>321.76799999999997</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="E120" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="11">
         <v>46050.563888888886</v>
       </c>
@@ -3238,15 +2767,11 @@
       <c r="D121" s="6">
         <v>1.47</v>
       </c>
-      <c r="E121" s="12">
-        <f>IF(F121="Sell",D121*C121*-1,D121*C121)</f>
-        <v>-234.06809999999999</v>
-      </c>
-      <c r="F121" s="2" t="s">
+      <c r="E121" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="11">
         <v>46055.650694444441</v>
       </c>
@@ -3259,15 +2784,11 @@
       <c r="D122" s="6">
         <v>0.91229000000000005</v>
       </c>
-      <c r="E122" s="12">
-        <f>IF(F122="Sell",D122*C122*-1,D122*C122)</f>
-        <v>-649.34065329999999</v>
-      </c>
-      <c r="F122" s="2" t="s">
+      <c r="E122" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="11">
         <v>46055.652083333334</v>
       </c>
@@ -3280,15 +2801,11 @@
       <c r="D123" s="6">
         <v>47.2</v>
       </c>
-      <c r="E123" s="12">
-        <f>IF(F123="Sell",D123*C123*-1,D123*C123)</f>
-        <v>234.11200000000002</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+      <c r="E123" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="11">
         <v>46059.484722222223</v>
       </c>
@@ -3301,15 +2818,11 @@
       <c r="D124" s="6">
         <v>10.89</v>
       </c>
-      <c r="E124" s="12">
-        <f>IF(F124="Sell",D124*C124*-1,D124*C124)</f>
-        <v>648.82619999999997</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+      <c r="E124" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="11">
         <v>46083.456250000003</v>
       </c>
@@ -3322,15 +2835,11 @@
       <c r="D125" s="6">
         <v>3</v>
       </c>
-      <c r="E125" s="12">
-        <f>IF(F125="Sell",D125*C125*-1,D125*C125)</f>
-        <v>480.63</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+      <c r="E125" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="11">
         <v>46086.664583333331</v>
       </c>
@@ -3343,15 +2852,11 @@
       <c r="D126" s="6">
         <v>1.77</v>
       </c>
-      <c r="E126" s="12">
-        <f>IF(F126="Sell",D126*C126*-1,D126*C126)</f>
-        <v>174.06180000000001</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+      <c r="E126" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="11">
         <v>46087.525000000001</v>
       </c>
@@ -3364,15 +2869,11 @@
       <c r="D127" s="6">
         <v>10.81</v>
       </c>
-      <c r="E127" s="12">
-        <f>IF(F127="Sell",D127*C127*-1,D127*C127)</f>
-        <v>-222.46979999999999</v>
-      </c>
-      <c r="F127" s="2" t="s">
+      <c r="E127" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="11">
         <v>46087.525694444441</v>
       </c>
@@ -3385,15 +2886,11 @@
       <c r="D128" s="6">
         <v>3.6</v>
       </c>
-      <c r="E128" s="12">
-        <f>IF(F128="Sell",D128*C128*-1,D128*C128)</f>
-        <v>-290.80799999999999</v>
-      </c>
-      <c r="F128" s="2" t="s">
+      <c r="E128" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="11">
         <v>46087.526388888888</v>
       </c>
@@ -3406,15 +2903,11 @@
       <c r="D129" s="6">
         <v>5.71</v>
       </c>
-      <c r="E129" s="12">
-        <f>IF(F129="Sell",D129*C129*-1,D129*C129)</f>
-        <v>-462.62419999999997</v>
-      </c>
-      <c r="F129" s="2" t="s">
+      <c r="E129" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="11">
         <v>46087.527777777781</v>
       </c>
@@ -3427,15 +2920,11 @@
       <c r="D130" s="6">
         <v>8.81</v>
       </c>
-      <c r="E130" s="12">
-        <f>IF(F130="Sell",D130*C130*-1,D130*C130)</f>
-        <v>-525.7808</v>
-      </c>
-      <c r="F130" s="2" t="s">
+      <c r="E130" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="11">
         <v>46087.52847222222</v>
       </c>
@@ -3448,15 +2937,11 @@
       <c r="D131" s="6">
         <v>20.09</v>
       </c>
-      <c r="E131" s="12">
-        <f>IF(F131="Sell",D131*C131*-1,D131*C131)</f>
-        <v>-333.09219999999999</v>
-      </c>
-      <c r="F131" s="2" t="s">
+      <c r="E131" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="11">
         <v>46087.52847222222</v>
       </c>
@@ -3469,15 +2954,11 @@
       <c r="D132" s="6">
         <v>10.29</v>
       </c>
-      <c r="E132" s="12">
-        <f>IF(F132="Sell",D132*C132*-1,D132*C132)</f>
-        <v>-467.06309999999996</v>
-      </c>
-      <c r="F132" s="2" t="s">
+      <c r="E132" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="11">
         <v>46087.529166666667</v>
       </c>
@@ -3490,15 +2971,11 @@
       <c r="D133" s="6">
         <v>2</v>
       </c>
-      <c r="E133" s="12">
-        <f>IF(F133="Sell",D133*C133*-1,D133*C133)</f>
-        <v>-598.82000000000005</v>
-      </c>
-      <c r="F133" s="2" t="s">
+      <c r="E133" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="11">
         <v>46090.397916666669</v>
       </c>
@@ -3511,15 +2988,11 @@
       <c r="D134" s="6">
         <v>13.92</v>
       </c>
-      <c r="E134" s="12">
-        <f>IF(F134="Sell",D134*C134*-1,D134*C134)</f>
-        <v>-790.79520000000002</v>
-      </c>
-      <c r="F134" s="2" t="s">
+      <c r="E134" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="11">
         <v>46090.400000000001</v>
       </c>
@@ -3532,15 +3005,11 @@
       <c r="D135" s="6">
         <v>6.76</v>
       </c>
-      <c r="E135" s="12">
-        <f>IF(F135="Sell",D135*C135*-1,D135*C135)</f>
-        <v>787.47239999999999</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
+      <c r="E135" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="11">
         <v>46090.401388888888</v>
       </c>
@@ -3553,15 +3022,11 @@
       <c r="D136" s="6">
         <v>13.19</v>
       </c>
-      <c r="E136" s="12">
-        <f>IF(F136="Sell",D136*C136*-1,D136*C136)</f>
-        <v>499.76909999999998</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+      <c r="E136" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="11">
         <v>46090.402083333334</v>
       </c>
@@ -3574,15 +3039,11 @@
       <c r="D137" s="6">
         <v>7.89</v>
       </c>
-      <c r="E137" s="12">
-        <f>IF(F137="Sell",D137*C137*-1,D137*C137)</f>
-        <v>499.91039999999998</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+      <c r="E137" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="11">
         <v>46090.65347222222</v>
       </c>
@@ -3595,15 +3056,11 @@
       <c r="D138" s="6">
         <v>1.64</v>
       </c>
-      <c r="E138" s="12">
-        <f>IF(F138="Sell",D138*C138*-1,D138*C138)</f>
-        <v>1111.0508</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
+      <c r="E138" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="11">
         <v>46091.431944444441</v>
       </c>
@@ -3616,15 +3073,11 @@
       <c r="D139" s="6">
         <v>3</v>
       </c>
-      <c r="E139" s="12">
-        <f>IF(F139="Sell",D139*C139*-1,D139*C139)</f>
-        <v>-476.34000000000003</v>
-      </c>
-      <c r="F139" s="2" t="s">
+      <c r="E139" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="11">
         <v>46091.434027777781</v>
       </c>
@@ -3637,15 +3090,11 @@
       <c r="D140" s="6">
         <v>13.19</v>
       </c>
-      <c r="E140" s="12">
-        <f>IF(F140="Sell",D140*C140*-1,D140*C140)</f>
-        <v>-489.34899999999999</v>
-      </c>
-      <c r="F140" s="2" t="s">
+      <c r="E140" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="11">
         <v>46091.436805555553</v>
       </c>
@@ -3658,15 +3107,11 @@
       <c r="D141" s="6">
         <v>1.43</v>
       </c>
-      <c r="E141" s="12">
-        <f>IF(F141="Sell",D141*C141*-1,D141*C141)</f>
-        <v>586.29999999999995</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
+      <c r="E141" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="11">
         <v>46091.449305555558</v>
       </c>
@@ -3679,15 +3124,11 @@
       <c r="D142" s="6">
         <v>5</v>
       </c>
-      <c r="E142" s="12">
-        <f>IF(F142="Sell",D142*C142*-1,D142*C142)</f>
-        <v>450.09999999999997</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+      <c r="E142" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="11">
         <v>46091.54583333333</v>
       </c>
@@ -3700,15 +3141,11 @@
       <c r="D143" s="6">
         <v>7.89</v>
       </c>
-      <c r="E143" s="12">
-        <f>IF(F143="Sell",D143*C143*-1,D143*C143)</f>
-        <v>-466.2201</v>
-      </c>
-      <c r="F143" s="2" t="s">
+      <c r="E143" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="11">
         <v>46092.438194444447</v>
       </c>
@@ -3721,15 +3158,11 @@
       <c r="D144" s="6">
         <v>24.92</v>
       </c>
-      <c r="E144" s="12">
-        <f>IF(F144="Sell",D144*C144*-1,D144*C144)</f>
-        <v>999.5412</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
+      <c r="E144" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="11">
         <v>46100.508333333331</v>
       </c>
@@ -3742,15 +3175,11 @@
       <c r="D145" s="6">
         <v>5</v>
       </c>
-      <c r="E145" s="12">
-        <f>IF(F145="Sell",D145*C145*-1,D145*C145)</f>
-        <v>-357.59999999999997</v>
-      </c>
-      <c r="F145" s="2" t="s">
+      <c r="E145" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="11">
         <v>46100.509027777778</v>
       </c>
@@ -3763,15 +3192,11 @@
       <c r="D146" s="6">
         <v>7.21</v>
       </c>
-      <c r="E146" s="12">
-        <f>IF(F146="Sell",D146*C146*-1,D146*C146)</f>
-        <v>534.62150000000008</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+      <c r="E146" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="11">
         <v>46113.460416666669</v>
       </c>
@@ -3784,15 +3209,11 @@
       <c r="D147" s="6">
         <v>8.5399999999999991</v>
       </c>
-      <c r="E147" s="12">
-        <f>IF(F147="Sell",D147*C147*-1,D147*C147)</f>
-        <v>-1053.7505999999998</v>
-      </c>
-      <c r="F147" s="2" t="s">
+      <c r="E147" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="11">
         <v>46113.463194444441</v>
       </c>
@@ -3805,15 +3226,11 @@
       <c r="D148" s="6">
         <v>7.21</v>
       </c>
-      <c r="E148" s="12">
-        <f>IF(F148="Sell",D148*C148*-1,D148*C148)</f>
-        <v>-515.22659999999996</v>
-      </c>
-      <c r="F148" s="2" t="s">
+      <c r="E148" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="11">
         <v>46113.464583333334</v>
       </c>
@@ -3826,15 +3243,11 @@
       <c r="D149" s="6">
         <v>74</v>
       </c>
-      <c r="E149" s="12">
-        <f>IF(F149="Sell",D149*C149*-1,D149*C149)</f>
-        <v>353.72</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
+      <c r="E149" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="11">
         <v>46113.46597222222</v>
       </c>
@@ -3847,15 +3260,11 @@
       <c r="D150" s="6">
         <v>6</v>
       </c>
-      <c r="E150" s="12">
-        <f>IF(F150="Sell",D150*C150*-1,D150*C150)</f>
-        <v>499.98</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="E150" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="11">
         <v>46114.560416666667</v>
       </c>
@@ -3868,15 +3277,11 @@
       <c r="D151" s="6">
         <v>1.92</v>
       </c>
-      <c r="E151" s="12">
-        <f>IF(F151="Sell",D151*C151*-1,D151*C151)</f>
-        <v>713.29919999999993</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
+      <c r="E151" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="11">
         <v>46128.462500000001</v>
       </c>
@@ -3889,15 +3294,11 @@
       <c r="D152" s="6">
         <v>3</v>
       </c>
-      <c r="E152" s="12">
-        <f>IF(F152="Sell",D152*C152*-1,D152*C152)</f>
-        <v>525.81000000000006</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="E152" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="11">
         <v>46128.463888888888</v>
       </c>
@@ -3910,15 +3311,11 @@
       <c r="D153" s="6">
         <v>7.42</v>
       </c>
-      <c r="E153" s="12">
-        <f>IF(F153="Sell",D153*C153*-1,D153*C153)</f>
-        <v>638.34259999999995</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
+      <c r="E153" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="11">
         <v>46150.423611111109</v>
       </c>
@@ -3931,15 +3328,11 @@
       <c r="D154" s="6">
         <v>7.18</v>
       </c>
-      <c r="E154" s="12">
-        <f>IF(F154="Sell",D154*C154*-1,D154*C154)</f>
-        <v>35.110199999999999</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
+      <c r="E154" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="11">
         <v>46153.446527777778</v>
       </c>
@@ -3952,15 +3345,11 @@
       <c r="D155" s="6">
         <v>6.52</v>
       </c>
-      <c r="E155" s="12">
-        <f>IF(F155="Sell",D155*C155*-1,D155*C155)</f>
-        <v>599.44879999999989</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
+      <c r="E155" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="11">
         <v>46174.410416666666</v>
       </c>
@@ -3973,15 +3362,11 @@
       <c r="D156" s="6">
         <v>24.92</v>
       </c>
-      <c r="E156" s="12">
-        <f>IF(F156="Sell",D156*C156*-1,D156*C156)</f>
-        <v>-1010.506</v>
-      </c>
-      <c r="F156" s="2" t="s">
+      <c r="E156" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="11">
         <v>46175.486111111109</v>
       </c>
@@ -3994,15 +3379,11 @@
       <c r="D157" s="6">
         <v>2.5</v>
       </c>
-      <c r="E157" s="12">
-        <f>IF(F157="Sell",D157*C157*-1,D157*C157)</f>
-        <v>578.17500000000007</v>
-      </c>
-      <c r="F157" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
+      <c r="E157" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="11">
         <v>46175.487500000003</v>
       </c>
@@ -4015,15 +3396,11 @@
       <c r="D158" s="6">
         <v>3.95</v>
       </c>
-      <c r="E158" s="12">
-        <f>IF(F158="Sell",D158*C158*-1,D158*C158)</f>
-        <v>409.69400000000002</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
+      <c r="E158" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="11">
         <v>46177.450694444444</v>
       </c>
@@ -4036,15 +3413,11 @@
       <c r="D159" s="6">
         <v>2.4300000000000002</v>
       </c>
-      <c r="E159" s="12">
-        <f>IF(F159="Sell",D159*C159*-1,D159*C159)</f>
-        <v>-2412.6741000000002</v>
-      </c>
-      <c r="F159" s="2" t="s">
+      <c r="E159" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="11">
         <v>46181.434027777781</v>
       </c>
@@ -4057,15 +3430,11 @@
       <c r="D160" s="6">
         <v>10.07</v>
       </c>
-      <c r="E160" s="12">
-        <f>IF(F160="Sell",D160*C160*-1,D160*C160)</f>
-        <v>999.24610000000007</v>
-      </c>
-      <c r="F160" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
+      <c r="E160" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="11">
         <v>46181.43472222222</v>
       </c>
@@ -4078,15 +3447,11 @@
       <c r="D161" s="6">
         <v>3</v>
       </c>
-      <c r="E161" s="12">
-        <f>IF(F161="Sell",D161*C161*-1,D161*C161)</f>
-        <v>551.01</v>
-      </c>
-      <c r="F161" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
+      <c r="E161" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="11">
         <v>46204.443055555559</v>
       </c>
@@ -4099,15 +3464,11 @@
       <c r="D162" s="6">
         <v>2.3199999999999998</v>
       </c>
-      <c r="E162" s="12">
-        <f>IF(F162="Sell",D162*C162*-1,D162*C162)</f>
-        <v>890.0447999999999</v>
-      </c>
-      <c r="F162" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
+      <c r="E162" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="11">
         <v>46227.419444444444</v>
       </c>
@@ -4120,15 +3481,11 @@
       <c r="D163" s="6">
         <v>3</v>
       </c>
-      <c r="E163" s="12">
-        <f>IF(F163="Sell",D163*C163*-1,D163*C163)</f>
-        <v>-483.54</v>
-      </c>
-      <c r="F163" s="2" t="s">
+      <c r="E163" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="11">
         <v>46230.398611111108</v>
       </c>
@@ -4141,15 +3498,11 @@
       <c r="D164" s="6">
         <v>121.42</v>
       </c>
-      <c r="E164" s="12">
-        <f>IF(F164="Sell",D164*C164*-1,D164*C164)</f>
-        <v>483.2516</v>
-      </c>
-      <c r="F164" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
+      <c r="E164" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="11">
         <v>46231.45</v>
       </c>
@@ -4162,15 +3515,11 @@
       <c r="D165" s="6">
         <v>1.22</v>
       </c>
-      <c r="E165" s="12">
-        <f>IF(F165="Sell",D165*C165*-1,D165*C165)</f>
-        <v>998.38700000000006</v>
-      </c>
-      <c r="F165" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
+      <c r="E165" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="11">
         <v>46233.619444444441</v>
       </c>
@@ -4183,15 +3532,11 @@
       <c r="D166" s="6">
         <v>2.5</v>
       </c>
-      <c r="E166" s="12">
-        <f>IF(F166="Sell",D166*C166*-1,D166*C166)</f>
-        <v>-580.77499999999998</v>
-      </c>
-      <c r="F166" s="2" t="s">
+      <c r="E166" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="11">
         <v>46233.624305555553</v>
       </c>
@@ -4204,15 +3549,11 @@
       <c r="D167" s="6">
         <v>5</v>
       </c>
-      <c r="E167" s="12">
-        <f>IF(F167="Sell",D167*C167*-1,D167*C167)</f>
-        <v>549.04999999999995</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
+      <c r="E167" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="11">
         <v>46233.625</v>
       </c>
@@ -4225,15 +3566,11 @@
       <c r="D168" s="6">
         <v>5</v>
       </c>
-      <c r="E168" s="12">
-        <f>IF(F168="Sell",D168*C168*-1,D168*C168)</f>
-        <v>633.54999999999995</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
+      <c r="E168" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="11">
         <v>46237.402777777781</v>
       </c>
@@ -4246,15 +3583,11 @@
       <c r="D169" s="6">
         <v>1.28</v>
       </c>
-      <c r="E169" s="12">
-        <f>IF(F169="Sell",D169*C169*-1,D169*C169)</f>
-        <v>997.28640000000007</v>
-      </c>
-      <c r="F169" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
+      <c r="E169" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="11">
         <v>46238.509722222225</v>
       </c>
@@ -4267,15 +3600,11 @@
       <c r="D170" s="6">
         <v>3.95</v>
       </c>
-      <c r="E170" s="12">
-        <f>IF(F170="Sell",D170*C170*-1,D170*C170)</f>
-        <v>-400.05600000000004</v>
-      </c>
-      <c r="F170" s="6" t="s">
+      <c r="E170" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="11">
         <v>46238.561111111114</v>
       </c>
@@ -4288,15 +3617,11 @@
       <c r="D171" s="6">
         <v>6.03</v>
       </c>
-      <c r="E171" s="12">
-        <f>IF(F171="Sell",D171*C171*-1,D171*C171)</f>
-        <v>-406.3014</v>
-      </c>
-      <c r="F171" s="2" t="s">
+      <c r="E171" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="11">
         <v>46238.567361111112</v>
       </c>
@@ -4309,15 +3634,11 @@
       <c r="D172" s="6">
         <v>275.64999999999998</v>
       </c>
-      <c r="E172" s="12">
-        <f>IF(F172="Sell",D172*C172*-1,D172*C172)</f>
-        <v>-1157.73</v>
-      </c>
-      <c r="F172" s="2" t="s">
+      <c r="E172" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="11">
         <v>46238.569444444445</v>
       </c>
@@ -4330,15 +3651,11 @@
       <c r="D173" s="6">
         <v>0.50543000000000005</v>
       </c>
-      <c r="E173" s="12">
-        <f>IF(F173="Sell",D173*C173*-1,D173*C173)</f>
-        <v>-454.17939800000005</v>
-      </c>
-      <c r="F173" s="2" t="s">
+      <c r="E173" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="11">
         <v>46238.570138888892</v>
       </c>
@@ -4351,15 +3668,11 @@
       <c r="D174" s="6">
         <v>0.26284999999999997</v>
       </c>
-      <c r="E174" s="12">
-        <f>IF(F174="Sell",D174*C174*-1,D174*C174)</f>
-        <v>-130.25006049999999</v>
-      </c>
-      <c r="F174" s="2" t="s">
+      <c r="E174" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="11">
         <v>46238.570833333331</v>
       </c>
@@ -4372,15 +3685,11 @@
       <c r="D175" s="6">
         <v>0.16203999999999999</v>
       </c>
-      <c r="E175" s="12">
-        <f>IF(F175="Sell",D175*C175*-1,D175*C175)</f>
-        <v>-125.12080639999999</v>
-      </c>
-      <c r="F175" s="2" t="s">
+      <c r="E175" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="11">
         <v>46241.428472222222</v>
       </c>
@@ -4393,15 +3702,11 @@
       <c r="D176" s="6">
         <v>1.5</v>
       </c>
-      <c r="E176" s="12">
-        <f>IF(F176="Sell",D176*C176*-1,D176*C176)</f>
-        <v>-1155.99</v>
-      </c>
-      <c r="F176" s="2" t="s">
+      <c r="E176" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="11">
         <v>46241.429861111108</v>
       </c>
@@ -4414,15 +3719,11 @@
       <c r="D177" s="6">
         <v>3</v>
       </c>
-      <c r="E177" s="12">
-        <f>IF(F177="Sell",D177*C177*-1,D177*C177)</f>
-        <v>1196.1299999999999</v>
-      </c>
-      <c r="F177" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
+      <c r="E177" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="11">
         <v>46241.4375</v>
       </c>
@@ -4435,15 +3736,11 @@
       <c r="D178" s="6">
         <v>90</v>
       </c>
-      <c r="E178" s="12">
-        <f>IF(F178="Sell",D178*C178*-1,D178*C178)</f>
-        <v>1033.2</v>
-      </c>
-      <c r="F178" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6">
+      <c r="E178" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="11">
         <v>46241.438888888886</v>
       </c>
@@ -4456,15 +3753,11 @@
       <c r="D179" s="6">
         <v>20</v>
       </c>
-      <c r="E179" s="12">
-        <f>IF(F179="Sell",D179*C179*-1,D179*C179)</f>
-        <v>1018</v>
-      </c>
-      <c r="F179" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
+      <c r="E179" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="11">
         <v>46241.443749999999</v>
       </c>
@@ -4477,15 +3770,11 @@
       <c r="D180" s="6">
         <v>1.5</v>
       </c>
-      <c r="E180" s="12">
-        <f>IF(F180="Sell",D180*C180*-1,D180*C180)</f>
-        <v>-1157.8799999999999</v>
-      </c>
-      <c r="F180" s="12" t="s">
+      <c r="E180" s="12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="11">
         <v>46247.428472222222</v>
       </c>
@@ -4498,15 +3787,11 @@
       <c r="D181" s="6">
         <v>20</v>
       </c>
-      <c r="E181" s="12">
-        <f>IF(F181="Sell",D181*C181*-1,D181*C181)</f>
-        <v>-953.40000000000009</v>
-      </c>
-      <c r="F181" s="12" t="s">
+      <c r="E181" s="12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="11">
         <v>46247.438194444447</v>
       </c>
@@ -4519,17 +3804,217 @@
       <c r="D182" s="6">
         <v>10</v>
       </c>
-      <c r="E182" s="12">
-        <f>IF(F182="Sell",D182*C182*-1,D182*C182)</f>
-        <v>459.7</v>
-      </c>
-      <c r="F182" s="2" t="s">
+      <c r="E182" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="11">
+        <v>46254.537499999999</v>
+      </c>
+      <c r="B183" t="s">
+        <v>72</v>
+      </c>
+      <c r="C183" s="12">
+        <v>41.15</v>
+      </c>
+      <c r="D183" s="6">
+        <v>10</v>
+      </c>
+      <c r="E183" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="11">
+        <v>46255.398611111108</v>
+      </c>
+      <c r="B184" t="s">
+        <v>19</v>
+      </c>
+      <c r="C184" s="12">
+        <v>546.4</v>
+      </c>
+      <c r="D184" s="6">
+        <v>2</v>
+      </c>
+      <c r="E184" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="11">
+        <v>46258.410416666666</v>
+      </c>
+      <c r="B185" t="s">
+        <v>62</v>
+      </c>
+      <c r="C185" s="12">
+        <v>105.18</v>
+      </c>
+      <c r="D185" s="6">
+        <v>7.42</v>
+      </c>
+      <c r="E185" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="11">
+        <v>46259.657638888886</v>
+      </c>
+      <c r="B186" t="s">
+        <v>73</v>
+      </c>
+      <c r="C186" s="12">
+        <v>309.26</v>
+      </c>
+      <c r="D186" s="6">
+        <v>4</v>
+      </c>
+      <c r="E186" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="11">
+        <v>46260.643750000003</v>
+      </c>
+      <c r="B187" t="s">
+        <v>67</v>
+      </c>
+      <c r="C187" s="12">
+        <v>205.54</v>
+      </c>
+      <c r="D187" s="6">
+        <v>5</v>
+      </c>
+      <c r="E187" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="11">
+        <v>46260.644444444442</v>
+      </c>
+      <c r="B188" t="s">
+        <v>74</v>
+      </c>
+      <c r="C188" s="12">
+        <v>130.28</v>
+      </c>
+      <c r="D188" s="6">
+        <v>7.67</v>
+      </c>
+      <c r="E188" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="11">
+        <v>46260.657638888886</v>
+      </c>
+      <c r="B189" t="s">
+        <v>75</v>
+      </c>
+      <c r="C189" s="12">
+        <v>209.73</v>
+      </c>
+      <c r="D189" s="6">
+        <v>4.76</v>
+      </c>
+      <c r="E189" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="11">
+        <v>46261.431250000001</v>
+      </c>
+      <c r="B190" t="s">
+        <v>55</v>
+      </c>
+      <c r="C190" s="12">
+        <v>932.61</v>
+      </c>
+      <c r="D190" s="6">
+        <v>2</v>
+      </c>
+      <c r="E190" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="11">
+        <v>46261.435416666667</v>
+      </c>
+      <c r="B191" t="s">
+        <v>67</v>
+      </c>
+      <c r="C191" s="12">
+        <v>249.04</v>
+      </c>
+      <c r="D191" s="6">
+        <v>5</v>
+      </c>
+      <c r="E191" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="11">
+        <v>46261.435416666667</v>
+      </c>
+      <c r="B192" t="s">
+        <v>74</v>
+      </c>
+      <c r="C192" s="12">
+        <v>164.57</v>
+      </c>
+      <c r="D192" s="6">
+        <v>7.67</v>
+      </c>
+      <c r="E192" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="11">
+        <v>46261.439583333333</v>
+      </c>
+      <c r="B193" t="s">
+        <v>75</v>
+      </c>
+      <c r="C193" s="12">
+        <v>225.31</v>
+      </c>
+      <c r="D193" s="6">
+        <v>4.76</v>
+      </c>
+      <c r="E193" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="11">
+        <v>46261.46875</v>
+      </c>
+      <c r="B194" t="s">
+        <v>13</v>
+      </c>
+      <c r="C194" s="12">
+        <v>13.42</v>
+      </c>
+      <c r="D194" s="6">
+        <v>67.62</v>
+      </c>
+      <c r="E194" s="12" t="s">
         <v>70</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F169" xr:uid="{C1E503C2-5372-44CA-920E-B8461526100B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F182">
+  <autoFilter ref="A1:E194" xr:uid="{C1E503C2-5372-44CA-920E-B8461526100B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E182">
       <sortCondition ref="A1:A182"/>
     </sortState>
   </autoFilter>
@@ -4540,17 +4025,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64184D08-D91B-1043-AEE3-17C45FED0F30}">
   <dimension ref="A1:F174"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="5" customWidth="1"/>
     <col min="4" max="4" width="21.5" style="5" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="6" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="2"/>
+    <col min="6" max="6" width="10.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4570,7 +4055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45903.418749999997</v>
       </c>
@@ -4591,7 +4076,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45903.43472222222</v>
       </c>
@@ -4612,7 +4097,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45903.435416666667</v>
       </c>
@@ -4633,7 +4118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45903.436111111114</v>
       </c>
@@ -4654,7 +4139,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45903.436805555553</v>
       </c>
@@ -4675,7 +4160,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45903.438194444447</v>
       </c>
@@ -4696,7 +4181,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45903.438888888886</v>
       </c>
@@ -4717,7 +4202,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45903.445138888892</v>
       </c>
@@ -4738,7 +4223,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45903.445833333331</v>
       </c>
@@ -4758,7 +4243,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45903.448611111111</v>
       </c>
@@ -4779,7 +4264,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45903.455555555556</v>
       </c>
@@ -4800,7 +4285,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45903.463888888888</v>
       </c>
@@ -4821,7 +4306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45903.46597222222</v>
       </c>
@@ -4842,7 +4327,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45903.467361111114</v>
       </c>
@@ -4863,7 +4348,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45903.46875</v>
       </c>
@@ -4884,7 +4369,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>45903.470138888886</v>
       </c>
@@ -4905,7 +4390,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45903.474999999999</v>
       </c>
@@ -4926,7 +4411,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>45903.476388888892</v>
       </c>
@@ -4947,7 +4432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>45903.479861111111</v>
       </c>
@@ -4968,7 +4453,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>45903.480555555558</v>
       </c>
@@ -4989,7 +4474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>45903.493750000001</v>
       </c>
@@ -5010,7 +4495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -5031,7 +4516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>45903.494444444441</v>
       </c>
@@ -5052,7 +4537,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>45903.495138888888</v>
       </c>
@@ -5073,7 +4558,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>45903.504861111112</v>
       </c>
@@ -5094,7 +4579,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>45904.404861111114</v>
       </c>
@@ -5115,7 +4600,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>45904.406944444447</v>
       </c>
@@ -5136,7 +4621,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>45904.407638888886</v>
       </c>
@@ -5157,7 +4642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>45904.412499999999</v>
       </c>
@@ -5178,7 +4663,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>45904.414583333331</v>
       </c>
@@ -5199,7 +4684,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>45904.418749999997</v>
       </c>
@@ -5220,7 +4705,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>45905.408333333333</v>
       </c>
@@ -5241,7 +4726,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>45908.665277777778</v>
       </c>
@@ -5262,7 +4747,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>45909.415277777778</v>
       </c>
@@ -5283,7 +4768,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>45909.418055555558</v>
       </c>
@@ -5304,7 +4789,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>45909.427083333336</v>
       </c>
@@ -5325,7 +4810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>45909.427777777775</v>
       </c>
@@ -5346,7 +4831,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>45909.431250000001</v>
       </c>
@@ -5367,7 +4852,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>45909.43472222222</v>
       </c>
@@ -5388,7 +4873,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>45909.439583333333</v>
       </c>
@@ -5409,7 +4894,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -5430,7 +4915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>45909.449305555558</v>
       </c>
@@ -5451,7 +4936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>45910</v>
       </c>
@@ -5472,7 +4957,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>45910</v>
       </c>
@@ -5493,7 +4978,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45911</v>
       </c>
@@ -5514,7 +4999,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45911</v>
       </c>
@@ -5535,7 +5020,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>45912</v>
       </c>
@@ -5556,7 +5041,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>45912</v>
       </c>
@@ -5577,7 +5062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>45912</v>
       </c>
@@ -5598,7 +5083,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>45912</v>
       </c>
@@ -5619,7 +5104,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>45923</v>
       </c>
@@ -5640,7 +5125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>45923</v>
       </c>
@@ -5661,7 +5146,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>45923</v>
       </c>
@@ -5682,7 +5167,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>45923</v>
       </c>
@@ -5703,7 +5188,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>45923</v>
       </c>
@@ -5724,7 +5209,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>45923</v>
       </c>
@@ -5745,7 +5230,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>45924</v>
       </c>
@@ -5766,7 +5251,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>45924</v>
       </c>
@@ -5787,7 +5272,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>45929</v>
       </c>
@@ -5808,7 +5293,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>45937</v>
       </c>
@@ -5829,7 +5314,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>45937</v>
       </c>
@@ -5850,7 +5335,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>45937</v>
       </c>
@@ -5871,7 +5356,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>45937.40625</v>
       </c>
@@ -5892,7 +5377,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>45937.462500000001</v>
       </c>
@@ -5913,7 +5398,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>45937.465277777781</v>
       </c>
@@ -5934,7 +5419,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>45938.413194444445</v>
       </c>
@@ -5954,7 +5439,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>45939.417361111111</v>
       </c>
@@ -5974,7 +5459,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>45943.410416666666</v>
       </c>
@@ -5994,7 +5479,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>45943.411805555559</v>
       </c>
@@ -6015,7 +5500,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>45943.412499999999</v>
       </c>
@@ -6035,7 +5520,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>45943.413194444445</v>
       </c>
@@ -6055,7 +5540,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>45943.415277777778</v>
       </c>
@@ -6075,7 +5560,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>45943.417361111111</v>
       </c>
@@ -6095,7 +5580,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>45946.399305555555</v>
       </c>
@@ -6115,7 +5600,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>45957.457638888889</v>
       </c>
@@ -6135,7 +5620,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>45957.459722222222</v>
       </c>
@@ -6155,7 +5640,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>45957.460416666669</v>
       </c>
@@ -6175,7 +5660,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>45957.462500000001</v>
       </c>
@@ -6195,7 +5680,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>45957.463194444441</v>
       </c>
@@ -6215,7 +5700,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>45957.463888888888</v>
       </c>
@@ -6235,7 +5720,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -6255,7 +5740,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>45957.464583333334</v>
       </c>
@@ -6275,7 +5760,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -6295,7 +5780,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>45957.470833333333</v>
       </c>
@@ -6315,7 +5800,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>45957.47152777778</v>
       </c>
@@ -6335,7 +5820,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>45958.512499999997</v>
       </c>
@@ -6355,7 +5840,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>45958.515277777777</v>
       </c>
@@ -6375,7 +5860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>45958.517361111109</v>
       </c>
@@ -6395,7 +5880,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>45958.520138888889</v>
       </c>
@@ -6415,7 +5900,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -6435,7 +5920,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>45958.522222222222</v>
       </c>
@@ -6455,7 +5940,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>45958.529166666667</v>
       </c>
@@ -6475,7 +5960,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>45965.642361111109</v>
       </c>
@@ -6495,7 +5980,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>45974.67291666667</v>
       </c>
@@ -6515,7 +6000,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46002</v>
       </c>
@@ -6535,7 +6020,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46002.439583333333</v>
       </c>
@@ -6555,7 +6040,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46002.443749999999</v>
       </c>
@@ -6575,7 +6060,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>46002.446527777778</v>
       </c>
@@ -6595,7 +6080,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>46008.648611111108</v>
       </c>
@@ -6615,7 +6100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>46008.650694444441</v>
       </c>
@@ -6635,7 +6120,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>46020.463888888888</v>
       </c>
@@ -6655,7 +6140,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>46021.472916666666</v>
       </c>
@@ -6675,7 +6160,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46027.567361111112</v>
       </c>
@@ -6695,7 +6180,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>46027.568055555559</v>
       </c>
@@ -6715,7 +6200,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>46027.568749999999</v>
       </c>
@@ -6735,7 +6220,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46029.449305555558</v>
       </c>
@@ -6755,7 +6240,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -6775,7 +6260,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>46034.47152777778</v>
       </c>
@@ -6795,7 +6280,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>46035.44027777778</v>
       </c>
@@ -6815,7 +6300,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>46035.441666666666</v>
       </c>
@@ -6835,7 +6320,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>46036.448611111111</v>
       </c>
@@ -6855,7 +6340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>46042.44027777778</v>
       </c>
@@ -6875,7 +6360,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>46042.441666666666</v>
       </c>
@@ -6895,7 +6380,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>46042.45</v>
       </c>
@@ -6915,7 +6400,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -6935,7 +6420,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>46044.496527777781</v>
       </c>
@@ -6956,7 +6441,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>46044.49722222222</v>
       </c>
@@ -6976,7 +6461,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>46045.445833333331</v>
       </c>
@@ -6996,7 +6481,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>46045.493055555555</v>
       </c>
@@ -7016,7 +6501,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>46048.572222222225</v>
       </c>
@@ -7036,7 +6521,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>46049.448611111111</v>
       </c>
@@ -7056,7 +6541,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>46050.563888888886</v>
       </c>
@@ -7076,7 +6561,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>46055.650694444441</v>
       </c>
@@ -7096,7 +6581,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>46055.652083333334</v>
       </c>
@@ -7116,7 +6601,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>46059</v>
       </c>
@@ -7136,7 +6621,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>46083.456250000003</v>
       </c>
@@ -7156,7 +6641,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>46086</v>
       </c>
@@ -7176,7 +6661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>46087</v>
       </c>
@@ -7196,7 +6681,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>46087</v>
       </c>
@@ -7216,7 +6701,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>46087</v>
       </c>
@@ -7236,7 +6721,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>46087</v>
       </c>
@@ -7256,7 +6741,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>46087</v>
       </c>
@@ -7276,7 +6761,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>46087</v>
       </c>
@@ -7296,7 +6781,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>46087</v>
       </c>
@@ -7316,7 +6801,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>46090</v>
       </c>
@@ -7336,7 +6821,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>46090</v>
       </c>
@@ -7356,7 +6841,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>46090</v>
       </c>
@@ -7376,7 +6861,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>46090</v>
       </c>
@@ -7396,7 +6881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>46090</v>
       </c>
@@ -7416,7 +6901,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>46091</v>
       </c>
@@ -7436,7 +6921,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>46091</v>
       </c>
@@ -7456,7 +6941,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>46091</v>
       </c>
@@ -7476,7 +6961,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>46091</v>
       </c>
@@ -7496,7 +6981,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>46091</v>
       </c>
@@ -7516,7 +7001,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>46092</v>
       </c>
@@ -7536,7 +7021,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>46100</v>
       </c>
@@ -7557,7 +7042,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>46100</v>
       </c>
@@ -7577,7 +7062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>46113</v>
       </c>
@@ -7597,7 +7082,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>46113</v>
       </c>
@@ -7617,7 +7102,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>46113</v>
       </c>
@@ -7637,7 +7122,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>46114</v>
       </c>
@@ -7657,7 +7142,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>46128</v>
       </c>
@@ -7677,7 +7162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>46128</v>
       </c>
@@ -7697,7 +7182,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>46113</v>
       </c>
@@ -7717,7 +7202,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>46113</v>
       </c>
@@ -7737,7 +7222,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>46114</v>
       </c>
@@ -7757,7 +7242,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>46128</v>
       </c>
@@ -7777,7 +7262,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>46128</v>
       </c>
@@ -7797,7 +7282,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>46150</v>
       </c>
@@ -7818,7 +7303,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>46153</v>
       </c>
@@ -7839,7 +7324,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>46174</v>
       </c>
@@ -7860,7 +7345,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>46175</v>
       </c>
@@ -7881,7 +7366,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>46175</v>
       </c>
@@ -7902,7 +7387,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>46177</v>
       </c>
@@ -7923,7 +7408,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>46181</v>
       </c>
@@ -7944,7 +7429,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>46181</v>
       </c>
@@ -7965,7 +7450,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>46204</v>
       </c>
@@ -7986,7 +7471,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>46227</v>
       </c>
@@ -8007,7 +7492,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>46230</v>
       </c>
@@ -8028,7 +7513,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>46231</v>
       </c>
@@ -8049,7 +7534,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>46233</v>
       </c>
@@ -8070,7 +7555,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>46233</v>
       </c>
@@ -8091,7 +7576,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>46233</v>
       </c>
